--- a/data/50001508 - XEMORTIZ STOCK.xlsx
+++ b/data/50001508 - XEMORTIZ STOCK.xlsx
@@ -1395,13 +1395,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.407749907405</v>
+        <v>46073.574416574076</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55430670139</v>
+        <v>46092.72097336805</v>
       </c>
       <c r="D4" s="5">
-        <v>46092.55432038194</v>
+        <v>46092.72098704861</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1448,13 +1448,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46073.40775033565</v>
+        <v>46073.57441700231</v>
       </c>
       <c r="C5" s="9">
-        <v>46092.554275752314</v>
+        <v>46092.72094241898</v>
       </c>
       <c r="D5" s="9">
-        <v>46092.554307094906</v>
+        <v>46092.72097376158</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1511,13 +1511,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.40775064815</v>
+        <v>46073.57441731481</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55427634259</v>
+        <v>46092.72094300926</v>
       </c>
       <c r="D6" s="5">
-        <v>46133.72324875</v>
+        <v>46133.88991541667</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1574,13 +1574,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="9">
-        <v>46073.407750949074</v>
+        <v>46073.574417615746</v>
       </c>
       <c r="C7" s="9">
-        <v>46092.55427680556</v>
+        <v>46092.72094347222</v>
       </c>
       <c r="D7" s="9">
-        <v>46133.723297847224</v>
+        <v>46133.88996451389</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>39</v>
@@ -1637,13 +1637,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.40775128472</v>
+        <v>46073.574417951386</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.554277268515</v>
+        <v>46092.72094393519</v>
       </c>
       <c r="D8" s="5">
-        <v>46133.724536319445</v>
+        <v>46133.89120298611</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1700,13 +1700,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46073.40775158565</v>
+        <v>46073.57441825232</v>
       </c>
       <c r="C9" s="9">
-        <v>46092.55427813657</v>
+        <v>46092.72094480324</v>
       </c>
       <c r="D9" s="9">
-        <v>46133.72464994213</v>
+        <v>46133.891316608795</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -1763,13 +1763,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.40775292824</v>
+        <v>46073.57441959491</v>
       </c>
       <c r="C10" s="5">
-        <v>46114.352509131946</v>
+        <v>46114.51917579861</v>
       </c>
       <c r="D10" s="5">
-        <v>46139.37187028935</v>
+        <v>46139.53853695602</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -1812,13 +1812,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="9">
-        <v>46073.40775053241</v>
+        <v>46073.574417199074</v>
       </c>
       <c r="C11" s="9">
-        <v>46097.38446746528</v>
+        <v>46097.55113413194</v>
       </c>
       <c r="D11" s="9">
-        <v>46097.38448552083</v>
+        <v>46097.5511521875</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -1877,13 +1877,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.40775118055</v>
+        <v>46073.57441784722</v>
       </c>
       <c r="C12" s="5">
-        <v>46114.35229440972</v>
+        <v>46114.51896107639</v>
       </c>
       <c r="D12" s="5">
-        <v>46133.73070047454</v>
+        <v>46133.8973671412</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -1942,13 +1942,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="9">
-        <v>46073.407751446764</v>
+        <v>46073.57441811342</v>
       </c>
       <c r="C13" s="9">
-        <v>46097.38480086805</v>
+        <v>46097.55146753472</v>
       </c>
       <c r="D13" s="9">
-        <v>46097.384814907404</v>
+        <v>46097.551481574075</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>58</v>
@@ -2007,13 +2007,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.407751736115</v>
+        <v>46073.57441840278</v>
       </c>
       <c r="C14" s="5">
-        <v>46134.44046914352</v>
+        <v>46134.60713581018</v>
       </c>
       <c r="D14" s="5">
-        <v>46134.440470347225</v>
+        <v>46134.60713701389</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2072,13 +2072,13 @@
         <v>62</v>
       </c>
       <c r="B15" s="9">
-        <v>46073.40775200231</v>
+        <v>46073.574418668984</v>
       </c>
       <c r="C15" s="9">
-        <v>46114.35522046297</v>
+        <v>46114.52188712963</v>
       </c>
       <c r="D15" s="9">
-        <v>46114.355231180554</v>
+        <v>46114.521897847226</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>63</v>
@@ -2125,13 +2125,13 @@
         <v>65</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.40775229166</v>
+        <v>46073.574418958335</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.35517708333</v>
+        <v>46114.52184375</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.35535027778</v>
+        <v>46114.522016944444</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>66</v>
@@ -2190,13 +2190,13 @@
         <v>68</v>
       </c>
       <c r="B17" s="9">
-        <v>46073.407753125</v>
+        <v>46073.574419791665</v>
       </c>
       <c r="C17" s="9">
-        <v>46114.35520486112</v>
+        <v>46114.52187152777</v>
       </c>
       <c r="D17" s="9">
-        <v>46133.72593783565</v>
+        <v>46133.89260450231</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>69</v>
@@ -2255,13 +2255,13 @@
         <v>73</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.407752569445</v>
+        <v>46073.574419236116</v>
       </c>
       <c r="C18" s="5">
-        <v>46097.38451211806</v>
+        <v>46097.55117878472</v>
       </c>
       <c r="D18" s="5">
-        <v>46133.72968005787</v>
+        <v>46133.896346724534</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>74</v>
@@ -2320,13 +2320,13 @@
         <v>77</v>
       </c>
       <c r="B19" s="9">
-        <v>46073.40774984953</v>
+        <v>46073.5744165162</v>
       </c>
       <c r="C19" s="9">
-        <v>46097.38483890046</v>
+        <v>46097.55150556713</v>
       </c>
       <c r="D19" s="9">
-        <v>46100.6192175926</v>
+        <v>46100.785884259254</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>78</v>
@@ -2385,13 +2385,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.40775021991</v>
+        <v>46073.57441688658</v>
       </c>
       <c r="C20" s="5">
-        <v>46134.440416412035</v>
+        <v>46134.60708307871</v>
       </c>
       <c r="D20" s="5">
-        <v>46134.440435219905</v>
+        <v>46134.60710188658</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2438,13 +2438,13 @@
         <v>85</v>
       </c>
       <c r="B21" s="9">
-        <v>46073.4077508912</v>
+        <v>46073.57441755787</v>
       </c>
       <c r="C21" s="9">
-        <v>46114.61439836805</v>
+        <v>46114.781065034724</v>
       </c>
       <c r="D21" s="9">
-        <v>46133.725540451385</v>
+        <v>46133.89220711806</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>86</v>
@@ -2503,13 +2503,13 @@
         <v>90</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.407751192135</v>
+        <v>46073.57441785879</v>
       </c>
       <c r="C22" s="5">
-        <v>46114.614341319444</v>
+        <v>46114.78100798611</v>
       </c>
       <c r="D22" s="5">
-        <v>46114.61434273148</v>
+        <v>46114.78100939815</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -2564,13 +2564,13 @@
         <v>95</v>
       </c>
       <c r="B23" s="9">
-        <v>46073.407751481485</v>
+        <v>46073.57441814815</v>
       </c>
       <c r="C23" s="9">
-        <v>46114.61438329861</v>
+        <v>46114.78104996528</v>
       </c>
       <c r="D23" s="9">
-        <v>46114.61438478009</v>
+        <v>46114.78105144676</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>96</v>
@@ -2625,13 +2625,13 @@
         <v>98</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.40775269676</v>
+        <v>46073.57441936343</v>
       </c>
       <c r="C24" s="5">
-        <v>46133.73091304398</v>
+        <v>46133.89757971065</v>
       </c>
       <c r="D24" s="5">
-        <v>46133.73092556713</v>
+        <v>46133.8975922338</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>99</v>
@@ -2690,13 +2690,13 @@
         <v>101</v>
       </c>
       <c r="B25" s="9">
-        <v>46073.40775298611</v>
+        <v>46073.57441965278</v>
       </c>
       <c r="C25" s="9">
-        <v>46122.537756412035</v>
+        <v>46122.7044230787</v>
       </c>
       <c r="D25" s="9">
-        <v>46122.537758101855</v>
+        <v>46122.70442476852</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>102</v>
@@ -2751,13 +2751,13 @@
         <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.40774980324</v>
+        <v>46073.574416469906</v>
       </c>
       <c r="C26" s="5">
-        <v>46133.73089946759</v>
+        <v>46133.897566134256</v>
       </c>
       <c r="D26" s="5">
-        <v>46133.730901006944</v>
+        <v>46133.897567673615</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -2812,13 +2812,13 @@
         <v>107</v>
       </c>
       <c r="B27" s="9">
-        <v>46073.40775017361</v>
+        <v>46073.574416840274</v>
       </c>
       <c r="C27" s="9">
-        <v>46097.384699664355</v>
+        <v>46097.55136633102</v>
       </c>
       <c r="D27" s="9">
-        <v>46097.38471313658</v>
+        <v>46097.55137980324</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>108</v>
@@ -2877,13 +2877,13 @@
         <v>110</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.40775046297</v>
+        <v>46073.574417129625</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.38461346064</v>
+        <v>46097.551280127314</v>
       </c>
       <c r="D28" s="5">
-        <v>46097.38461493056</v>
+        <v>46097.55128159722</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>111</v>
@@ -2938,13 +2938,13 @@
         <v>113</v>
       </c>
       <c r="B29" s="9">
-        <v>46073.407750729166</v>
+        <v>46073.57441739584</v>
       </c>
       <c r="C29" s="9">
-        <v>46097.384648148145</v>
+        <v>46097.55131481482</v>
       </c>
       <c r="D29" s="9">
-        <v>46097.38464950232</v>
+        <v>46097.55131616898</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>114</v>
@@ -2999,13 +2999,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.40775103009</v>
+        <v>46073.57441769676</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.38468446759</v>
+        <v>46097.55135113426</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.38468596065</v>
+        <v>46097.55135262731</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>117</v>
@@ -3060,13 +3060,13 @@
         <v>119</v>
       </c>
       <c r="B31" s="9">
-        <v>46073.40775128472</v>
+        <v>46073.574417951386</v>
       </c>
       <c r="C31" s="9">
-        <v>46111.63208436343</v>
+        <v>46111.79875103009</v>
       </c>
       <c r="D31" s="9">
-        <v>46111.632097361115</v>
+        <v>46111.79876402778</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>120</v>
@@ -3125,13 +3125,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.40775155093</v>
+        <v>46073.57441821759</v>
       </c>
       <c r="C32" s="5">
-        <v>46097.38526033565</v>
+        <v>46097.551927002314</v>
       </c>
       <c r="D32" s="5">
-        <v>46097.38526181713</v>
+        <v>46097.551928483794</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3186,13 +3186,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="9">
-        <v>46073.40775180556</v>
+        <v>46073.57441847222</v>
       </c>
       <c r="C33" s="9">
-        <v>46111.63206998842</v>
+        <v>46111.798736655095</v>
       </c>
       <c r="D33" s="9">
-        <v>46111.63207150463</v>
+        <v>46111.798738171296</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>128</v>
@@ -3247,11 +3247,11 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.40775208334</v>
+        <v>46073.574418749995</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46108.6014222338</v>
+        <v>46108.76808890046</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3294,13 +3294,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="9">
-        <v>46073.407752349536</v>
+        <v>46073.57441901621</v>
       </c>
       <c r="C35" s="9">
-        <v>46108.60108274306</v>
+        <v>46108.76774940972</v>
       </c>
       <c r="D35" s="9">
-        <v>46108.6010999537</v>
+        <v>46108.76776662037</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>134</v>
@@ -3359,13 +3359,13 @@
         <v>138</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.40775028935</v>
+        <v>46073.57441695602</v>
       </c>
       <c r="C36" s="5">
-        <v>46108.60118219907</v>
+        <v>46108.76784886574</v>
       </c>
       <c r="D36" s="5">
-        <v>46108.60119883102</v>
+        <v>46108.767865497684</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>139</v>
@@ -3424,13 +3424,13 @@
         <v>142</v>
       </c>
       <c r="B37" s="9">
-        <v>46090.529563310185</v>
+        <v>46090.69622997685</v>
       </c>
       <c r="C37" s="9">
-        <v>46108.60141636574</v>
+        <v>46108.76808303241</v>
       </c>
       <c r="D37" s="9">
-        <v>46108.60143265047</v>
+        <v>46108.76809931713</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>143</v>
@@ -3489,11 +3489,11 @@
         <v>145</v>
       </c>
       <c r="B38" s="5">
-        <v>46090.52978670139</v>
+        <v>46090.69645336806</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46127.526258819446</v>
+        <v>46127.69292548611</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>146</v>
@@ -3552,13 +3552,13 @@
         <v>151</v>
       </c>
       <c r="B39" s="9">
-        <v>46073.4077505787</v>
+        <v>46073.57441724537</v>
       </c>
       <c r="C39" s="9">
-        <v>46111.63221431713</v>
+        <v>46111.7988809838</v>
       </c>
       <c r="D39" s="9">
-        <v>46111.63222694444</v>
+        <v>46111.79889361111</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>152</v>
@@ -3605,13 +3605,13 @@
         <v>154</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.40775079861</v>
+        <v>46073.57441746528</v>
       </c>
       <c r="C40" s="5">
-        <v>46111.63215450232</v>
+        <v>46111.79882116898</v>
       </c>
       <c r="D40" s="5">
-        <v>46111.63217065972</v>
+        <v>46111.798837326394</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>155</v>
@@ -3670,13 +3670,13 @@
         <v>159</v>
       </c>
       <c r="B41" s="9">
-        <v>46073.40775103009</v>
+        <v>46073.57441769676</v>
       </c>
       <c r="C41" s="9">
-        <v>46111.632198287036</v>
+        <v>46111.7988649537</v>
       </c>
       <c r="D41" s="9">
-        <v>46111.632214178244</v>
+        <v>46111.79888084491</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>160</v>
@@ -3735,11 +3735,11 @@
         <v>163</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.40775126158</v>
+        <v>46073.57441792824</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46146.396794953704</v>
+        <v>46146.563461620375</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>164</v>
@@ -3782,13 +3782,13 @@
         <v>166</v>
       </c>
       <c r="B43" s="9">
-        <v>46073.407751493054</v>
+        <v>46073.574418159726</v>
       </c>
       <c r="C43" s="9">
-        <v>46107.56083722222</v>
+        <v>46107.72750388889</v>
       </c>
       <c r="D43" s="9">
-        <v>46113.389261018514</v>
+        <v>46113.555927685185</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>167</v>
@@ -3847,13 +3847,13 @@
         <v>172</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.40775171296</v>
+        <v>46073.574418379634</v>
       </c>
       <c r="C44" s="5">
-        <v>46146.39678314815</v>
+        <v>46146.563449814814</v>
       </c>
       <c r="D44" s="5">
-        <v>46146.45547221065</v>
+        <v>46146.62213887731</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>173</v>
@@ -3912,11 +3912,11 @@
         <v>176</v>
       </c>
       <c r="B45" s="9">
-        <v>46073.40775194444</v>
+        <v>46073.57441861111</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46157.6872724537</v>
+        <v>46157.85393912037</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>177</v>
@@ -3975,11 +3975,11 @@
         <v>180</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.4077521875</v>
+        <v>46073.57441885417</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46127.48360924768</v>
+        <v>46127.65027591435</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>152</v>
@@ -4022,13 +4022,13 @@
         <v>182</v>
       </c>
       <c r="B47" s="9">
-        <v>46073.40775005787</v>
+        <v>46073.574416724536</v>
       </c>
       <c r="C47" s="9">
-        <v>46127.48360153935</v>
+        <v>46127.65026820602</v>
       </c>
       <c r="D47" s="9">
-        <v>46127.48373905093</v>
+        <v>46127.65040571759</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>183</v>
@@ -4087,11 +4087,11 @@
         <v>185</v>
       </c>
       <c r="B48" s="5">
-        <v>46073.40775244213</v>
+        <v>46073.5744191088</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46157.70016392361</v>
+        <v>46157.86683059028</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>186</v>
@@ -4150,13 +4150,13 @@
         <v>188</v>
       </c>
       <c r="B49" s="9">
-        <v>46073.40775033565</v>
+        <v>46073.57441700231</v>
       </c>
       <c r="C49" s="9">
-        <v>46122.48811438658</v>
+        <v>46122.654781053236</v>
       </c>
       <c r="D49" s="9">
-        <v>46122.488134652776</v>
+        <v>46122.65480131944</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>189</v>
@@ -4215,11 +4215,11 @@
         <v>191</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.40775060185</v>
+        <v>46073.57441726852</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46090.5349555787</v>
+        <v>46090.70162224537</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>192</v>
@@ -4262,11 +4262,11 @@
         <v>194</v>
       </c>
       <c r="B51" s="9">
-        <v>46073.407751192135</v>
+        <v>46073.57441785879</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46184.419481550925</v>
+        <v>46184.5861482176</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>195</v>
@@ -4325,11 +4325,11 @@
         <v>197</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.4077514699</v>
+        <v>46073.57441813657</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46122.48812170139</v>
+        <v>46122.654788368054</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>198</v>
@@ -4388,11 +4388,11 @@
         <v>201</v>
       </c>
       <c r="B53" s="9">
-        <v>46073.40775171296</v>
+        <v>46073.574418379634</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46127.483610034724</v>
+        <v>46127.65027670139</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>202</v>
@@ -4451,11 +4451,11 @@
         <v>204</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.40775196759</v>
+        <v>46073.57441863426</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46108.60142795139</v>
+        <v>46108.768094618055</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>205</v>
@@ -4514,11 +4514,11 @@
         <v>207</v>
       </c>
       <c r="B55" s="9">
-        <v>46073.40775226852</v>
+        <v>46073.57441893518</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46101.97055766203</v>
+        <v>46102.137224328704</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>149</v>
@@ -4575,11 +4575,11 @@
         <v>210</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.407752534724</v>
+        <v>46073.57441920139</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46105.95859030093</v>
+        <v>46106.12525696759</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>211</v>
@@ -4636,11 +4636,11 @@
         <v>213</v>
       </c>
       <c r="B57" s="9">
-        <v>46073.40775020834</v>
+        <v>46073.574416874995</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46090.5351549537</v>
+        <v>46090.70182162037</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>214</v>
@@ -4683,11 +4683,11 @@
         <v>216</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.407750555554</v>
+        <v>46073.57441722222</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46133.731815046296</v>
+        <v>46133.89848171297</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>217</v>
@@ -4744,11 +4744,11 @@
         <v>220</v>
       </c>
       <c r="B59" s="9">
-        <v>46073.407750810184</v>
+        <v>46073.57441747685</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46107.99797167824</v>
+        <v>46108.16463834491</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>221</v>
@@ -4805,11 +4805,11 @@
         <v>223</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.40775108796</v>
+        <v>46073.57441775463</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46108.08432915509</v>
+        <v>46108.250995821756</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>224</v>
@@ -4868,11 +4868,11 @@
         <v>226</v>
       </c>
       <c r="B61" s="9">
-        <v>46073.40775134259</v>
+        <v>46073.57441800926</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46111.96357416667</v>
+        <v>46112.13024083333</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>227</v>
@@ -4931,11 +4931,11 @@
         <v>229</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.4077516088</v>
+        <v>46073.574418275464</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46090.53515497685</v>
+        <v>46090.70182164352</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>230</v>
@@ -4978,11 +4978,11 @@
         <v>232</v>
       </c>
       <c r="B63" s="9">
-        <v>46073.40775190972</v>
+        <v>46073.57441857639</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46121.00034344908</v>
+        <v>46121.167010115736</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>233</v>
@@ -5041,11 +5041,11 @@
         <v>236</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.407752175925</v>
+        <v>46073.57441884259</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46121.00034346065</v>
+        <v>46121.16701012732</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>237</v>

--- a/data/50001508 - XEMORTIZ STOCK.xlsx
+++ b/data/50001508 - XEMORTIZ STOCK.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="238">
   <si>
     <t>50001508 - XEMORTIZ STOCK</t>
   </si>
@@ -3977,9 +3977,11 @@
       <c r="B46" s="5">
         <v>46073.57441885417</v>
       </c>
-      <c r="C46" s="6"/>
+      <c r="C46" s="5">
+        <v>46195.60707819444</v>
+      </c>
       <c r="D46" s="5">
-        <v>46127.65027591435</v>
+        <v>46195.607089745376</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>152</v>
@@ -4014,8 +4016,12 @@
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
       <c r="S46" s="6"/>
-      <c r="T46" s="6"/>
-      <c r="U46" s="6"/>
+      <c r="T46" s="6">
+        <v>1</v>
+      </c>
+      <c r="U46" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
@@ -4089,9 +4095,11 @@
       <c r="B48" s="5">
         <v>46073.5744191088</v>
       </c>
-      <c r="C48" s="6"/>
+      <c r="C48" s="5">
+        <v>46195.607060462964</v>
+      </c>
       <c r="D48" s="5">
-        <v>46157.86683059028</v>
+        <v>46195.607078368055</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>186</v>
@@ -4139,10 +4147,10 @@
         <v>32</v>
       </c>
       <c r="T48" s="6">
-        <v>0</v>
-      </c>
-      <c r="U48" s="12" t="s">
-        <v>171</v>
+        <v>1</v>
+      </c>
+      <c r="U48" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -4455,7 +4463,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46108.768094618055</v>
+        <v>46195.60706916667</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>205</v>

--- a/data/50001508 - XEMORTIZ STOCK.xlsx
+++ b/data/50001508 - XEMORTIZ STOCK.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="238">
   <si>
     <t>50001508 - XEMORTIZ STOCK</t>
   </si>
@@ -3737,9 +3737,11 @@
       <c r="B42" s="5">
         <v>46073.57441792824</v>
       </c>
-      <c r="C42" s="6"/>
+      <c r="C42" s="5">
+        <v>46195.91189378472</v>
+      </c>
       <c r="D42" s="5">
-        <v>46146.563461620375</v>
+        <v>46195.91191255787</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>164</v>
@@ -3774,8 +3776,12 @@
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
       <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
+      <c r="T42" s="6">
+        <v>1</v>
+      </c>
+      <c r="U42" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
@@ -3853,7 +3859,7 @@
         <v>46146.563449814814</v>
       </c>
       <c r="D44" s="5">
-        <v>46146.62213887731</v>
+        <v>46195.911566111114</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>173</v>
@@ -3914,9 +3920,11 @@
       <c r="B45" s="9">
         <v>46073.57441861111</v>
       </c>
-      <c r="C45" s="10"/>
+      <c r="C45" s="9">
+        <v>46195.91187329861</v>
+      </c>
       <c r="D45" s="9">
-        <v>46157.85393912037</v>
+        <v>46195.91189555556</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>177</v>
@@ -3964,10 +3972,10 @@
         <v>32</v>
       </c>
       <c r="T45" s="10">
-        <v>0</v>
-      </c>
-      <c r="U45" s="12" t="s">
-        <v>171</v>
+        <v>1</v>
+      </c>
+      <c r="U45" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
@@ -4274,7 +4282,7 @@
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46184.5861482176</v>
+        <v>46195.911894756944</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>195</v>
@@ -4324,8 +4332,8 @@
       <c r="T51" s="10">
         <v>0</v>
       </c>
-      <c r="U51" s="11" t="s">
-        <v>94</v>
+      <c r="U51" s="12" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001508 - XEMORTIZ STOCK.xlsx
+++ b/data/50001508 - XEMORTIZ STOCK.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="238">
   <si>
     <t>50001508 - XEMORTIZ STOCK</t>
   </si>
@@ -570,82 +570,82 @@
     <t>Armado,Caldereria:</t>
   </si>
   <si>
+    <t>1213377491559689</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Check Planos</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,Caldereria:</t>
+  </si>
+  <si>
+    <t>1213377491559690</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>Armado,Check Planos</t>
+  </si>
+  <si>
+    <t>Caldereria:,Revestimiento</t>
+  </si>
+  <si>
+    <t>1213377491559691</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete,Recepcion Alabe,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1213333053701053</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1213377491559692</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1213333053701054</t>
+  </si>
+  <si>
+    <t>Recepcion motor</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje motor</t>
+  </si>
+  <si>
+    <t>1213333053701055</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Revestimiento,Montaje motor,Montaje Alabe,Montaje Rodete,Pruebas FAT,RE-PINTADO</t>
+  </si>
+  <si>
+    <t>1213333053701056</t>
+  </si>
+  <si>
+    <t>Revestimiento</t>
+  </si>
+  <si>
+    <t>Montaje motor,Montaje Alabe,Montaje Rodete,Montaje:</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1213377491559689</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Check Planos</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,Caldereria:</t>
-  </si>
-  <si>
-    <t>1213377491559690</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>Armado,Check Planos</t>
-  </si>
-  <si>
-    <t>Caldereria:,Revestimiento</t>
-  </si>
-  <si>
-    <t>1213377491559691</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete,Recepcion Alabe,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1213333053701053</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1213377491559692</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1213333053701054</t>
-  </si>
-  <si>
-    <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje motor</t>
-  </si>
-  <si>
-    <t>1213333053701055</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Revestimiento,Montaje motor,Montaje Alabe,Montaje Rodete,Pruebas FAT,RE-PINTADO</t>
-  </si>
-  <si>
-    <t>1213333053701056</t>
-  </si>
-  <si>
-    <t>Revestimiento</t>
-  </si>
-  <si>
-    <t>Montaje motor,Montaje Alabe,Montaje Rodete,Montaje:</t>
   </si>
   <si>
     <t>1213333053701057</t>
@@ -3741,7 +3741,7 @@
         <v>46195.91189378472</v>
       </c>
       <c r="D42" s="5">
-        <v>46195.91191255787</v>
+        <v>46196.8510114699</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>164</v>
@@ -3776,12 +3776,8 @@
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
       <c r="S42" s="6"/>
-      <c r="T42" s="6">
-        <v>1</v>
-      </c>
-      <c r="U42" s="7" t="s">
-        <v>27</v>
-      </c>
+      <c r="T42" s="6"/>
+      <c r="U42" s="6"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
@@ -3794,7 +3790,7 @@
         <v>46107.72750388889</v>
       </c>
       <c r="D43" s="9">
-        <v>46113.555927685185</v>
+        <v>46196.850968819446</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>167</v>
@@ -3844,13 +3840,13 @@
       <c r="T43" s="10">
         <v>1</v>
       </c>
-      <c r="U43" s="12" t="s">
-        <v>171</v>
+      <c r="U43" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B44" s="5">
         <v>46073.574418379634</v>
@@ -3862,7 +3858,7 @@
         <v>46195.911566111114</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
@@ -3892,10 +3888,10 @@
         <v>164</v>
       </c>
       <c r="O44" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="P44" s="6" t="s">
         <v>174</v>
-      </c>
-      <c r="P44" s="6" t="s">
-        <v>175</v>
       </c>
       <c r="Q44" s="5">
         <v>46087</v>
@@ -3915,7 +3911,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B45" s="9">
         <v>46073.57441861111</v>
@@ -3927,7 +3923,7 @@
         <v>46195.91189555556</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
@@ -3957,10 +3953,10 @@
         <v>164</v>
       </c>
       <c r="O45" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="P45" s="10" t="s">
         <v>178</v>
-      </c>
-      <c r="P45" s="10" t="s">
-        <v>179</v>
       </c>
       <c r="Q45" s="9">
         <v>46090</v>
@@ -3980,7 +3976,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B46" s="5">
         <v>46073.57441885417</v>
@@ -4016,7 +4012,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4033,7 +4029,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B47" s="9">
         <v>46073.574416724536</v>
@@ -4045,7 +4041,7 @@
         <v>46127.65040571759</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
@@ -4078,7 +4074,7 @@
         <v>96</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q47" s="9">
         <v>46049</v>
@@ -4098,7 +4094,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B48" s="5">
         <v>46073.5744191088</v>
@@ -4110,7 +4106,7 @@
         <v>46195.607078368055</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
@@ -4143,7 +4139,7 @@
         <v>105</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q48" s="5">
         <v>46065</v>
@@ -4163,7 +4159,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B49" s="9">
         <v>46073.57441700231</v>
@@ -4175,7 +4171,7 @@
         <v>46122.65480131944</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
@@ -4208,7 +4204,7 @@
         <v>114</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q49" s="9">
         <v>46083</v>
@@ -4228,7 +4224,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B50" s="5">
         <v>46073.57441726852</v>
@@ -4238,7 +4234,7 @@
         <v>46090.70162224537</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4262,7 +4258,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4275,7 +4271,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B51" s="9">
         <v>46073.57441785879</v>
@@ -4285,7 +4281,7 @@
         <v>46195.911894756944</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4312,13 +4308,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q51" s="9">
         <v>46097</v>
@@ -4333,7 +4329,7 @@
         <v>0</v>
       </c>
       <c r="U51" s="12" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4375,7 +4371,7 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>199</v>
@@ -4438,7 +4434,7 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O53" s="10" t="s">
         <v>203</v>
@@ -4501,7 +4497,7 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>206</v>
@@ -4562,7 +4558,7 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>208</v>
@@ -4623,7 +4619,7 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>146</v>

--- a/data/50001508 - XEMORTIZ STOCK.xlsx
+++ b/data/50001508 - XEMORTIZ STOCK.xlsx
@@ -3920,7 +3920,7 @@
         <v>46195.91187329861</v>
       </c>
       <c r="D45" s="9">
-        <v>46195.91189555556</v>
+        <v>46196.91052092593</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>176</v>

--- a/data/50001508 - XEMORTIZ STOCK.xlsx
+++ b/data/50001508 - XEMORTIZ STOCK.xlsx
@@ -510,6 +510,9 @@
     <t>Ingenieria y diseñoo:,RE-PINTADO</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
     <t>1213377491559684</t>
   </si>
   <si>
@@ -643,9 +646,6 @@
   </si>
   <si>
     <t>Montaje motor,Montaje Alabe,Montaje Rodete,Montaje:</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1213333053701057</t>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46127.69292548611</v>
+        <v>46197.505977395835</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>146</v>
@@ -3543,13 +3543,13 @@
       <c r="T38" s="6">
         <v>0</v>
       </c>
-      <c r="U38" s="11" t="s">
-        <v>94</v>
+      <c r="U38" s="12" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B39" s="9">
         <v>46073.57441724537</v>
@@ -3561,7 +3561,7 @@
         <v>46111.79889361111</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>25</v>
@@ -3585,7 +3585,7 @@
         <v>26</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3602,7 +3602,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B40" s="5">
         <v>46073.57441746528</v>
@@ -3614,16 +3614,16 @@
         <v>46111.798837326394</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I40" s="5">
         <v>46072</v>
@@ -3641,13 +3641,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>128</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q40" s="5">
         <v>46073</v>
@@ -3667,7 +3667,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B41" s="9">
         <v>46073.57441769676</v>
@@ -3679,16 +3679,16 @@
         <v>46111.79888084491</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I41" s="9">
         <v>46076</v>
@@ -3706,13 +3706,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q41" s="9">
         <v>46077</v>
@@ -3732,7 +3732,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B42" s="5">
         <v>46073.57441792824</v>
@@ -3744,7 +3744,7 @@
         <v>46196.8510114699</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3768,7 +3768,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3781,7 +3781,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B43" s="9">
         <v>46073.574418159726</v>
@@ -3793,16 +3793,16 @@
         <v>46196.850968819446</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I43" s="9">
         <v>46078</v>
@@ -3820,13 +3820,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q43" s="9">
         <v>46080</v>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B44" s="5">
         <v>46073.574418379634</v>
@@ -3858,16 +3858,16 @@
         <v>46195.911566111114</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I44" s="5">
         <v>46083</v>
@@ -3885,13 +3885,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q44" s="5">
         <v>46087</v>
@@ -3911,7 +3911,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B45" s="9">
         <v>46073.57441861111</v>
@@ -3923,16 +3923,16 @@
         <v>46196.91052092593</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I45" s="9">
         <v>46090</v>
@@ -3950,13 +3950,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q45" s="9">
         <v>46090</v>
@@ -3976,7 +3976,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B46" s="5">
         <v>46073.57441885417</v>
@@ -3988,7 +3988,7 @@
         <v>46195.607089745376</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4012,7 +4012,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4029,7 +4029,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B47" s="9">
         <v>46073.574416724536</v>
@@ -4041,16 +4041,16 @@
         <v>46127.65040571759</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I47" s="9">
         <v>46049</v>
@@ -4068,13 +4068,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>96</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q47" s="9">
         <v>46049</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B48" s="5">
         <v>46073.5744191088</v>
@@ -4106,16 +4106,16 @@
         <v>46195.607078368055</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I48" s="5">
         <v>46065</v>
@@ -4133,13 +4133,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>105</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q48" s="5">
         <v>46065</v>
@@ -4159,7 +4159,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B49" s="9">
         <v>46073.57441700231</v>
@@ -4171,16 +4171,16 @@
         <v>46122.65480131944</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I49" s="9">
         <v>46083</v>
@@ -4198,13 +4198,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O49" s="10" t="s">
         <v>114</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q49" s="9">
         <v>46083</v>
@@ -4224,17 +4224,17 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B50" s="5">
         <v>46073.57441726852</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46090.70162224537</v>
+        <v>46197.505966261575</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4258,7 +4258,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4271,17 +4271,19 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B51" s="9">
         <v>46073.57441785879</v>
       </c>
-      <c r="C51" s="10"/>
+      <c r="C51" s="9">
+        <v>46197.50546392361</v>
+      </c>
       <c r="D51" s="9">
-        <v>46195.911894756944</v>
+        <v>46197.50548082176</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4308,13 +4310,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q51" s="9">
         <v>46097</v>
@@ -4326,10 +4328,10 @@
         <v>32</v>
       </c>
       <c r="T51" s="10">
-        <v>0</v>
-      </c>
-      <c r="U51" s="12" t="s">
-        <v>196</v>
+        <v>1</v>
+      </c>
+      <c r="U51" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4339,9 +4341,11 @@
       <c r="B52" s="5">
         <v>46073.57441813657</v>
       </c>
-      <c r="C52" s="6"/>
+      <c r="C52" s="5">
+        <v>46197.50555307871</v>
+      </c>
       <c r="D52" s="5">
-        <v>46122.654788368054</v>
+        <v>46197.50556809027</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>198</v>
@@ -4371,7 +4375,7 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>199</v>
@@ -4389,10 +4393,10 @@
         <v>32</v>
       </c>
       <c r="T52" s="6">
-        <v>0</v>
-      </c>
-      <c r="U52" s="11" t="s">
-        <v>94</v>
+        <v>1</v>
+      </c>
+      <c r="U52" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -4402,9 +4406,11 @@
       <c r="B53" s="9">
         <v>46073.574418379634</v>
       </c>
-      <c r="C53" s="10"/>
+      <c r="C53" s="9">
+        <v>46197.50557114583</v>
+      </c>
       <c r="D53" s="9">
-        <v>46127.65027670139</v>
+        <v>46197.50558877314</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>202</v>
@@ -4434,7 +4440,7 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O53" s="10" t="s">
         <v>203</v>
@@ -4452,10 +4458,10 @@
         <v>32</v>
       </c>
       <c r="T53" s="10">
-        <v>0</v>
-      </c>
-      <c r="U53" s="11" t="s">
-        <v>94</v>
+        <v>1</v>
+      </c>
+      <c r="U53" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
@@ -4465,9 +4471,11 @@
       <c r="B54" s="5">
         <v>46073.57441863426</v>
       </c>
-      <c r="C54" s="6"/>
+      <c r="C54" s="5">
+        <v>46197.505863240745</v>
+      </c>
       <c r="D54" s="5">
-        <v>46195.60706916667</v>
+        <v>46197.5058797338</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>205</v>
@@ -4497,7 +4505,7 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>206</v>
@@ -4515,10 +4523,10 @@
         <v>32</v>
       </c>
       <c r="T54" s="6">
-        <v>0</v>
-      </c>
-      <c r="U54" s="11" t="s">
-        <v>94</v>
+        <v>1</v>
+      </c>
+      <c r="U54" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -4528,9 +4536,11 @@
       <c r="B55" s="9">
         <v>46073.57441893518</v>
       </c>
-      <c r="C55" s="10"/>
+      <c r="C55" s="9">
+        <v>46197.505959166665</v>
+      </c>
       <c r="D55" s="9">
-        <v>46102.137224328704</v>
+        <v>46197.50597680555</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>149</v>
@@ -4558,7 +4568,7 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>208</v>
@@ -4576,10 +4586,10 @@
         <v>32</v>
       </c>
       <c r="T55" s="10">
-        <v>0</v>
-      </c>
-      <c r="U55" s="11" t="s">
-        <v>94</v>
+        <v>1</v>
+      </c>
+      <c r="U55" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -4619,7 +4629,7 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>146</v>
@@ -4830,10 +4840,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I60" s="5">
         <v>46108</v>
@@ -4893,10 +4903,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I61" s="9">
         <v>46111</v>

--- a/data/50001508 - XEMORTIZ STOCK.xlsx
+++ b/data/50001508 - XEMORTIZ STOCK.xlsx
@@ -1395,13 +1395,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.574416574076</v>
+        <v>46073.407749907405</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.72097336805</v>
+        <v>46092.55430670139</v>
       </c>
       <c r="D4" s="5">
-        <v>46092.72098704861</v>
+        <v>46092.55432038194</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1448,13 +1448,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46073.57441700231</v>
+        <v>46073.40775033565</v>
       </c>
       <c r="C5" s="9">
-        <v>46092.72094241898</v>
+        <v>46092.554275752314</v>
       </c>
       <c r="D5" s="9">
-        <v>46092.72097376158</v>
+        <v>46092.554307094906</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1511,13 +1511,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.57441731481</v>
+        <v>46073.40775064815</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.72094300926</v>
+        <v>46092.55427634259</v>
       </c>
       <c r="D6" s="5">
-        <v>46133.88991541667</v>
+        <v>46133.72324875</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1574,13 +1574,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="9">
-        <v>46073.574417615746</v>
+        <v>46073.407750949074</v>
       </c>
       <c r="C7" s="9">
-        <v>46092.72094347222</v>
+        <v>46092.55427680556</v>
       </c>
       <c r="D7" s="9">
-        <v>46133.88996451389</v>
+        <v>46133.723297847224</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>39</v>
@@ -1637,13 +1637,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.574417951386</v>
+        <v>46073.40775128472</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.72094393519</v>
+        <v>46092.554277268515</v>
       </c>
       <c r="D8" s="5">
-        <v>46133.89120298611</v>
+        <v>46133.724536319445</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1700,13 +1700,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46073.57441825232</v>
+        <v>46073.40775158565</v>
       </c>
       <c r="C9" s="9">
-        <v>46092.72094480324</v>
+        <v>46092.55427813657</v>
       </c>
       <c r="D9" s="9">
-        <v>46133.891316608795</v>
+        <v>46133.72464994213</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -1763,13 +1763,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.57441959491</v>
+        <v>46073.40775292824</v>
       </c>
       <c r="C10" s="5">
-        <v>46114.51917579861</v>
+        <v>46114.352509131946</v>
       </c>
       <c r="D10" s="5">
-        <v>46139.53853695602</v>
+        <v>46139.37187028935</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -1812,13 +1812,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="9">
-        <v>46073.574417199074</v>
+        <v>46073.40775053241</v>
       </c>
       <c r="C11" s="9">
-        <v>46097.55113413194</v>
+        <v>46097.38446746528</v>
       </c>
       <c r="D11" s="9">
-        <v>46097.5511521875</v>
+        <v>46097.38448552083</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -1877,13 +1877,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.57441784722</v>
+        <v>46073.40775118055</v>
       </c>
       <c r="C12" s="5">
-        <v>46114.51896107639</v>
+        <v>46114.35229440972</v>
       </c>
       <c r="D12" s="5">
-        <v>46133.8973671412</v>
+        <v>46133.73070047454</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -1942,13 +1942,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="9">
-        <v>46073.57441811342</v>
+        <v>46073.407751446764</v>
       </c>
       <c r="C13" s="9">
-        <v>46097.55146753472</v>
+        <v>46097.38480086805</v>
       </c>
       <c r="D13" s="9">
-        <v>46097.551481574075</v>
+        <v>46097.384814907404</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>58</v>
@@ -2007,13 +2007,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.57441840278</v>
+        <v>46073.407751736115</v>
       </c>
       <c r="C14" s="5">
-        <v>46134.60713581018</v>
+        <v>46134.44046914352</v>
       </c>
       <c r="D14" s="5">
-        <v>46134.60713701389</v>
+        <v>46134.440470347225</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2072,13 +2072,13 @@
         <v>62</v>
       </c>
       <c r="B15" s="9">
-        <v>46073.574418668984</v>
+        <v>46073.40775200231</v>
       </c>
       <c r="C15" s="9">
-        <v>46114.52188712963</v>
+        <v>46114.35522046297</v>
       </c>
       <c r="D15" s="9">
-        <v>46114.521897847226</v>
+        <v>46114.355231180554</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>63</v>
@@ -2125,13 +2125,13 @@
         <v>65</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.574418958335</v>
+        <v>46073.40775229166</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.52184375</v>
+        <v>46114.35517708333</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.522016944444</v>
+        <v>46114.35535027778</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>66</v>
@@ -2190,13 +2190,13 @@
         <v>68</v>
       </c>
       <c r="B17" s="9">
-        <v>46073.574419791665</v>
+        <v>46073.407753125</v>
       </c>
       <c r="C17" s="9">
-        <v>46114.52187152777</v>
+        <v>46114.35520486112</v>
       </c>
       <c r="D17" s="9">
-        <v>46133.89260450231</v>
+        <v>46133.72593783565</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>69</v>
@@ -2255,13 +2255,13 @@
         <v>73</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.574419236116</v>
+        <v>46073.407752569445</v>
       </c>
       <c r="C18" s="5">
-        <v>46097.55117878472</v>
+        <v>46097.38451211806</v>
       </c>
       <c r="D18" s="5">
-        <v>46133.896346724534</v>
+        <v>46133.72968005787</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>74</v>
@@ -2320,13 +2320,13 @@
         <v>77</v>
       </c>
       <c r="B19" s="9">
-        <v>46073.5744165162</v>
+        <v>46073.40774984953</v>
       </c>
       <c r="C19" s="9">
-        <v>46097.55150556713</v>
+        <v>46097.38483890046</v>
       </c>
       <c r="D19" s="9">
-        <v>46100.785884259254</v>
+        <v>46100.6192175926</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>78</v>
@@ -2385,13 +2385,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.57441688658</v>
+        <v>46073.40775021991</v>
       </c>
       <c r="C20" s="5">
-        <v>46134.60708307871</v>
+        <v>46134.440416412035</v>
       </c>
       <c r="D20" s="5">
-        <v>46134.60710188658</v>
+        <v>46134.440435219905</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2438,13 +2438,13 @@
         <v>85</v>
       </c>
       <c r="B21" s="9">
-        <v>46073.57441755787</v>
+        <v>46073.4077508912</v>
       </c>
       <c r="C21" s="9">
-        <v>46114.781065034724</v>
+        <v>46114.61439836805</v>
       </c>
       <c r="D21" s="9">
-        <v>46133.89220711806</v>
+        <v>46133.725540451385</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>86</v>
@@ -2503,13 +2503,13 @@
         <v>90</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.57441785879</v>
+        <v>46073.407751192135</v>
       </c>
       <c r="C22" s="5">
-        <v>46114.78100798611</v>
+        <v>46114.614341319444</v>
       </c>
       <c r="D22" s="5">
-        <v>46114.78100939815</v>
+        <v>46114.61434273148</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -2564,13 +2564,13 @@
         <v>95</v>
       </c>
       <c r="B23" s="9">
-        <v>46073.57441814815</v>
+        <v>46073.407751481485</v>
       </c>
       <c r="C23" s="9">
-        <v>46114.78104996528</v>
+        <v>46114.61438329861</v>
       </c>
       <c r="D23" s="9">
-        <v>46114.78105144676</v>
+        <v>46114.61438478009</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>96</v>
@@ -2625,13 +2625,13 @@
         <v>98</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.57441936343</v>
+        <v>46073.40775269676</v>
       </c>
       <c r="C24" s="5">
-        <v>46133.89757971065</v>
+        <v>46133.73091304398</v>
       </c>
       <c r="D24" s="5">
-        <v>46133.8975922338</v>
+        <v>46133.73092556713</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>99</v>
@@ -2690,13 +2690,13 @@
         <v>101</v>
       </c>
       <c r="B25" s="9">
-        <v>46073.57441965278</v>
+        <v>46073.40775298611</v>
       </c>
       <c r="C25" s="9">
-        <v>46122.7044230787</v>
+        <v>46122.537756412035</v>
       </c>
       <c r="D25" s="9">
-        <v>46122.70442476852</v>
+        <v>46122.537758101855</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>102</v>
@@ -2751,13 +2751,13 @@
         <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.574416469906</v>
+        <v>46073.40774980324</v>
       </c>
       <c r="C26" s="5">
-        <v>46133.897566134256</v>
+        <v>46133.73089946759</v>
       </c>
       <c r="D26" s="5">
-        <v>46133.897567673615</v>
+        <v>46133.730901006944</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -2812,13 +2812,13 @@
         <v>107</v>
       </c>
       <c r="B27" s="9">
-        <v>46073.574416840274</v>
+        <v>46073.40775017361</v>
       </c>
       <c r="C27" s="9">
-        <v>46097.55136633102</v>
+        <v>46097.384699664355</v>
       </c>
       <c r="D27" s="9">
-        <v>46097.55137980324</v>
+        <v>46097.38471313658</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>108</v>
@@ -2877,13 +2877,13 @@
         <v>110</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.574417129625</v>
+        <v>46073.40775046297</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.551280127314</v>
+        <v>46097.38461346064</v>
       </c>
       <c r="D28" s="5">
-        <v>46097.55128159722</v>
+        <v>46097.38461493056</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>111</v>
@@ -2938,13 +2938,13 @@
         <v>113</v>
       </c>
       <c r="B29" s="9">
-        <v>46073.57441739584</v>
+        <v>46073.407750729166</v>
       </c>
       <c r="C29" s="9">
-        <v>46097.55131481482</v>
+        <v>46097.384648148145</v>
       </c>
       <c r="D29" s="9">
-        <v>46097.55131616898</v>
+        <v>46097.38464950232</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>114</v>
@@ -2999,13 +2999,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.57441769676</v>
+        <v>46073.40775103009</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.55135113426</v>
+        <v>46097.38468446759</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.55135262731</v>
+        <v>46097.38468596065</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>117</v>
@@ -3060,13 +3060,13 @@
         <v>119</v>
       </c>
       <c r="B31" s="9">
-        <v>46073.574417951386</v>
+        <v>46073.40775128472</v>
       </c>
       <c r="C31" s="9">
-        <v>46111.79875103009</v>
+        <v>46111.63208436343</v>
       </c>
       <c r="D31" s="9">
-        <v>46111.79876402778</v>
+        <v>46111.632097361115</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>120</v>
@@ -3125,13 +3125,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.57441821759</v>
+        <v>46073.40775155093</v>
       </c>
       <c r="C32" s="5">
-        <v>46097.551927002314</v>
+        <v>46097.38526033565</v>
       </c>
       <c r="D32" s="5">
-        <v>46097.551928483794</v>
+        <v>46097.38526181713</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3186,13 +3186,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="9">
-        <v>46073.57441847222</v>
+        <v>46073.40775180556</v>
       </c>
       <c r="C33" s="9">
-        <v>46111.798736655095</v>
+        <v>46111.63206998842</v>
       </c>
       <c r="D33" s="9">
-        <v>46111.798738171296</v>
+        <v>46111.63207150463</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>128</v>
@@ -3247,11 +3247,11 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.574418749995</v>
+        <v>46073.40775208334</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46108.76808890046</v>
+        <v>46108.6014222338</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3294,13 +3294,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="9">
-        <v>46073.57441901621</v>
+        <v>46073.407752349536</v>
       </c>
       <c r="C35" s="9">
-        <v>46108.76774940972</v>
+        <v>46108.60108274306</v>
       </c>
       <c r="D35" s="9">
-        <v>46108.76776662037</v>
+        <v>46108.6010999537</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>134</v>
@@ -3359,13 +3359,13 @@
         <v>138</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.57441695602</v>
+        <v>46073.40775028935</v>
       </c>
       <c r="C36" s="5">
-        <v>46108.76784886574</v>
+        <v>46108.60118219907</v>
       </c>
       <c r="D36" s="5">
-        <v>46108.767865497684</v>
+        <v>46108.60119883102</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>139</v>
@@ -3424,13 +3424,13 @@
         <v>142</v>
       </c>
       <c r="B37" s="9">
-        <v>46090.69622997685</v>
+        <v>46090.529563310185</v>
       </c>
       <c r="C37" s="9">
-        <v>46108.76808303241</v>
+        <v>46108.60141636574</v>
       </c>
       <c r="D37" s="9">
-        <v>46108.76809931713</v>
+        <v>46108.60143265047</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>143</v>
@@ -3489,11 +3489,11 @@
         <v>145</v>
       </c>
       <c r="B38" s="5">
-        <v>46090.69645336806</v>
+        <v>46090.52978670139</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46197.505977395835</v>
+        <v>46197.33931072916</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>146</v>
@@ -3552,13 +3552,13 @@
         <v>152</v>
       </c>
       <c r="B39" s="9">
-        <v>46073.57441724537</v>
+        <v>46073.4077505787</v>
       </c>
       <c r="C39" s="9">
-        <v>46111.7988809838</v>
+        <v>46111.63221431713</v>
       </c>
       <c r="D39" s="9">
-        <v>46111.79889361111</v>
+        <v>46111.63222694444</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>153</v>
@@ -3605,13 +3605,13 @@
         <v>155</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.57441746528</v>
+        <v>46073.40775079861</v>
       </c>
       <c r="C40" s="5">
-        <v>46111.79882116898</v>
+        <v>46111.63215450232</v>
       </c>
       <c r="D40" s="5">
-        <v>46111.798837326394</v>
+        <v>46111.63217065972</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>156</v>
@@ -3670,13 +3670,13 @@
         <v>160</v>
       </c>
       <c r="B41" s="9">
-        <v>46073.57441769676</v>
+        <v>46073.40775103009</v>
       </c>
       <c r="C41" s="9">
-        <v>46111.7988649537</v>
+        <v>46111.632198287036</v>
       </c>
       <c r="D41" s="9">
-        <v>46111.79888084491</v>
+        <v>46111.632214178244</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>161</v>
@@ -3735,13 +3735,13 @@
         <v>164</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.57441792824</v>
+        <v>46073.40775126158</v>
       </c>
       <c r="C42" s="5">
-        <v>46195.91189378472</v>
+        <v>46195.74522711805</v>
       </c>
       <c r="D42" s="5">
-        <v>46196.8510114699</v>
+        <v>46196.684344803245</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>165</v>
@@ -3784,13 +3784,13 @@
         <v>167</v>
       </c>
       <c r="B43" s="9">
-        <v>46073.574418159726</v>
+        <v>46073.407751493054</v>
       </c>
       <c r="C43" s="9">
-        <v>46107.72750388889</v>
+        <v>46107.56083722222</v>
       </c>
       <c r="D43" s="9">
-        <v>46196.850968819446</v>
+        <v>46196.684302152775</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>168</v>
@@ -3849,13 +3849,13 @@
         <v>172</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.574418379634</v>
+        <v>46073.40775171296</v>
       </c>
       <c r="C44" s="5">
-        <v>46146.563449814814</v>
+        <v>46146.39678314815</v>
       </c>
       <c r="D44" s="5">
-        <v>46195.911566111114</v>
+        <v>46195.74489944444</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>173</v>
@@ -3914,13 +3914,13 @@
         <v>176</v>
       </c>
       <c r="B45" s="9">
-        <v>46073.57441861111</v>
+        <v>46073.40775194444</v>
       </c>
       <c r="C45" s="9">
-        <v>46195.91187329861</v>
+        <v>46195.745206631946</v>
       </c>
       <c r="D45" s="9">
-        <v>46196.91052092593</v>
+        <v>46196.74385425926</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>177</v>
@@ -3979,13 +3979,13 @@
         <v>180</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.57441885417</v>
+        <v>46073.4077521875</v>
       </c>
       <c r="C46" s="5">
-        <v>46195.60707819444</v>
+        <v>46195.44041152778</v>
       </c>
       <c r="D46" s="5">
-        <v>46195.607089745376</v>
+        <v>46195.440423078704</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>153</v>
@@ -4032,13 +4032,13 @@
         <v>182</v>
       </c>
       <c r="B47" s="9">
-        <v>46073.574416724536</v>
+        <v>46073.40775005787</v>
       </c>
       <c r="C47" s="9">
-        <v>46127.65026820602</v>
+        <v>46127.48360153935</v>
       </c>
       <c r="D47" s="9">
-        <v>46127.65040571759</v>
+        <v>46127.48373905093</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>183</v>
@@ -4097,13 +4097,13 @@
         <v>185</v>
       </c>
       <c r="B48" s="5">
-        <v>46073.5744191088</v>
+        <v>46073.40775244213</v>
       </c>
       <c r="C48" s="5">
-        <v>46195.607060462964</v>
+        <v>46195.44039379629</v>
       </c>
       <c r="D48" s="5">
-        <v>46195.607078368055</v>
+        <v>46195.44041170139</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>186</v>
@@ -4162,13 +4162,13 @@
         <v>188</v>
       </c>
       <c r="B49" s="9">
-        <v>46073.57441700231</v>
+        <v>46073.40775033565</v>
       </c>
       <c r="C49" s="9">
-        <v>46122.654781053236</v>
+        <v>46122.48811438658</v>
       </c>
       <c r="D49" s="9">
-        <v>46122.65480131944</v>
+        <v>46122.488134652776</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>189</v>
@@ -4227,11 +4227,11 @@
         <v>191</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.57441726852</v>
+        <v>46073.40775060185</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46197.505966261575</v>
+        <v>46197.33929959491</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>192</v>
@@ -4274,13 +4274,13 @@
         <v>194</v>
       </c>
       <c r="B51" s="9">
-        <v>46073.57441785879</v>
+        <v>46073.407751192135</v>
       </c>
       <c r="C51" s="9">
-        <v>46197.50546392361</v>
+        <v>46197.33879725695</v>
       </c>
       <c r="D51" s="9">
-        <v>46197.50548082176</v>
+        <v>46197.3388141551</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>195</v>
@@ -4339,13 +4339,13 @@
         <v>197</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.57441813657</v>
+        <v>46073.4077514699</v>
       </c>
       <c r="C52" s="5">
-        <v>46197.50555307871</v>
+        <v>46197.338886412035</v>
       </c>
       <c r="D52" s="5">
-        <v>46197.50556809027</v>
+        <v>46197.338901423616</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>198</v>
@@ -4404,13 +4404,13 @@
         <v>201</v>
       </c>
       <c r="B53" s="9">
-        <v>46073.574418379634</v>
+        <v>46073.40775171296</v>
       </c>
       <c r="C53" s="9">
-        <v>46197.50557114583</v>
+        <v>46197.33890447917</v>
       </c>
       <c r="D53" s="9">
-        <v>46197.50558877314</v>
+        <v>46197.338922106486</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>202</v>
@@ -4469,13 +4469,13 @@
         <v>204</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.57441863426</v>
+        <v>46073.40775196759</v>
       </c>
       <c r="C54" s="5">
-        <v>46197.505863240745</v>
+        <v>46197.339196574074</v>
       </c>
       <c r="D54" s="5">
-        <v>46197.5058797338</v>
+        <v>46197.33921306713</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>205</v>
@@ -4534,13 +4534,13 @@
         <v>207</v>
       </c>
       <c r="B55" s="9">
-        <v>46073.57441893518</v>
+        <v>46073.40775226852</v>
       </c>
       <c r="C55" s="9">
-        <v>46197.505959166665</v>
+        <v>46197.3392925</v>
       </c>
       <c r="D55" s="9">
-        <v>46197.50597680555</v>
+        <v>46197.339310138894</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>149</v>
@@ -4597,11 +4597,11 @@
         <v>210</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.57441920139</v>
+        <v>46073.407752534724</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46106.12525696759</v>
+        <v>46105.95859030093</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>211</v>
@@ -4658,11 +4658,11 @@
         <v>213</v>
       </c>
       <c r="B57" s="9">
-        <v>46073.574416874995</v>
+        <v>46073.40775020834</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46090.70182162037</v>
+        <v>46090.5351549537</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>214</v>
@@ -4705,11 +4705,11 @@
         <v>216</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.57441722222</v>
+        <v>46073.407750555554</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46133.89848171297</v>
+        <v>46133.731815046296</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>217</v>
@@ -4766,11 +4766,11 @@
         <v>220</v>
       </c>
       <c r="B59" s="9">
-        <v>46073.57441747685</v>
+        <v>46073.407750810184</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46108.16463834491</v>
+        <v>46107.99797167824</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>221</v>
@@ -4827,11 +4827,11 @@
         <v>223</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.57441775463</v>
+        <v>46073.40775108796</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46108.250995821756</v>
+        <v>46108.08432915509</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>224</v>
@@ -4890,11 +4890,11 @@
         <v>226</v>
       </c>
       <c r="B61" s="9">
-        <v>46073.57441800926</v>
+        <v>46073.40775134259</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46112.13024083333</v>
+        <v>46111.96357416667</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>227</v>
@@ -4953,11 +4953,11 @@
         <v>229</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.574418275464</v>
+        <v>46073.4077516088</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46090.70182164352</v>
+        <v>46090.53515497685</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>230</v>
@@ -5000,11 +5000,11 @@
         <v>232</v>
       </c>
       <c r="B63" s="9">
-        <v>46073.57441857639</v>
+        <v>46073.40775190972</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46121.167010115736</v>
+        <v>46121.00034344908</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>233</v>
@@ -5063,11 +5063,11 @@
         <v>236</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.57441884259</v>
+        <v>46073.407752175925</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46121.16701012732</v>
+        <v>46121.00034346065</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>237</v>

--- a/data/50001508 - XEMORTIZ STOCK.xlsx
+++ b/data/50001508 - XEMORTIZ STOCK.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="240">
   <si>
     <t>50001508 - XEMORTIZ STOCK</t>
   </si>
@@ -462,31 +462,37 @@
     <t>Plano Preliminar</t>
   </si>
   <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Plano Definitivos</t>
+  </si>
+  <si>
+    <t>1213377491559683</t>
+  </si>
+  <si>
+    <t>Plano Definitivos</t>
+  </si>
+  <si>
+    <t>Plano Preliminar,Planos motor proveedor</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Check Planos</t>
+  </si>
+  <si>
+    <t>1213575386156355</t>
+  </si>
+  <si>
+    <t>Check Planos</t>
+  </si>
+  <si>
     <t>Hernan Roberto Gutierrez Barrientos</t>
   </si>
   <si>
     <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Plano Definitivos</t>
-  </si>
-  <si>
-    <t>1213377491559683</t>
-  </si>
-  <si>
-    <t>Plano Definitivos</t>
-  </si>
-  <si>
-    <t>Plano Preliminar,Planos motor proveedor</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Check Planos</t>
-  </si>
-  <si>
-    <t>1213575386156355</t>
-  </si>
-  <si>
-    <t>Check Planos</t>
   </si>
   <si>
     <t>Ingenieria y diseñoo:,Control de calidad Armado,Armado,Montaje motor,Montaje Alabe,Montaje Rodete</t>
@@ -1395,13 +1401,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.407749907405</v>
+        <v>46073.574416574076</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55430670139</v>
+        <v>46092.72097336805</v>
       </c>
       <c r="D4" s="5">
-        <v>46092.55432038194</v>
+        <v>46092.72098704861</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1448,13 +1454,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46073.40775033565</v>
+        <v>46073.57441700231</v>
       </c>
       <c r="C5" s="9">
-        <v>46092.554275752314</v>
+        <v>46092.72094241898</v>
       </c>
       <c r="D5" s="9">
-        <v>46092.554307094906</v>
+        <v>46092.72097376158</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1511,13 +1517,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.40775064815</v>
+        <v>46073.57441731481</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55427634259</v>
+        <v>46092.72094300926</v>
       </c>
       <c r="D6" s="5">
-        <v>46133.72324875</v>
+        <v>46133.88991541667</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1574,13 +1580,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="9">
-        <v>46073.407750949074</v>
+        <v>46073.574417615746</v>
       </c>
       <c r="C7" s="9">
-        <v>46092.55427680556</v>
+        <v>46092.72094347222</v>
       </c>
       <c r="D7" s="9">
-        <v>46133.723297847224</v>
+        <v>46133.88996451389</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>39</v>
@@ -1637,13 +1643,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.40775128472</v>
+        <v>46073.574417951386</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.554277268515</v>
+        <v>46092.72094393519</v>
       </c>
       <c r="D8" s="5">
-        <v>46133.724536319445</v>
+        <v>46133.89120298611</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1700,13 +1706,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46073.40775158565</v>
+        <v>46073.57441825232</v>
       </c>
       <c r="C9" s="9">
-        <v>46092.55427813657</v>
+        <v>46092.72094480324</v>
       </c>
       <c r="D9" s="9">
-        <v>46133.72464994213</v>
+        <v>46133.891316608795</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -1763,13 +1769,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.40775292824</v>
+        <v>46073.57441959491</v>
       </c>
       <c r="C10" s="5">
-        <v>46114.352509131946</v>
+        <v>46114.51917579861</v>
       </c>
       <c r="D10" s="5">
-        <v>46139.37187028935</v>
+        <v>46139.53853695602</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -1812,13 +1818,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="9">
-        <v>46073.40775053241</v>
+        <v>46073.574417199074</v>
       </c>
       <c r="C11" s="9">
-        <v>46097.38446746528</v>
+        <v>46097.55113413194</v>
       </c>
       <c r="D11" s="9">
-        <v>46097.38448552083</v>
+        <v>46097.5511521875</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -1877,13 +1883,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.40775118055</v>
+        <v>46073.57441784722</v>
       </c>
       <c r="C12" s="5">
-        <v>46114.35229440972</v>
+        <v>46114.51896107639</v>
       </c>
       <c r="D12" s="5">
-        <v>46133.73070047454</v>
+        <v>46133.8973671412</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -1942,13 +1948,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="9">
-        <v>46073.407751446764</v>
+        <v>46073.57441811342</v>
       </c>
       <c r="C13" s="9">
-        <v>46097.38480086805</v>
+        <v>46097.55146753472</v>
       </c>
       <c r="D13" s="9">
-        <v>46097.384814907404</v>
+        <v>46097.551481574075</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>58</v>
@@ -2007,13 +2013,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.407751736115</v>
+        <v>46073.57441840278</v>
       </c>
       <c r="C14" s="5">
-        <v>46134.44046914352</v>
+        <v>46134.60713581018</v>
       </c>
       <c r="D14" s="5">
-        <v>46134.440470347225</v>
+        <v>46134.60713701389</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2072,13 +2078,13 @@
         <v>62</v>
       </c>
       <c r="B15" s="9">
-        <v>46073.40775200231</v>
+        <v>46073.574418668984</v>
       </c>
       <c r="C15" s="9">
-        <v>46114.35522046297</v>
+        <v>46114.52188712963</v>
       </c>
       <c r="D15" s="9">
-        <v>46114.355231180554</v>
+        <v>46114.521897847226</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>63</v>
@@ -2125,13 +2131,13 @@
         <v>65</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.40775229166</v>
+        <v>46073.574418958335</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.35517708333</v>
+        <v>46114.52184375</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.35535027778</v>
+        <v>46114.522016944444</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>66</v>
@@ -2190,13 +2196,13 @@
         <v>68</v>
       </c>
       <c r="B17" s="9">
-        <v>46073.407753125</v>
+        <v>46073.574419791665</v>
       </c>
       <c r="C17" s="9">
-        <v>46114.35520486112</v>
+        <v>46114.52187152777</v>
       </c>
       <c r="D17" s="9">
-        <v>46133.72593783565</v>
+        <v>46133.89260450231</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>69</v>
@@ -2255,13 +2261,13 @@
         <v>73</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.407752569445</v>
+        <v>46073.574419236116</v>
       </c>
       <c r="C18" s="5">
-        <v>46097.38451211806</v>
+        <v>46097.55117878472</v>
       </c>
       <c r="D18" s="5">
-        <v>46133.72968005787</v>
+        <v>46133.896346724534</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>74</v>
@@ -2320,13 +2326,13 @@
         <v>77</v>
       </c>
       <c r="B19" s="9">
-        <v>46073.40774984953</v>
+        <v>46073.5744165162</v>
       </c>
       <c r="C19" s="9">
-        <v>46097.38483890046</v>
+        <v>46097.55150556713</v>
       </c>
       <c r="D19" s="9">
-        <v>46100.6192175926</v>
+        <v>46100.785884259254</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>78</v>
@@ -2385,13 +2391,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.40775021991</v>
+        <v>46073.57441688658</v>
       </c>
       <c r="C20" s="5">
-        <v>46134.440416412035</v>
+        <v>46134.60708307871</v>
       </c>
       <c r="D20" s="5">
-        <v>46134.440435219905</v>
+        <v>46134.60710188658</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2438,13 +2444,13 @@
         <v>85</v>
       </c>
       <c r="B21" s="9">
-        <v>46073.4077508912</v>
+        <v>46073.57441755787</v>
       </c>
       <c r="C21" s="9">
-        <v>46114.61439836805</v>
+        <v>46114.781065034724</v>
       </c>
       <c r="D21" s="9">
-        <v>46133.725540451385</v>
+        <v>46133.89220711806</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>86</v>
@@ -2503,13 +2509,13 @@
         <v>90</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.407751192135</v>
+        <v>46073.57441785879</v>
       </c>
       <c r="C22" s="5">
-        <v>46114.614341319444</v>
+        <v>46114.78100798611</v>
       </c>
       <c r="D22" s="5">
-        <v>46114.61434273148</v>
+        <v>46114.78100939815</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -2564,13 +2570,13 @@
         <v>95</v>
       </c>
       <c r="B23" s="9">
-        <v>46073.407751481485</v>
+        <v>46073.57441814815</v>
       </c>
       <c r="C23" s="9">
-        <v>46114.61438329861</v>
+        <v>46114.78104996528</v>
       </c>
       <c r="D23" s="9">
-        <v>46114.61438478009</v>
+        <v>46114.78105144676</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>96</v>
@@ -2625,13 +2631,13 @@
         <v>98</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.40775269676</v>
+        <v>46073.57441936343</v>
       </c>
       <c r="C24" s="5">
-        <v>46133.73091304398</v>
+        <v>46133.89757971065</v>
       </c>
       <c r="D24" s="5">
-        <v>46133.73092556713</v>
+        <v>46133.8975922338</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>99</v>
@@ -2690,13 +2696,13 @@
         <v>101</v>
       </c>
       <c r="B25" s="9">
-        <v>46073.40775298611</v>
+        <v>46073.57441965278</v>
       </c>
       <c r="C25" s="9">
-        <v>46122.537756412035</v>
+        <v>46122.7044230787</v>
       </c>
       <c r="D25" s="9">
-        <v>46122.537758101855</v>
+        <v>46122.70442476852</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>102</v>
@@ -2751,13 +2757,13 @@
         <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.40774980324</v>
+        <v>46073.574416469906</v>
       </c>
       <c r="C26" s="5">
-        <v>46133.73089946759</v>
+        <v>46133.897566134256</v>
       </c>
       <c r="D26" s="5">
-        <v>46133.730901006944</v>
+        <v>46133.897567673615</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -2812,13 +2818,13 @@
         <v>107</v>
       </c>
       <c r="B27" s="9">
-        <v>46073.40775017361</v>
+        <v>46073.574416840274</v>
       </c>
       <c r="C27" s="9">
-        <v>46097.384699664355</v>
+        <v>46097.55136633102</v>
       </c>
       <c r="D27" s="9">
-        <v>46097.38471313658</v>
+        <v>46097.55137980324</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>108</v>
@@ -2877,13 +2883,13 @@
         <v>110</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.40775046297</v>
+        <v>46073.574417129625</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.38461346064</v>
+        <v>46097.551280127314</v>
       </c>
       <c r="D28" s="5">
-        <v>46097.38461493056</v>
+        <v>46097.55128159722</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>111</v>
@@ -2938,13 +2944,13 @@
         <v>113</v>
       </c>
       <c r="B29" s="9">
-        <v>46073.407750729166</v>
+        <v>46073.57441739584</v>
       </c>
       <c r="C29" s="9">
-        <v>46097.384648148145</v>
+        <v>46097.55131481482</v>
       </c>
       <c r="D29" s="9">
-        <v>46097.38464950232</v>
+        <v>46097.55131616898</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>114</v>
@@ -2999,13 +3005,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.40775103009</v>
+        <v>46073.57441769676</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.38468446759</v>
+        <v>46097.55135113426</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.38468596065</v>
+        <v>46097.55135262731</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>117</v>
@@ -3060,13 +3066,13 @@
         <v>119</v>
       </c>
       <c r="B31" s="9">
-        <v>46073.40775128472</v>
+        <v>46073.574417951386</v>
       </c>
       <c r="C31" s="9">
-        <v>46111.63208436343</v>
+        <v>46111.79875103009</v>
       </c>
       <c r="D31" s="9">
-        <v>46111.632097361115</v>
+        <v>46111.79876402778</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>120</v>
@@ -3125,13 +3131,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.40775155093</v>
+        <v>46073.57441821759</v>
       </c>
       <c r="C32" s="5">
-        <v>46097.38526033565</v>
+        <v>46097.551927002314</v>
       </c>
       <c r="D32" s="5">
-        <v>46097.38526181713</v>
+        <v>46097.551928483794</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3186,13 +3192,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="9">
-        <v>46073.40775180556</v>
+        <v>46073.57441847222</v>
       </c>
       <c r="C33" s="9">
-        <v>46111.63206998842</v>
+        <v>46111.798736655095</v>
       </c>
       <c r="D33" s="9">
-        <v>46111.63207150463</v>
+        <v>46111.798738171296</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>128</v>
@@ -3247,11 +3253,11 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.40775208334</v>
+        <v>46073.574418749995</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46108.6014222338</v>
+        <v>46108.76808890046</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3294,13 +3300,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="9">
-        <v>46073.407752349536</v>
+        <v>46073.57441901621</v>
       </c>
       <c r="C35" s="9">
-        <v>46108.60108274306</v>
+        <v>46108.76774940972</v>
       </c>
       <c r="D35" s="9">
-        <v>46108.6010999537</v>
+        <v>46197.70911202546</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>134</v>
@@ -3359,13 +3365,13 @@
         <v>138</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.40775028935</v>
+        <v>46073.57441695602</v>
       </c>
       <c r="C36" s="5">
-        <v>46108.60118219907</v>
+        <v>46108.76784886574</v>
       </c>
       <c r="D36" s="5">
-        <v>46108.60119883102</v>
+        <v>46197.70914525463</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>139</v>
@@ -3424,13 +3430,13 @@
         <v>142</v>
       </c>
       <c r="B37" s="9">
-        <v>46090.529563310185</v>
+        <v>46090.69622997685</v>
       </c>
       <c r="C37" s="9">
-        <v>46108.60141636574</v>
+        <v>46108.76808303241</v>
       </c>
       <c r="D37" s="9">
-        <v>46108.60143265047</v>
+        <v>46108.76809931713</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>143</v>
@@ -3439,10 +3445,10 @@
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="I37" s="9">
         <v>46066</v>
@@ -3466,7 +3472,7 @@
         <v>139</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Q37" s="9">
         <v>46066</v>
@@ -3486,26 +3492,26 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B38" s="5">
-        <v>46090.52978670139</v>
+        <v>46090.69645336806</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46197.33931072916</v>
+        <v>46197.505977395835</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I38" s="5">
         <v>46104</v>
@@ -3526,10 +3532,10 @@
         <v>131</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q38" s="5">
         <v>46104</v>
@@ -3544,24 +3550,24 @@
         <v>0</v>
       </c>
       <c r="U38" s="12" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B39" s="9">
-        <v>46073.4077505787</v>
+        <v>46073.57441724537</v>
       </c>
       <c r="C39" s="9">
-        <v>46111.63221431713</v>
+        <v>46111.7988809838</v>
       </c>
       <c r="D39" s="9">
-        <v>46111.63222694444</v>
+        <v>46111.79889361111</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>25</v>
@@ -3585,7 +3591,7 @@
         <v>26</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3602,28 +3608,28 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.40775079861</v>
+        <v>46073.57441746528</v>
       </c>
       <c r="C40" s="5">
-        <v>46111.63215450232</v>
+        <v>46111.79882116898</v>
       </c>
       <c r="D40" s="5">
-        <v>46111.63217065972</v>
+        <v>46111.798837326394</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I40" s="5">
         <v>46072</v>
@@ -3641,13 +3647,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>128</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q40" s="5">
         <v>46073</v>
@@ -3667,28 +3673,28 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B41" s="9">
-        <v>46073.40775103009</v>
+        <v>46073.57441769676</v>
       </c>
       <c r="C41" s="9">
-        <v>46111.632198287036</v>
+        <v>46111.7988649537</v>
       </c>
       <c r="D41" s="9">
-        <v>46111.632214178244</v>
+        <v>46111.79888084491</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I41" s="9">
         <v>46076</v>
@@ -3706,13 +3712,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="9">
         <v>46077</v>
@@ -3732,19 +3738,19 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.40775126158</v>
+        <v>46073.57441792824</v>
       </c>
       <c r="C42" s="5">
-        <v>46195.74522711805</v>
+        <v>46195.91189378472</v>
       </c>
       <c r="D42" s="5">
-        <v>46196.684344803245</v>
+        <v>46196.8510114699</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3768,7 +3774,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3781,28 +3787,28 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B43" s="9">
-        <v>46073.407751493054</v>
+        <v>46073.574418159726</v>
       </c>
       <c r="C43" s="9">
-        <v>46107.56083722222</v>
+        <v>46107.72750388889</v>
       </c>
       <c r="D43" s="9">
-        <v>46196.684302152775</v>
+        <v>46196.850968819446</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I43" s="9">
         <v>46078</v>
@@ -3820,13 +3826,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q43" s="9">
         <v>46080</v>
@@ -3846,28 +3852,28 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B44" s="5">
+        <v>46073.574418379634</v>
+      </c>
+      <c r="C44" s="5">
+        <v>46146.563449814814</v>
+      </c>
+      <c r="D44" s="5">
+        <v>46195.911566111114</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>172</v>
-      </c>
-      <c r="B44" s="5">
-        <v>46073.40775171296</v>
-      </c>
-      <c r="C44" s="5">
-        <v>46146.39678314815</v>
-      </c>
-      <c r="D44" s="5">
-        <v>46195.74489944444</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>170</v>
       </c>
       <c r="I44" s="5">
         <v>46083</v>
@@ -3885,13 +3891,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q44" s="5">
         <v>46087</v>
@@ -3911,28 +3917,28 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B45" s="9">
-        <v>46073.40775194444</v>
+        <v>46073.57441861111</v>
       </c>
       <c r="C45" s="9">
-        <v>46195.745206631946</v>
+        <v>46195.91187329861</v>
       </c>
       <c r="D45" s="9">
-        <v>46196.74385425926</v>
+        <v>46196.91052092593</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I45" s="9">
         <v>46090</v>
@@ -3950,13 +3956,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q45" s="9">
         <v>46090</v>
@@ -3976,19 +3982,19 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.4077521875</v>
+        <v>46073.57441885417</v>
       </c>
       <c r="C46" s="5">
-        <v>46195.44041152778</v>
+        <v>46195.60707819444</v>
       </c>
       <c r="D46" s="5">
-        <v>46195.440423078704</v>
+        <v>46195.607089745376</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4012,7 +4018,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4029,28 +4035,28 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B47" s="9">
-        <v>46073.40775005787</v>
+        <v>46073.574416724536</v>
       </c>
       <c r="C47" s="9">
-        <v>46127.48360153935</v>
+        <v>46127.65026820602</v>
       </c>
       <c r="D47" s="9">
-        <v>46127.48373905093</v>
+        <v>46127.65040571759</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I47" s="9">
         <v>46049</v>
@@ -4068,13 +4074,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>96</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q47" s="9">
         <v>46049</v>
@@ -4094,28 +4100,28 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B48" s="5">
-        <v>46073.40775244213</v>
+        <v>46073.5744191088</v>
       </c>
       <c r="C48" s="5">
-        <v>46195.44039379629</v>
+        <v>46195.607060462964</v>
       </c>
       <c r="D48" s="5">
-        <v>46195.44041170139</v>
+        <v>46195.607078368055</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I48" s="5">
         <v>46065</v>
@@ -4133,13 +4139,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>105</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q48" s="5">
         <v>46065</v>
@@ -4159,28 +4165,28 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B49" s="9">
-        <v>46073.40775033565</v>
+        <v>46073.57441700231</v>
       </c>
       <c r="C49" s="9">
-        <v>46122.48811438658</v>
+        <v>46122.654781053236</v>
       </c>
       <c r="D49" s="9">
-        <v>46122.488134652776</v>
+        <v>46122.65480131944</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I49" s="9">
         <v>46083</v>
@@ -4198,13 +4204,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O49" s="10" t="s">
         <v>114</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q49" s="9">
         <v>46083</v>
@@ -4224,17 +4230,17 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.40775060185</v>
+        <v>46073.57441726852</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46197.33929959491</v>
+        <v>46197.505966261575</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4258,7 +4264,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4271,19 +4277,19 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B51" s="9">
-        <v>46073.407751192135</v>
+        <v>46073.57441785879</v>
       </c>
       <c r="C51" s="9">
-        <v>46197.33879725695</v>
+        <v>46197.50546392361</v>
       </c>
       <c r="D51" s="9">
-        <v>46197.3388141551</v>
+        <v>46197.50548082176</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4310,13 +4316,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q51" s="9">
         <v>46097</v>
@@ -4336,19 +4342,19 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.4077514699</v>
+        <v>46073.57441813657</v>
       </c>
       <c r="C52" s="5">
-        <v>46197.338886412035</v>
+        <v>46197.50555307871</v>
       </c>
       <c r="D52" s="5">
-        <v>46197.338901423616</v>
+        <v>46197.50556809027</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4375,13 +4381,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q52" s="5">
         <v>46098</v>
@@ -4401,19 +4407,19 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B53" s="9">
-        <v>46073.40775171296</v>
+        <v>46073.574418379634</v>
       </c>
       <c r="C53" s="9">
-        <v>46197.33890447917</v>
+        <v>46197.50557114583</v>
       </c>
       <c r="D53" s="9">
-        <v>46197.338922106486</v>
+        <v>46197.50558877314</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
@@ -4440,13 +4446,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q53" s="9">
         <v>46099</v>
@@ -4466,19 +4472,19 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.40775196759</v>
+        <v>46073.57441863426</v>
       </c>
       <c r="C54" s="5">
-        <v>46197.339196574074</v>
+        <v>46197.505863240745</v>
       </c>
       <c r="D54" s="5">
-        <v>46197.33921306713</v>
+        <v>46197.5058797338</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -4505,13 +4511,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q54" s="5">
         <v>46100</v>
@@ -4531,19 +4537,19 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B55" s="9">
-        <v>46073.40775226852</v>
+        <v>46073.57441893518</v>
       </c>
       <c r="C55" s="9">
-        <v>46197.3392925</v>
+        <v>46197.505959166665</v>
       </c>
       <c r="D55" s="9">
-        <v>46197.339310138894</v>
+        <v>46197.50597680555</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
@@ -4568,13 +4574,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q55" s="9">
         <v>46101</v>
@@ -4594,17 +4600,17 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.407752534724</v>
+        <v>46073.57441920139</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46105.95859030093</v>
+        <v>46106.12525696759</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -4629,13 +4635,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q56" s="5">
         <v>46105</v>
@@ -4655,17 +4661,17 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B57" s="9">
-        <v>46073.40775020834</v>
+        <v>46073.574416874995</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46090.5351549537</v>
+        <v>46090.70182162037</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>25</v>
@@ -4689,7 +4695,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -4702,17 +4708,17 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.407750555554</v>
+        <v>46073.57441722222</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46133.731815046296</v>
+        <v>46133.89848171297</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -4731,19 +4737,19 @@
         <v>26</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q58" s="5">
         <v>46106</v>
@@ -4763,17 +4769,17 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B59" s="9">
-        <v>46073.407750810184</v>
+        <v>46073.57441747685</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46107.99797167824</v>
+        <v>46108.16463834491</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -4798,13 +4804,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q59" s="9">
         <v>46107</v>
@@ -4824,26 +4830,26 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.40775108796</v>
+        <v>46073.57441775463</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46108.08432915509</v>
+        <v>46108.250995821756</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I60" s="5">
         <v>46108</v>
@@ -4861,13 +4867,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q60" s="5">
         <v>46080</v>
@@ -4887,26 +4893,26 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B61" s="9">
-        <v>46073.40775134259</v>
+        <v>46073.57441800926</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46111.96357416667</v>
+        <v>46112.13024083333</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I61" s="9">
         <v>46111</v>
@@ -4924,13 +4930,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q61" s="9">
         <v>46111</v>
@@ -4950,17 +4956,17 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.4077516088</v>
+        <v>46073.574418275464</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46090.53515497685</v>
+        <v>46090.70182164352</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -4984,7 +4990,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -4997,26 +5003,26 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B63" s="9">
-        <v>46073.40775190972</v>
+        <v>46073.57441857639</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46121.00034344908</v>
+        <v>46121.167010115736</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="I63" s="9">
         <v>46112</v>
@@ -5034,13 +5040,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q63" s="9">
         <v>46120</v>
@@ -5060,26 +5066,26 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.407752175925</v>
+        <v>46073.57441884259</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46121.00034346065</v>
+        <v>46121.16701012732</v>
       </c>
       <c r="E64" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>237</v>
-      </c>
-      <c r="F64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G64" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>235</v>
       </c>
       <c r="I64" s="5">
         <v>46112</v>
@@ -5097,13 +5103,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q64" s="5">
         <v>46120</v>

--- a/data/50001508 - XEMORTIZ STOCK.xlsx
+++ b/data/50001508 - XEMORTIZ STOCK.xlsx
@@ -1401,13 +1401,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.574416574076</v>
+        <v>46073.407749907405</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.72097336805</v>
+        <v>46092.55430670139</v>
       </c>
       <c r="D4" s="5">
-        <v>46092.72098704861</v>
+        <v>46092.55432038194</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1454,13 +1454,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46073.57441700231</v>
+        <v>46073.40775033565</v>
       </c>
       <c r="C5" s="9">
-        <v>46092.72094241898</v>
+        <v>46092.554275752314</v>
       </c>
       <c r="D5" s="9">
-        <v>46092.72097376158</v>
+        <v>46092.554307094906</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1517,13 +1517,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.57441731481</v>
+        <v>46073.40775064815</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.72094300926</v>
+        <v>46092.55427634259</v>
       </c>
       <c r="D6" s="5">
-        <v>46133.88991541667</v>
+        <v>46133.72324875</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1580,13 +1580,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="9">
-        <v>46073.574417615746</v>
+        <v>46073.407750949074</v>
       </c>
       <c r="C7" s="9">
-        <v>46092.72094347222</v>
+        <v>46092.55427680556</v>
       </c>
       <c r="D7" s="9">
-        <v>46133.88996451389</v>
+        <v>46133.723297847224</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>39</v>
@@ -1643,13 +1643,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.574417951386</v>
+        <v>46073.40775128472</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.72094393519</v>
+        <v>46092.554277268515</v>
       </c>
       <c r="D8" s="5">
-        <v>46133.89120298611</v>
+        <v>46133.724536319445</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1706,13 +1706,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46073.57441825232</v>
+        <v>46073.40775158565</v>
       </c>
       <c r="C9" s="9">
-        <v>46092.72094480324</v>
+        <v>46092.55427813657</v>
       </c>
       <c r="D9" s="9">
-        <v>46133.891316608795</v>
+        <v>46133.72464994213</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -1769,13 +1769,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.57441959491</v>
+        <v>46073.40775292824</v>
       </c>
       <c r="C10" s="5">
-        <v>46114.51917579861</v>
+        <v>46114.352509131946</v>
       </c>
       <c r="D10" s="5">
-        <v>46139.53853695602</v>
+        <v>46139.37187028935</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -1818,13 +1818,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="9">
-        <v>46073.574417199074</v>
+        <v>46073.40775053241</v>
       </c>
       <c r="C11" s="9">
-        <v>46097.55113413194</v>
+        <v>46097.38446746528</v>
       </c>
       <c r="D11" s="9">
-        <v>46097.5511521875</v>
+        <v>46097.38448552083</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -1883,13 +1883,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.57441784722</v>
+        <v>46073.40775118055</v>
       </c>
       <c r="C12" s="5">
-        <v>46114.51896107639</v>
+        <v>46114.35229440972</v>
       </c>
       <c r="D12" s="5">
-        <v>46133.8973671412</v>
+        <v>46133.73070047454</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -1948,13 +1948,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="9">
-        <v>46073.57441811342</v>
+        <v>46073.407751446764</v>
       </c>
       <c r="C13" s="9">
-        <v>46097.55146753472</v>
+        <v>46097.38480086805</v>
       </c>
       <c r="D13" s="9">
-        <v>46097.551481574075</v>
+        <v>46097.384814907404</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>58</v>
@@ -2013,13 +2013,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.57441840278</v>
+        <v>46073.407751736115</v>
       </c>
       <c r="C14" s="5">
-        <v>46134.60713581018</v>
+        <v>46134.44046914352</v>
       </c>
       <c r="D14" s="5">
-        <v>46134.60713701389</v>
+        <v>46134.440470347225</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2078,13 +2078,13 @@
         <v>62</v>
       </c>
       <c r="B15" s="9">
-        <v>46073.574418668984</v>
+        <v>46073.40775200231</v>
       </c>
       <c r="C15" s="9">
-        <v>46114.52188712963</v>
+        <v>46114.35522046297</v>
       </c>
       <c r="D15" s="9">
-        <v>46114.521897847226</v>
+        <v>46114.355231180554</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>63</v>
@@ -2131,13 +2131,13 @@
         <v>65</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.574418958335</v>
+        <v>46073.40775229166</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.52184375</v>
+        <v>46114.35517708333</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.522016944444</v>
+        <v>46114.35535027778</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>66</v>
@@ -2196,13 +2196,13 @@
         <v>68</v>
       </c>
       <c r="B17" s="9">
-        <v>46073.574419791665</v>
+        <v>46073.407753125</v>
       </c>
       <c r="C17" s="9">
-        <v>46114.52187152777</v>
+        <v>46114.35520486112</v>
       </c>
       <c r="D17" s="9">
-        <v>46133.89260450231</v>
+        <v>46133.72593783565</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>69</v>
@@ -2261,13 +2261,13 @@
         <v>73</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.574419236116</v>
+        <v>46073.407752569445</v>
       </c>
       <c r="C18" s="5">
-        <v>46097.55117878472</v>
+        <v>46097.38451211806</v>
       </c>
       <c r="D18" s="5">
-        <v>46133.896346724534</v>
+        <v>46133.72968005787</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>74</v>
@@ -2326,13 +2326,13 @@
         <v>77</v>
       </c>
       <c r="B19" s="9">
-        <v>46073.5744165162</v>
+        <v>46073.40774984953</v>
       </c>
       <c r="C19" s="9">
-        <v>46097.55150556713</v>
+        <v>46097.38483890046</v>
       </c>
       <c r="D19" s="9">
-        <v>46100.785884259254</v>
+        <v>46100.6192175926</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>78</v>
@@ -2391,13 +2391,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.57441688658</v>
+        <v>46073.40775021991</v>
       </c>
       <c r="C20" s="5">
-        <v>46134.60708307871</v>
+        <v>46134.440416412035</v>
       </c>
       <c r="D20" s="5">
-        <v>46134.60710188658</v>
+        <v>46134.440435219905</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2444,13 +2444,13 @@
         <v>85</v>
       </c>
       <c r="B21" s="9">
-        <v>46073.57441755787</v>
+        <v>46073.4077508912</v>
       </c>
       <c r="C21" s="9">
-        <v>46114.781065034724</v>
+        <v>46114.61439836805</v>
       </c>
       <c r="D21" s="9">
-        <v>46133.89220711806</v>
+        <v>46133.725540451385</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>86</v>
@@ -2509,13 +2509,13 @@
         <v>90</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.57441785879</v>
+        <v>46073.407751192135</v>
       </c>
       <c r="C22" s="5">
-        <v>46114.78100798611</v>
+        <v>46114.614341319444</v>
       </c>
       <c r="D22" s="5">
-        <v>46114.78100939815</v>
+        <v>46114.61434273148</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -2570,13 +2570,13 @@
         <v>95</v>
       </c>
       <c r="B23" s="9">
-        <v>46073.57441814815</v>
+        <v>46073.407751481485</v>
       </c>
       <c r="C23" s="9">
-        <v>46114.78104996528</v>
+        <v>46114.61438329861</v>
       </c>
       <c r="D23" s="9">
-        <v>46114.78105144676</v>
+        <v>46114.61438478009</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>96</v>
@@ -2631,13 +2631,13 @@
         <v>98</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.57441936343</v>
+        <v>46073.40775269676</v>
       </c>
       <c r="C24" s="5">
-        <v>46133.89757971065</v>
+        <v>46133.73091304398</v>
       </c>
       <c r="D24" s="5">
-        <v>46133.8975922338</v>
+        <v>46133.73092556713</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>99</v>
@@ -2696,13 +2696,13 @@
         <v>101</v>
       </c>
       <c r="B25" s="9">
-        <v>46073.57441965278</v>
+        <v>46073.40775298611</v>
       </c>
       <c r="C25" s="9">
-        <v>46122.7044230787</v>
+        <v>46122.537756412035</v>
       </c>
       <c r="D25" s="9">
-        <v>46122.70442476852</v>
+        <v>46122.537758101855</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>102</v>
@@ -2757,13 +2757,13 @@
         <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.574416469906</v>
+        <v>46073.40774980324</v>
       </c>
       <c r="C26" s="5">
-        <v>46133.897566134256</v>
+        <v>46133.73089946759</v>
       </c>
       <c r="D26" s="5">
-        <v>46133.897567673615</v>
+        <v>46133.730901006944</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -2818,13 +2818,13 @@
         <v>107</v>
       </c>
       <c r="B27" s="9">
-        <v>46073.574416840274</v>
+        <v>46073.40775017361</v>
       </c>
       <c r="C27" s="9">
-        <v>46097.55136633102</v>
+        <v>46097.384699664355</v>
       </c>
       <c r="D27" s="9">
-        <v>46097.55137980324</v>
+        <v>46097.38471313658</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>108</v>
@@ -2883,13 +2883,13 @@
         <v>110</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.574417129625</v>
+        <v>46073.40775046297</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.551280127314</v>
+        <v>46097.38461346064</v>
       </c>
       <c r="D28" s="5">
-        <v>46097.55128159722</v>
+        <v>46097.38461493056</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>111</v>
@@ -2944,13 +2944,13 @@
         <v>113</v>
       </c>
       <c r="B29" s="9">
-        <v>46073.57441739584</v>
+        <v>46073.407750729166</v>
       </c>
       <c r="C29" s="9">
-        <v>46097.55131481482</v>
+        <v>46097.384648148145</v>
       </c>
       <c r="D29" s="9">
-        <v>46097.55131616898</v>
+        <v>46097.38464950232</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>114</v>
@@ -3005,13 +3005,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.57441769676</v>
+        <v>46073.40775103009</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.55135113426</v>
+        <v>46097.38468446759</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.55135262731</v>
+        <v>46097.38468596065</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>117</v>
@@ -3066,13 +3066,13 @@
         <v>119</v>
       </c>
       <c r="B31" s="9">
-        <v>46073.574417951386</v>
+        <v>46073.40775128472</v>
       </c>
       <c r="C31" s="9">
-        <v>46111.79875103009</v>
+        <v>46111.63208436343</v>
       </c>
       <c r="D31" s="9">
-        <v>46111.79876402778</v>
+        <v>46111.632097361115</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>120</v>
@@ -3131,13 +3131,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.57441821759</v>
+        <v>46073.40775155093</v>
       </c>
       <c r="C32" s="5">
-        <v>46097.551927002314</v>
+        <v>46097.38526033565</v>
       </c>
       <c r="D32" s="5">
-        <v>46097.551928483794</v>
+        <v>46097.38526181713</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3192,13 +3192,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="9">
-        <v>46073.57441847222</v>
+        <v>46073.40775180556</v>
       </c>
       <c r="C33" s="9">
-        <v>46111.798736655095</v>
+        <v>46111.63206998842</v>
       </c>
       <c r="D33" s="9">
-        <v>46111.798738171296</v>
+        <v>46111.63207150463</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>128</v>
@@ -3253,11 +3253,11 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.574418749995</v>
+        <v>46073.40775208334</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46108.76808890046</v>
+        <v>46108.6014222338</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3300,13 +3300,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="9">
-        <v>46073.57441901621</v>
+        <v>46073.407752349536</v>
       </c>
       <c r="C35" s="9">
-        <v>46108.76774940972</v>
+        <v>46108.60108274306</v>
       </c>
       <c r="D35" s="9">
-        <v>46197.70911202546</v>
+        <v>46197.54244535879</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>134</v>
@@ -3365,13 +3365,13 @@
         <v>138</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.57441695602</v>
+        <v>46073.40775028935</v>
       </c>
       <c r="C36" s="5">
-        <v>46108.76784886574</v>
+        <v>46108.60118219907</v>
       </c>
       <c r="D36" s="5">
-        <v>46197.70914525463</v>
+        <v>46197.54247858796</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>139</v>
@@ -3430,13 +3430,13 @@
         <v>142</v>
       </c>
       <c r="B37" s="9">
-        <v>46090.69622997685</v>
+        <v>46090.529563310185</v>
       </c>
       <c r="C37" s="9">
-        <v>46108.76808303241</v>
+        <v>46108.60141636574</v>
       </c>
       <c r="D37" s="9">
-        <v>46108.76809931713</v>
+        <v>46108.60143265047</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>143</v>
@@ -3495,11 +3495,11 @@
         <v>147</v>
       </c>
       <c r="B38" s="5">
-        <v>46090.69645336806</v>
+        <v>46090.52978670139</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46197.505977395835</v>
+        <v>46197.33931072916</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>148</v>
@@ -3558,13 +3558,13 @@
         <v>154</v>
       </c>
       <c r="B39" s="9">
-        <v>46073.57441724537</v>
+        <v>46073.4077505787</v>
       </c>
       <c r="C39" s="9">
-        <v>46111.7988809838</v>
+        <v>46111.63221431713</v>
       </c>
       <c r="D39" s="9">
-        <v>46111.79889361111</v>
+        <v>46111.63222694444</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>155</v>
@@ -3611,13 +3611,13 @@
         <v>157</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.57441746528</v>
+        <v>46073.40775079861</v>
       </c>
       <c r="C40" s="5">
-        <v>46111.79882116898</v>
+        <v>46111.63215450232</v>
       </c>
       <c r="D40" s="5">
-        <v>46111.798837326394</v>
+        <v>46111.63217065972</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>158</v>
@@ -3676,13 +3676,13 @@
         <v>162</v>
       </c>
       <c r="B41" s="9">
-        <v>46073.57441769676</v>
+        <v>46073.40775103009</v>
       </c>
       <c r="C41" s="9">
-        <v>46111.7988649537</v>
+        <v>46111.632198287036</v>
       </c>
       <c r="D41" s="9">
-        <v>46111.79888084491</v>
+        <v>46111.632214178244</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>163</v>
@@ -3741,13 +3741,13 @@
         <v>166</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.57441792824</v>
+        <v>46073.40775126158</v>
       </c>
       <c r="C42" s="5">
-        <v>46195.91189378472</v>
+        <v>46195.74522711805</v>
       </c>
       <c r="D42" s="5">
-        <v>46196.8510114699</v>
+        <v>46196.684344803245</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>167</v>
@@ -3790,13 +3790,13 @@
         <v>169</v>
       </c>
       <c r="B43" s="9">
-        <v>46073.574418159726</v>
+        <v>46073.407751493054</v>
       </c>
       <c r="C43" s="9">
-        <v>46107.72750388889</v>
+        <v>46107.56083722222</v>
       </c>
       <c r="D43" s="9">
-        <v>46196.850968819446</v>
+        <v>46196.684302152775</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>170</v>
@@ -3855,13 +3855,13 @@
         <v>174</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.574418379634</v>
+        <v>46073.40775171296</v>
       </c>
       <c r="C44" s="5">
-        <v>46146.563449814814</v>
+        <v>46146.39678314815</v>
       </c>
       <c r="D44" s="5">
-        <v>46195.911566111114</v>
+        <v>46195.74489944444</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>175</v>
@@ -3920,13 +3920,13 @@
         <v>178</v>
       </c>
       <c r="B45" s="9">
-        <v>46073.57441861111</v>
+        <v>46073.40775194444</v>
       </c>
       <c r="C45" s="9">
-        <v>46195.91187329861</v>
+        <v>46195.745206631946</v>
       </c>
       <c r="D45" s="9">
-        <v>46196.91052092593</v>
+        <v>46196.74385425926</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>179</v>
@@ -3985,13 +3985,13 @@
         <v>182</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.57441885417</v>
+        <v>46073.4077521875</v>
       </c>
       <c r="C46" s="5">
-        <v>46195.60707819444</v>
+        <v>46195.44041152778</v>
       </c>
       <c r="D46" s="5">
-        <v>46195.607089745376</v>
+        <v>46195.440423078704</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>155</v>
@@ -4038,13 +4038,13 @@
         <v>184</v>
       </c>
       <c r="B47" s="9">
-        <v>46073.574416724536</v>
+        <v>46073.40775005787</v>
       </c>
       <c r="C47" s="9">
-        <v>46127.65026820602</v>
+        <v>46127.48360153935</v>
       </c>
       <c r="D47" s="9">
-        <v>46127.65040571759</v>
+        <v>46127.48373905093</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>185</v>
@@ -4103,13 +4103,13 @@
         <v>187</v>
       </c>
       <c r="B48" s="5">
-        <v>46073.5744191088</v>
+        <v>46073.40775244213</v>
       </c>
       <c r="C48" s="5">
-        <v>46195.607060462964</v>
+        <v>46195.44039379629</v>
       </c>
       <c r="D48" s="5">
-        <v>46195.607078368055</v>
+        <v>46195.44041170139</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>188</v>
@@ -4168,13 +4168,13 @@
         <v>190</v>
       </c>
       <c r="B49" s="9">
-        <v>46073.57441700231</v>
+        <v>46073.40775033565</v>
       </c>
       <c r="C49" s="9">
-        <v>46122.654781053236</v>
+        <v>46122.48811438658</v>
       </c>
       <c r="D49" s="9">
-        <v>46122.65480131944</v>
+        <v>46122.488134652776</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>191</v>
@@ -4233,11 +4233,11 @@
         <v>193</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.57441726852</v>
+        <v>46073.40775060185</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46197.505966261575</v>
+        <v>46197.33929959491</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>194</v>
@@ -4280,13 +4280,13 @@
         <v>196</v>
       </c>
       <c r="B51" s="9">
-        <v>46073.57441785879</v>
+        <v>46073.407751192135</v>
       </c>
       <c r="C51" s="9">
-        <v>46197.50546392361</v>
+        <v>46197.33879725695</v>
       </c>
       <c r="D51" s="9">
-        <v>46197.50548082176</v>
+        <v>46197.3388141551</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>197</v>
@@ -4345,13 +4345,13 @@
         <v>199</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.57441813657</v>
+        <v>46073.4077514699</v>
       </c>
       <c r="C52" s="5">
-        <v>46197.50555307871</v>
+        <v>46197.338886412035</v>
       </c>
       <c r="D52" s="5">
-        <v>46197.50556809027</v>
+        <v>46197.338901423616</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>200</v>
@@ -4410,13 +4410,13 @@
         <v>203</v>
       </c>
       <c r="B53" s="9">
-        <v>46073.574418379634</v>
+        <v>46073.40775171296</v>
       </c>
       <c r="C53" s="9">
-        <v>46197.50557114583</v>
+        <v>46197.33890447917</v>
       </c>
       <c r="D53" s="9">
-        <v>46197.50558877314</v>
+        <v>46197.338922106486</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>204</v>
@@ -4475,13 +4475,13 @@
         <v>206</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.57441863426</v>
+        <v>46073.40775196759</v>
       </c>
       <c r="C54" s="5">
-        <v>46197.505863240745</v>
+        <v>46197.339196574074</v>
       </c>
       <c r="D54" s="5">
-        <v>46197.5058797338</v>
+        <v>46197.33921306713</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>207</v>
@@ -4540,13 +4540,13 @@
         <v>209</v>
       </c>
       <c r="B55" s="9">
-        <v>46073.57441893518</v>
+        <v>46073.40775226852</v>
       </c>
       <c r="C55" s="9">
-        <v>46197.505959166665</v>
+        <v>46197.3392925</v>
       </c>
       <c r="D55" s="9">
-        <v>46197.50597680555</v>
+        <v>46197.339310138894</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>151</v>
@@ -4603,11 +4603,11 @@
         <v>212</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.57441920139</v>
+        <v>46073.407752534724</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46106.12525696759</v>
+        <v>46105.95859030093</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>213</v>
@@ -4664,11 +4664,11 @@
         <v>215</v>
       </c>
       <c r="B57" s="9">
-        <v>46073.574416874995</v>
+        <v>46073.40775020834</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46090.70182162037</v>
+        <v>46090.5351549537</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>216</v>
@@ -4711,11 +4711,11 @@
         <v>218</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.57441722222</v>
+        <v>46073.407750555554</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46133.89848171297</v>
+        <v>46133.731815046296</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>219</v>
@@ -4772,11 +4772,11 @@
         <v>222</v>
       </c>
       <c r="B59" s="9">
-        <v>46073.57441747685</v>
+        <v>46073.407750810184</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46108.16463834491</v>
+        <v>46107.99797167824</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>223</v>
@@ -4833,11 +4833,11 @@
         <v>225</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.57441775463</v>
+        <v>46073.40775108796</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46108.250995821756</v>
+        <v>46108.08432915509</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>226</v>
@@ -4896,11 +4896,11 @@
         <v>228</v>
       </c>
       <c r="B61" s="9">
-        <v>46073.57441800926</v>
+        <v>46073.40775134259</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46112.13024083333</v>
+        <v>46111.96357416667</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>229</v>
@@ -4959,11 +4959,11 @@
         <v>231</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.574418275464</v>
+        <v>46073.4077516088</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46090.70182164352</v>
+        <v>46090.53515497685</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>232</v>
@@ -5006,11 +5006,11 @@
         <v>234</v>
       </c>
       <c r="B63" s="9">
-        <v>46073.57441857639</v>
+        <v>46073.40775190972</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46121.167010115736</v>
+        <v>46121.00034344908</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>235</v>
@@ -5069,11 +5069,11 @@
         <v>238</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.57441884259</v>
+        <v>46073.407752175925</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46121.16701012732</v>
+        <v>46121.00034346065</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>239</v>

--- a/data/50001508 - XEMORTIZ STOCK.xlsx
+++ b/data/50001508 - XEMORTIZ STOCK.xlsx
@@ -1401,13 +1401,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.407749907405</v>
+        <v>46073.574416574076</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55430670139</v>
+        <v>46092.72097336805</v>
       </c>
       <c r="D4" s="5">
-        <v>46092.55432038194</v>
+        <v>46092.72098704861</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1454,13 +1454,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46073.40775033565</v>
+        <v>46073.57441700231</v>
       </c>
       <c r="C5" s="9">
-        <v>46092.554275752314</v>
+        <v>46092.72094241898</v>
       </c>
       <c r="D5" s="9">
-        <v>46092.554307094906</v>
+        <v>46092.72097376158</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1517,13 +1517,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.40775064815</v>
+        <v>46073.57441731481</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55427634259</v>
+        <v>46092.72094300926</v>
       </c>
       <c r="D6" s="5">
-        <v>46133.72324875</v>
+        <v>46133.88991541667</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1580,13 +1580,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="9">
-        <v>46073.407750949074</v>
+        <v>46073.574417615746</v>
       </c>
       <c r="C7" s="9">
-        <v>46092.55427680556</v>
+        <v>46092.72094347222</v>
       </c>
       <c r="D7" s="9">
-        <v>46133.723297847224</v>
+        <v>46133.88996451389</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>39</v>
@@ -1643,13 +1643,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.40775128472</v>
+        <v>46073.574417951386</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.554277268515</v>
+        <v>46092.72094393519</v>
       </c>
       <c r="D8" s="5">
-        <v>46133.724536319445</v>
+        <v>46133.89120298611</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1706,13 +1706,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46073.40775158565</v>
+        <v>46073.57441825232</v>
       </c>
       <c r="C9" s="9">
-        <v>46092.55427813657</v>
+        <v>46092.72094480324</v>
       </c>
       <c r="D9" s="9">
-        <v>46133.72464994213</v>
+        <v>46133.891316608795</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -1769,13 +1769,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.40775292824</v>
+        <v>46073.57441959491</v>
       </c>
       <c r="C10" s="5">
-        <v>46114.352509131946</v>
+        <v>46114.51917579861</v>
       </c>
       <c r="D10" s="5">
-        <v>46139.37187028935</v>
+        <v>46139.53853695602</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -1818,13 +1818,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="9">
-        <v>46073.40775053241</v>
+        <v>46073.574417199074</v>
       </c>
       <c r="C11" s="9">
-        <v>46097.38446746528</v>
+        <v>46097.55113413194</v>
       </c>
       <c r="D11" s="9">
-        <v>46097.38448552083</v>
+        <v>46097.5511521875</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -1883,13 +1883,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.40775118055</v>
+        <v>46073.57441784722</v>
       </c>
       <c r="C12" s="5">
-        <v>46114.35229440972</v>
+        <v>46114.51896107639</v>
       </c>
       <c r="D12" s="5">
-        <v>46133.73070047454</v>
+        <v>46133.8973671412</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -1948,13 +1948,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="9">
-        <v>46073.407751446764</v>
+        <v>46073.57441811342</v>
       </c>
       <c r="C13" s="9">
-        <v>46097.38480086805</v>
+        <v>46097.55146753472</v>
       </c>
       <c r="D13" s="9">
-        <v>46097.384814907404</v>
+        <v>46097.551481574075</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>58</v>
@@ -2013,13 +2013,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.407751736115</v>
+        <v>46073.57441840278</v>
       </c>
       <c r="C14" s="5">
-        <v>46134.44046914352</v>
+        <v>46134.60713581018</v>
       </c>
       <c r="D14" s="5">
-        <v>46134.440470347225</v>
+        <v>46134.60713701389</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2078,13 +2078,13 @@
         <v>62</v>
       </c>
       <c r="B15" s="9">
-        <v>46073.40775200231</v>
+        <v>46073.574418668984</v>
       </c>
       <c r="C15" s="9">
-        <v>46114.35522046297</v>
+        <v>46114.52188712963</v>
       </c>
       <c r="D15" s="9">
-        <v>46114.355231180554</v>
+        <v>46114.521897847226</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>63</v>
@@ -2131,13 +2131,13 @@
         <v>65</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.40775229166</v>
+        <v>46073.574418958335</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.35517708333</v>
+        <v>46114.52184375</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.35535027778</v>
+        <v>46114.522016944444</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>66</v>
@@ -2196,13 +2196,13 @@
         <v>68</v>
       </c>
       <c r="B17" s="9">
-        <v>46073.407753125</v>
+        <v>46073.574419791665</v>
       </c>
       <c r="C17" s="9">
-        <v>46114.35520486112</v>
+        <v>46114.52187152777</v>
       </c>
       <c r="D17" s="9">
-        <v>46133.72593783565</v>
+        <v>46133.89260450231</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>69</v>
@@ -2261,13 +2261,13 @@
         <v>73</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.407752569445</v>
+        <v>46073.574419236116</v>
       </c>
       <c r="C18" s="5">
-        <v>46097.38451211806</v>
+        <v>46097.55117878472</v>
       </c>
       <c r="D18" s="5">
-        <v>46133.72968005787</v>
+        <v>46133.896346724534</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>74</v>
@@ -2326,13 +2326,13 @@
         <v>77</v>
       </c>
       <c r="B19" s="9">
-        <v>46073.40774984953</v>
+        <v>46073.5744165162</v>
       </c>
       <c r="C19" s="9">
-        <v>46097.38483890046</v>
+        <v>46097.55150556713</v>
       </c>
       <c r="D19" s="9">
-        <v>46100.6192175926</v>
+        <v>46100.785884259254</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>78</v>
@@ -2391,13 +2391,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.40775021991</v>
+        <v>46073.57441688658</v>
       </c>
       <c r="C20" s="5">
-        <v>46134.440416412035</v>
+        <v>46134.60708307871</v>
       </c>
       <c r="D20" s="5">
-        <v>46134.440435219905</v>
+        <v>46134.60710188658</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2444,13 +2444,13 @@
         <v>85</v>
       </c>
       <c r="B21" s="9">
-        <v>46073.4077508912</v>
+        <v>46073.57441755787</v>
       </c>
       <c r="C21" s="9">
-        <v>46114.61439836805</v>
+        <v>46114.781065034724</v>
       </c>
       <c r="D21" s="9">
-        <v>46133.725540451385</v>
+        <v>46133.89220711806</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>86</v>
@@ -2509,13 +2509,13 @@
         <v>90</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.407751192135</v>
+        <v>46073.57441785879</v>
       </c>
       <c r="C22" s="5">
-        <v>46114.614341319444</v>
+        <v>46114.78100798611</v>
       </c>
       <c r="D22" s="5">
-        <v>46114.61434273148</v>
+        <v>46114.78100939815</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -2570,13 +2570,13 @@
         <v>95</v>
       </c>
       <c r="B23" s="9">
-        <v>46073.407751481485</v>
+        <v>46073.57441814815</v>
       </c>
       <c r="C23" s="9">
-        <v>46114.61438329861</v>
+        <v>46114.78104996528</v>
       </c>
       <c r="D23" s="9">
-        <v>46114.61438478009</v>
+        <v>46114.78105144676</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>96</v>
@@ -2631,13 +2631,13 @@
         <v>98</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.40775269676</v>
+        <v>46073.57441936343</v>
       </c>
       <c r="C24" s="5">
-        <v>46133.73091304398</v>
+        <v>46133.89757971065</v>
       </c>
       <c r="D24" s="5">
-        <v>46133.73092556713</v>
+        <v>46133.8975922338</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>99</v>
@@ -2696,13 +2696,13 @@
         <v>101</v>
       </c>
       <c r="B25" s="9">
-        <v>46073.40775298611</v>
+        <v>46073.57441965278</v>
       </c>
       <c r="C25" s="9">
-        <v>46122.537756412035</v>
+        <v>46122.7044230787</v>
       </c>
       <c r="D25" s="9">
-        <v>46122.537758101855</v>
+        <v>46122.70442476852</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>102</v>
@@ -2757,13 +2757,13 @@
         <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.40774980324</v>
+        <v>46073.574416469906</v>
       </c>
       <c r="C26" s="5">
-        <v>46133.73089946759</v>
+        <v>46133.897566134256</v>
       </c>
       <c r="D26" s="5">
-        <v>46133.730901006944</v>
+        <v>46133.897567673615</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -2818,13 +2818,13 @@
         <v>107</v>
       </c>
       <c r="B27" s="9">
-        <v>46073.40775017361</v>
+        <v>46073.574416840274</v>
       </c>
       <c r="C27" s="9">
-        <v>46097.384699664355</v>
+        <v>46097.55136633102</v>
       </c>
       <c r="D27" s="9">
-        <v>46097.38471313658</v>
+        <v>46097.55137980324</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>108</v>
@@ -2883,13 +2883,13 @@
         <v>110</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.40775046297</v>
+        <v>46073.574417129625</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.38461346064</v>
+        <v>46097.551280127314</v>
       </c>
       <c r="D28" s="5">
-        <v>46097.38461493056</v>
+        <v>46097.55128159722</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>111</v>
@@ -2944,13 +2944,13 @@
         <v>113</v>
       </c>
       <c r="B29" s="9">
-        <v>46073.407750729166</v>
+        <v>46073.57441739584</v>
       </c>
       <c r="C29" s="9">
-        <v>46097.384648148145</v>
+        <v>46097.55131481482</v>
       </c>
       <c r="D29" s="9">
-        <v>46097.38464950232</v>
+        <v>46097.55131616898</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>114</v>
@@ -3005,13 +3005,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.40775103009</v>
+        <v>46073.57441769676</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.38468446759</v>
+        <v>46097.55135113426</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.38468596065</v>
+        <v>46097.55135262731</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>117</v>
@@ -3066,13 +3066,13 @@
         <v>119</v>
       </c>
       <c r="B31" s="9">
-        <v>46073.40775128472</v>
+        <v>46073.574417951386</v>
       </c>
       <c r="C31" s="9">
-        <v>46111.63208436343</v>
+        <v>46111.79875103009</v>
       </c>
       <c r="D31" s="9">
-        <v>46111.632097361115</v>
+        <v>46111.79876402778</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>120</v>
@@ -3131,13 +3131,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.40775155093</v>
+        <v>46073.57441821759</v>
       </c>
       <c r="C32" s="5">
-        <v>46097.38526033565</v>
+        <v>46097.551927002314</v>
       </c>
       <c r="D32" s="5">
-        <v>46097.38526181713</v>
+        <v>46097.551928483794</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3192,13 +3192,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="9">
-        <v>46073.40775180556</v>
+        <v>46073.57441847222</v>
       </c>
       <c r="C33" s="9">
-        <v>46111.63206998842</v>
+        <v>46111.798736655095</v>
       </c>
       <c r="D33" s="9">
-        <v>46111.63207150463</v>
+        <v>46111.798738171296</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>128</v>
@@ -3253,11 +3253,11 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.40775208334</v>
+        <v>46073.574418749995</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46108.6014222338</v>
+        <v>46108.76808890046</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3300,13 +3300,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="9">
-        <v>46073.407752349536</v>
+        <v>46073.57441901621</v>
       </c>
       <c r="C35" s="9">
-        <v>46108.60108274306</v>
+        <v>46108.76774940972</v>
       </c>
       <c r="D35" s="9">
-        <v>46197.54244535879</v>
+        <v>46197.70911202546</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>134</v>
@@ -3365,13 +3365,13 @@
         <v>138</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.40775028935</v>
+        <v>46073.57441695602</v>
       </c>
       <c r="C36" s="5">
-        <v>46108.60118219907</v>
+        <v>46108.76784886574</v>
       </c>
       <c r="D36" s="5">
-        <v>46197.54247858796</v>
+        <v>46197.70914525463</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>139</v>
@@ -3430,13 +3430,13 @@
         <v>142</v>
       </c>
       <c r="B37" s="9">
-        <v>46090.529563310185</v>
+        <v>46090.69622997685</v>
       </c>
       <c r="C37" s="9">
-        <v>46108.60141636574</v>
+        <v>46108.76808303241</v>
       </c>
       <c r="D37" s="9">
-        <v>46108.60143265047</v>
+        <v>46108.76809931713</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>143</v>
@@ -3495,11 +3495,11 @@
         <v>147</v>
       </c>
       <c r="B38" s="5">
-        <v>46090.52978670139</v>
+        <v>46090.69645336806</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46197.33931072916</v>
+        <v>46197.505977395835</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>148</v>
@@ -3558,13 +3558,13 @@
         <v>154</v>
       </c>
       <c r="B39" s="9">
-        <v>46073.4077505787</v>
+        <v>46073.57441724537</v>
       </c>
       <c r="C39" s="9">
-        <v>46111.63221431713</v>
+        <v>46111.7988809838</v>
       </c>
       <c r="D39" s="9">
-        <v>46111.63222694444</v>
+        <v>46111.79889361111</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>155</v>
@@ -3611,13 +3611,13 @@
         <v>157</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.40775079861</v>
+        <v>46073.57441746528</v>
       </c>
       <c r="C40" s="5">
-        <v>46111.63215450232</v>
+        <v>46111.79882116898</v>
       </c>
       <c r="D40" s="5">
-        <v>46111.63217065972</v>
+        <v>46111.798837326394</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>158</v>
@@ -3676,13 +3676,13 @@
         <v>162</v>
       </c>
       <c r="B41" s="9">
-        <v>46073.40775103009</v>
+        <v>46073.57441769676</v>
       </c>
       <c r="C41" s="9">
-        <v>46111.632198287036</v>
+        <v>46111.7988649537</v>
       </c>
       <c r="D41" s="9">
-        <v>46111.632214178244</v>
+        <v>46111.79888084491</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>163</v>
@@ -3741,13 +3741,13 @@
         <v>166</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.40775126158</v>
+        <v>46073.57441792824</v>
       </c>
       <c r="C42" s="5">
-        <v>46195.74522711805</v>
+        <v>46195.91189378472</v>
       </c>
       <c r="D42" s="5">
-        <v>46196.684344803245</v>
+        <v>46196.8510114699</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>167</v>
@@ -3790,13 +3790,13 @@
         <v>169</v>
       </c>
       <c r="B43" s="9">
-        <v>46073.407751493054</v>
+        <v>46073.574418159726</v>
       </c>
       <c r="C43" s="9">
-        <v>46107.56083722222</v>
+        <v>46107.72750388889</v>
       </c>
       <c r="D43" s="9">
-        <v>46196.684302152775</v>
+        <v>46196.850968819446</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>170</v>
@@ -3855,13 +3855,13 @@
         <v>174</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.40775171296</v>
+        <v>46073.574418379634</v>
       </c>
       <c r="C44" s="5">
-        <v>46146.39678314815</v>
+        <v>46146.563449814814</v>
       </c>
       <c r="D44" s="5">
-        <v>46195.74489944444</v>
+        <v>46195.911566111114</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>175</v>
@@ -3920,13 +3920,13 @@
         <v>178</v>
       </c>
       <c r="B45" s="9">
-        <v>46073.40775194444</v>
+        <v>46073.57441861111</v>
       </c>
       <c r="C45" s="9">
-        <v>46195.745206631946</v>
+        <v>46195.91187329861</v>
       </c>
       <c r="D45" s="9">
-        <v>46196.74385425926</v>
+        <v>46196.91052092593</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>179</v>
@@ -3985,13 +3985,13 @@
         <v>182</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.4077521875</v>
+        <v>46073.57441885417</v>
       </c>
       <c r="C46" s="5">
-        <v>46195.44041152778</v>
+        <v>46195.60707819444</v>
       </c>
       <c r="D46" s="5">
-        <v>46195.440423078704</v>
+        <v>46195.607089745376</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>155</v>
@@ -4038,13 +4038,13 @@
         <v>184</v>
       </c>
       <c r="B47" s="9">
-        <v>46073.40775005787</v>
+        <v>46073.574416724536</v>
       </c>
       <c r="C47" s="9">
-        <v>46127.48360153935</v>
+        <v>46127.65026820602</v>
       </c>
       <c r="D47" s="9">
-        <v>46127.48373905093</v>
+        <v>46127.65040571759</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>185</v>
@@ -4103,13 +4103,13 @@
         <v>187</v>
       </c>
       <c r="B48" s="5">
-        <v>46073.40775244213</v>
+        <v>46073.5744191088</v>
       </c>
       <c r="C48" s="5">
-        <v>46195.44039379629</v>
+        <v>46195.607060462964</v>
       </c>
       <c r="D48" s="5">
-        <v>46195.44041170139</v>
+        <v>46195.607078368055</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>188</v>
@@ -4168,13 +4168,13 @@
         <v>190</v>
       </c>
       <c r="B49" s="9">
-        <v>46073.40775033565</v>
+        <v>46073.57441700231</v>
       </c>
       <c r="C49" s="9">
-        <v>46122.48811438658</v>
+        <v>46122.654781053236</v>
       </c>
       <c r="D49" s="9">
-        <v>46122.488134652776</v>
+        <v>46122.65480131944</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>191</v>
@@ -4233,11 +4233,11 @@
         <v>193</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.40775060185</v>
+        <v>46073.57441726852</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46197.33929959491</v>
+        <v>46197.505966261575</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>194</v>
@@ -4280,13 +4280,13 @@
         <v>196</v>
       </c>
       <c r="B51" s="9">
-        <v>46073.407751192135</v>
+        <v>46073.57441785879</v>
       </c>
       <c r="C51" s="9">
-        <v>46197.33879725695</v>
+        <v>46197.50546392361</v>
       </c>
       <c r="D51" s="9">
-        <v>46197.3388141551</v>
+        <v>46197.50548082176</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>197</v>
@@ -4345,13 +4345,13 @@
         <v>199</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.4077514699</v>
+        <v>46073.57441813657</v>
       </c>
       <c r="C52" s="5">
-        <v>46197.338886412035</v>
+        <v>46197.50555307871</v>
       </c>
       <c r="D52" s="5">
-        <v>46197.338901423616</v>
+        <v>46197.50556809027</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>200</v>
@@ -4410,13 +4410,13 @@
         <v>203</v>
       </c>
       <c r="B53" s="9">
-        <v>46073.40775171296</v>
+        <v>46073.574418379634</v>
       </c>
       <c r="C53" s="9">
-        <v>46197.33890447917</v>
+        <v>46197.50557114583</v>
       </c>
       <c r="D53" s="9">
-        <v>46197.338922106486</v>
+        <v>46197.50558877314</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>204</v>
@@ -4475,13 +4475,13 @@
         <v>206</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.40775196759</v>
+        <v>46073.57441863426</v>
       </c>
       <c r="C54" s="5">
-        <v>46197.339196574074</v>
+        <v>46197.505863240745</v>
       </c>
       <c r="D54" s="5">
-        <v>46197.33921306713</v>
+        <v>46197.5058797338</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>207</v>
@@ -4540,13 +4540,13 @@
         <v>209</v>
       </c>
       <c r="B55" s="9">
-        <v>46073.40775226852</v>
+        <v>46073.57441893518</v>
       </c>
       <c r="C55" s="9">
-        <v>46197.3392925</v>
+        <v>46197.505959166665</v>
       </c>
       <c r="D55" s="9">
-        <v>46197.339310138894</v>
+        <v>46197.50597680555</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>151</v>
@@ -4603,11 +4603,11 @@
         <v>212</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.407752534724</v>
+        <v>46073.57441920139</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46105.95859030093</v>
+        <v>46106.12525696759</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>213</v>
@@ -4664,11 +4664,11 @@
         <v>215</v>
       </c>
       <c r="B57" s="9">
-        <v>46073.40775020834</v>
+        <v>46073.574416874995</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46090.5351549537</v>
+        <v>46090.70182162037</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>216</v>
@@ -4711,11 +4711,11 @@
         <v>218</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.407750555554</v>
+        <v>46073.57441722222</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46133.731815046296</v>
+        <v>46133.89848171297</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>219</v>
@@ -4772,11 +4772,11 @@
         <v>222</v>
       </c>
       <c r="B59" s="9">
-        <v>46073.407750810184</v>
+        <v>46073.57441747685</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46107.99797167824</v>
+        <v>46108.16463834491</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>223</v>
@@ -4833,11 +4833,11 @@
         <v>225</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.40775108796</v>
+        <v>46073.57441775463</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46108.08432915509</v>
+        <v>46108.250995821756</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>226</v>
@@ -4896,11 +4896,11 @@
         <v>228</v>
       </c>
       <c r="B61" s="9">
-        <v>46073.40775134259</v>
+        <v>46073.57441800926</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46111.96357416667</v>
+        <v>46112.13024083333</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>229</v>
@@ -4959,11 +4959,11 @@
         <v>231</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.4077516088</v>
+        <v>46073.574418275464</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46090.53515497685</v>
+        <v>46090.70182164352</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>232</v>
@@ -5006,11 +5006,11 @@
         <v>234</v>
       </c>
       <c r="B63" s="9">
-        <v>46073.40775190972</v>
+        <v>46073.57441857639</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46121.00034344908</v>
+        <v>46121.167010115736</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>235</v>
@@ -5069,11 +5069,11 @@
         <v>238</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.407752175925</v>
+        <v>46073.57441884259</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46121.00034346065</v>
+        <v>46121.16701012732</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>239</v>

--- a/data/50001508 - XEMORTIZ STOCK.xlsx
+++ b/data/50001508 - XEMORTIZ STOCK.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="240">
   <si>
     <t>50001508 - XEMORTIZ STOCK</t>
   </si>
@@ -516,190 +516,190 @@
     <t>Ingenieria y diseñoo:,RE-PINTADO</t>
   </si>
   <si>
+    <t>1213377491559684</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1213377491559685</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento,Bodega:,Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1213377491559686</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1213377491559687</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1213377491559688</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>Armado,Caldereria:</t>
+  </si>
+  <si>
+    <t>1213377491559689</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Check Planos</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,Caldereria:</t>
+  </si>
+  <si>
+    <t>1213377491559690</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>Armado,Check Planos</t>
+  </si>
+  <si>
+    <t>Caldereria:,Revestimiento</t>
+  </si>
+  <si>
+    <t>1213377491559691</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete,Recepcion Alabe,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1213333053701053</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1213377491559692</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1213333053701054</t>
+  </si>
+  <si>
+    <t>Recepcion motor</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje motor</t>
+  </si>
+  <si>
+    <t>1213333053701055</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Revestimiento,Montaje motor,Montaje Alabe,Montaje Rodete,Pruebas FAT,RE-PINTADO</t>
+  </si>
+  <si>
+    <t>1213333053701056</t>
+  </si>
+  <si>
+    <t>Revestimiento</t>
+  </si>
+  <si>
+    <t>Montaje motor,Montaje Alabe,Montaje Rodete,Montaje:</t>
+  </si>
+  <si>
+    <t>1213333053701057</t>
+  </si>
+  <si>
+    <t>Montaje motor</t>
+  </si>
+  <si>
+    <t>Revestimiento,Recepcion motor,Check Planos</t>
+  </si>
+  <si>
+    <t>Pruebas FAT,Montaje:</t>
+  </si>
+  <si>
+    <t>1213333053701058</t>
+  </si>
+  <si>
+    <t>Montaje Alabe</t>
+  </si>
+  <si>
+    <t>Revestimiento,Recepcion Alabe,Check Planos</t>
+  </si>
+  <si>
+    <t>1213333053701059</t>
+  </si>
+  <si>
+    <t>Montaje Rodete</t>
+  </si>
+  <si>
+    <t>Revestimiento,Recepcion Rodete,Check Planos</t>
+  </si>
+  <si>
+    <t>1213333053701060</t>
+  </si>
+  <si>
+    <t>Montaje Alabe,Montaje motor,Montaje Rodete</t>
+  </si>
+  <si>
+    <t>Montaje:,Check pruebas FAT</t>
+  </si>
+  <si>
+    <t>1213333053701061</t>
+  </si>
+  <si>
+    <t>RE-PINTADO</t>
+  </si>
+  <si>
+    <t>Montaje:,Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1213377491559684</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1213377491559685</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento,Bodega:,Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1213377491559686</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1213377491559687</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1213377491559688</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>Armado,Caldereria:</t>
-  </si>
-  <si>
-    <t>1213377491559689</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Check Planos</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,Caldereria:</t>
-  </si>
-  <si>
-    <t>1213377491559690</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>Armado,Check Planos</t>
-  </si>
-  <si>
-    <t>Caldereria:,Revestimiento</t>
-  </si>
-  <si>
-    <t>1213377491559691</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete,Recepcion Alabe,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1213333053701053</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1213377491559692</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1213333053701054</t>
-  </si>
-  <si>
-    <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje motor</t>
-  </si>
-  <si>
-    <t>1213333053701055</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Revestimiento,Montaje motor,Montaje Alabe,Montaje Rodete,Pruebas FAT,RE-PINTADO</t>
-  </si>
-  <si>
-    <t>1213333053701056</t>
-  </si>
-  <si>
-    <t>Revestimiento</t>
-  </si>
-  <si>
-    <t>Montaje motor,Montaje Alabe,Montaje Rodete,Montaje:</t>
-  </si>
-  <si>
-    <t>1213333053701057</t>
-  </si>
-  <si>
-    <t>Montaje motor</t>
-  </si>
-  <si>
-    <t>Revestimiento,Recepcion motor,Check Planos</t>
-  </si>
-  <si>
-    <t>Pruebas FAT,Montaje:</t>
-  </si>
-  <si>
-    <t>1213333053701058</t>
-  </si>
-  <si>
-    <t>Montaje Alabe</t>
-  </si>
-  <si>
-    <t>Revestimiento,Recepcion Alabe,Check Planos</t>
-  </si>
-  <si>
-    <t>1213333053701059</t>
-  </si>
-  <si>
-    <t>Montaje Rodete</t>
-  </si>
-  <si>
-    <t>Revestimiento,Recepcion Rodete,Check Planos</t>
-  </si>
-  <si>
-    <t>1213333053701060</t>
-  </si>
-  <si>
-    <t>Montaje Alabe,Montaje motor,Montaje Rodete</t>
-  </si>
-  <si>
-    <t>Montaje:,Check pruebas FAT</t>
-  </si>
-  <si>
-    <t>1213333053701061</t>
-  </si>
-  <si>
-    <t>RE-PINTADO</t>
-  </si>
-  <si>
-    <t>Montaje:,Coordinacion Entrega con Cliente</t>
   </si>
   <si>
     <t>1213333053701062</t>
@@ -3255,9 +3255,11 @@
       <c r="B34" s="5">
         <v>46073.574418749995</v>
       </c>
-      <c r="C34" s="6"/>
+      <c r="C34" s="5">
+        <v>46198.565049375</v>
+      </c>
       <c r="D34" s="5">
-        <v>46108.76808890046</v>
+        <v>46198.565061875</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3292,8 +3294,12 @@
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="6"/>
-      <c r="T34" s="6"/>
-      <c r="U34" s="6"/>
+      <c r="T34" s="6">
+        <v>1</v>
+      </c>
+      <c r="U34" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
@@ -3497,9 +3503,11 @@
       <c r="B38" s="5">
         <v>46090.69645336806</v>
       </c>
-      <c r="C38" s="6"/>
+      <c r="C38" s="5">
+        <v>46198.565030763886</v>
+      </c>
       <c r="D38" s="5">
-        <v>46197.505977395835</v>
+        <v>46198.565049791665</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>148</v>
@@ -3547,15 +3555,15 @@
         <v>32</v>
       </c>
       <c r="T38" s="6">
-        <v>0</v>
-      </c>
-      <c r="U38" s="12" t="s">
-        <v>153</v>
+        <v>1</v>
+      </c>
+      <c r="U38" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B39" s="9">
         <v>46073.57441724537</v>
@@ -3567,7 +3575,7 @@
         <v>46111.79889361111</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>25</v>
@@ -3591,7 +3599,7 @@
         <v>26</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3608,7 +3616,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B40" s="5">
         <v>46073.57441746528</v>
@@ -3620,16 +3628,16 @@
         <v>46111.798837326394</v>
       </c>
       <c r="E40" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="6" t="s">
+      <c r="H40" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I40" s="5">
         <v>46072</v>
@@ -3647,13 +3655,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>128</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q40" s="5">
         <v>46073</v>
@@ -3673,7 +3681,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B41" s="9">
         <v>46073.57441769676</v>
@@ -3685,16 +3693,16 @@
         <v>46111.79888084491</v>
       </c>
       <c r="E41" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="F41" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="10" t="s">
+      <c r="H41" s="10" t="s">
         <v>164</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>165</v>
       </c>
       <c r="I41" s="9">
         <v>46076</v>
@@ -3712,13 +3720,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q41" s="9">
         <v>46077</v>
@@ -3738,7 +3746,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B42" s="5">
         <v>46073.57441792824</v>
@@ -3750,7 +3758,7 @@
         <v>46196.8510114699</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3774,7 +3782,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3787,7 +3795,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B43" s="9">
         <v>46073.574418159726</v>
@@ -3799,16 +3807,16 @@
         <v>46196.850968819446</v>
       </c>
       <c r="E43" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="10" t="s">
+      <c r="H43" s="10" t="s">
         <v>171</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>172</v>
       </c>
       <c r="I43" s="9">
         <v>46078</v>
@@ -3826,13 +3834,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q43" s="9">
         <v>46080</v>
@@ -3852,7 +3860,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B44" s="5">
         <v>46073.574418379634</v>
@@ -3864,16 +3872,16 @@
         <v>46195.911566111114</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>171</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>172</v>
       </c>
       <c r="I44" s="5">
         <v>46083</v>
@@ -3891,13 +3899,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O44" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="P44" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="P44" s="6" t="s">
-        <v>177</v>
       </c>
       <c r="Q44" s="5">
         <v>46087</v>
@@ -3917,7 +3925,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B45" s="9">
         <v>46073.57441861111</v>
@@ -3929,16 +3937,16 @@
         <v>46196.91052092593</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>164</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>165</v>
       </c>
       <c r="I45" s="9">
         <v>46090</v>
@@ -3956,13 +3964,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O45" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="P45" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="P45" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="Q45" s="9">
         <v>46090</v>
@@ -3982,7 +3990,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B46" s="5">
         <v>46073.57441885417</v>
@@ -3994,7 +4002,7 @@
         <v>46195.607089745376</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4018,7 +4026,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4035,7 +4043,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B47" s="9">
         <v>46073.574416724536</v>
@@ -4047,16 +4055,16 @@
         <v>46127.65040571759</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H47" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I47" s="9">
         <v>46049</v>
@@ -4074,13 +4082,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>96</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q47" s="9">
         <v>46049</v>
@@ -4100,7 +4108,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B48" s="5">
         <v>46073.5744191088</v>
@@ -4112,16 +4120,16 @@
         <v>46195.607078368055</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I48" s="5">
         <v>46065</v>
@@ -4139,13 +4147,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>105</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q48" s="5">
         <v>46065</v>
@@ -4165,7 +4173,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B49" s="9">
         <v>46073.57441700231</v>
@@ -4177,16 +4185,16 @@
         <v>46122.65480131944</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I49" s="9">
         <v>46083</v>
@@ -4204,13 +4212,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O49" s="10" t="s">
         <v>114</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q49" s="9">
         <v>46083</v>
@@ -4230,7 +4238,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B50" s="5">
         <v>46073.57441726852</v>
@@ -4240,7 +4248,7 @@
         <v>46197.505966261575</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4264,7 +4272,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4277,7 +4285,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B51" s="9">
         <v>46073.57441785879</v>
@@ -4289,7 +4297,7 @@
         <v>46197.50548082176</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4316,13 +4324,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q51" s="9">
         <v>46097</v>
@@ -4342,7 +4350,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B52" s="5">
         <v>46073.57441813657</v>
@@ -4354,7 +4362,7 @@
         <v>46197.50556809027</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4381,13 +4389,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O52" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="P52" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="P52" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="Q52" s="5">
         <v>46098</v>
@@ -4407,7 +4415,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B53" s="9">
         <v>46073.574418379634</v>
@@ -4419,7 +4427,7 @@
         <v>46197.50558877314</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
@@ -4446,13 +4454,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q53" s="9">
         <v>46099</v>
@@ -4472,7 +4480,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B54" s="5">
         <v>46073.57441863426</v>
@@ -4484,7 +4492,7 @@
         <v>46197.5058797338</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -4511,13 +4519,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q54" s="5">
         <v>46100</v>
@@ -4537,7 +4545,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B55" s="9">
         <v>46073.57441893518</v>
@@ -4574,13 +4582,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O55" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="P55" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="P55" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="Q55" s="9">
         <v>46101</v>
@@ -4600,17 +4608,17 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B56" s="5">
         <v>46073.57441920139</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46106.12525696759</v>
+        <v>46198.565050185185</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -4635,13 +4643,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>148</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q56" s="5">
         <v>46105</v>
@@ -4655,8 +4663,8 @@
       <c r="T56" s="6">
         <v>0</v>
       </c>
-      <c r="U56" s="11" t="s">
-        <v>94</v>
+      <c r="U56" s="12" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -4746,7 +4754,7 @@
         <v>216</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>221</v>
@@ -4846,10 +4854,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>171</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>172</v>
       </c>
       <c r="I60" s="5">
         <v>46108</v>
@@ -4909,10 +4917,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>171</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>172</v>
       </c>
       <c r="I61" s="9">
         <v>46111</v>

--- a/data/50001508 - XEMORTIZ STOCK.xlsx
+++ b/data/50001508 - XEMORTIZ STOCK.xlsx
@@ -1401,13 +1401,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.574416574076</v>
+        <v>46073.407749907405</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.72097336805</v>
+        <v>46092.55430670139</v>
       </c>
       <c r="D4" s="5">
-        <v>46092.72098704861</v>
+        <v>46092.55432038194</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1454,13 +1454,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46073.57441700231</v>
+        <v>46073.40775033565</v>
       </c>
       <c r="C5" s="9">
-        <v>46092.72094241898</v>
+        <v>46092.554275752314</v>
       </c>
       <c r="D5" s="9">
-        <v>46092.72097376158</v>
+        <v>46092.554307094906</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1517,13 +1517,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.57441731481</v>
+        <v>46073.40775064815</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.72094300926</v>
+        <v>46092.55427634259</v>
       </c>
       <c r="D6" s="5">
-        <v>46133.88991541667</v>
+        <v>46133.72324875</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1580,13 +1580,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="9">
-        <v>46073.574417615746</v>
+        <v>46073.407750949074</v>
       </c>
       <c r="C7" s="9">
-        <v>46092.72094347222</v>
+        <v>46092.55427680556</v>
       </c>
       <c r="D7" s="9">
-        <v>46133.88996451389</v>
+        <v>46133.723297847224</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>39</v>
@@ -1643,13 +1643,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.574417951386</v>
+        <v>46073.40775128472</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.72094393519</v>
+        <v>46092.554277268515</v>
       </c>
       <c r="D8" s="5">
-        <v>46133.89120298611</v>
+        <v>46133.724536319445</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1706,13 +1706,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46073.57441825232</v>
+        <v>46073.40775158565</v>
       </c>
       <c r="C9" s="9">
-        <v>46092.72094480324</v>
+        <v>46092.55427813657</v>
       </c>
       <c r="D9" s="9">
-        <v>46133.891316608795</v>
+        <v>46133.72464994213</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -1769,13 +1769,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.57441959491</v>
+        <v>46073.40775292824</v>
       </c>
       <c r="C10" s="5">
-        <v>46114.51917579861</v>
+        <v>46114.352509131946</v>
       </c>
       <c r="D10" s="5">
-        <v>46139.53853695602</v>
+        <v>46139.37187028935</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -1818,13 +1818,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="9">
-        <v>46073.574417199074</v>
+        <v>46073.40775053241</v>
       </c>
       <c r="C11" s="9">
-        <v>46097.55113413194</v>
+        <v>46097.38446746528</v>
       </c>
       <c r="D11" s="9">
-        <v>46097.5511521875</v>
+        <v>46097.38448552083</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -1883,13 +1883,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.57441784722</v>
+        <v>46073.40775118055</v>
       </c>
       <c r="C12" s="5">
-        <v>46114.51896107639</v>
+        <v>46114.35229440972</v>
       </c>
       <c r="D12" s="5">
-        <v>46133.8973671412</v>
+        <v>46133.73070047454</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -1948,13 +1948,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="9">
-        <v>46073.57441811342</v>
+        <v>46073.407751446764</v>
       </c>
       <c r="C13" s="9">
-        <v>46097.55146753472</v>
+        <v>46097.38480086805</v>
       </c>
       <c r="D13" s="9">
-        <v>46097.551481574075</v>
+        <v>46097.384814907404</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>58</v>
@@ -2013,13 +2013,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.57441840278</v>
+        <v>46073.407751736115</v>
       </c>
       <c r="C14" s="5">
-        <v>46134.60713581018</v>
+        <v>46134.44046914352</v>
       </c>
       <c r="D14" s="5">
-        <v>46134.60713701389</v>
+        <v>46134.440470347225</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2078,13 +2078,13 @@
         <v>62</v>
       </c>
       <c r="B15" s="9">
-        <v>46073.574418668984</v>
+        <v>46073.40775200231</v>
       </c>
       <c r="C15" s="9">
-        <v>46114.52188712963</v>
+        <v>46114.35522046297</v>
       </c>
       <c r="D15" s="9">
-        <v>46114.521897847226</v>
+        <v>46114.355231180554</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>63</v>
@@ -2131,13 +2131,13 @@
         <v>65</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.574418958335</v>
+        <v>46073.40775229166</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.52184375</v>
+        <v>46114.35517708333</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.522016944444</v>
+        <v>46114.35535027778</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>66</v>
@@ -2196,13 +2196,13 @@
         <v>68</v>
       </c>
       <c r="B17" s="9">
-        <v>46073.574419791665</v>
+        <v>46073.407753125</v>
       </c>
       <c r="C17" s="9">
-        <v>46114.52187152777</v>
+        <v>46114.35520486112</v>
       </c>
       <c r="D17" s="9">
-        <v>46133.89260450231</v>
+        <v>46133.72593783565</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>69</v>
@@ -2261,13 +2261,13 @@
         <v>73</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.574419236116</v>
+        <v>46073.407752569445</v>
       </c>
       <c r="C18" s="5">
-        <v>46097.55117878472</v>
+        <v>46097.38451211806</v>
       </c>
       <c r="D18" s="5">
-        <v>46133.896346724534</v>
+        <v>46133.72968005787</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>74</v>
@@ -2326,13 +2326,13 @@
         <v>77</v>
       </c>
       <c r="B19" s="9">
-        <v>46073.5744165162</v>
+        <v>46073.40774984953</v>
       </c>
       <c r="C19" s="9">
-        <v>46097.55150556713</v>
+        <v>46097.38483890046</v>
       </c>
       <c r="D19" s="9">
-        <v>46100.785884259254</v>
+        <v>46100.6192175926</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>78</v>
@@ -2391,13 +2391,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.57441688658</v>
+        <v>46073.40775021991</v>
       </c>
       <c r="C20" s="5">
-        <v>46134.60708307871</v>
+        <v>46134.440416412035</v>
       </c>
       <c r="D20" s="5">
-        <v>46134.60710188658</v>
+        <v>46134.440435219905</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2444,13 +2444,13 @@
         <v>85</v>
       </c>
       <c r="B21" s="9">
-        <v>46073.57441755787</v>
+        <v>46073.4077508912</v>
       </c>
       <c r="C21" s="9">
-        <v>46114.781065034724</v>
+        <v>46114.61439836805</v>
       </c>
       <c r="D21" s="9">
-        <v>46133.89220711806</v>
+        <v>46133.725540451385</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>86</v>
@@ -2509,13 +2509,13 @@
         <v>90</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.57441785879</v>
+        <v>46073.407751192135</v>
       </c>
       <c r="C22" s="5">
-        <v>46114.78100798611</v>
+        <v>46114.614341319444</v>
       </c>
       <c r="D22" s="5">
-        <v>46114.78100939815</v>
+        <v>46114.61434273148</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -2570,13 +2570,13 @@
         <v>95</v>
       </c>
       <c r="B23" s="9">
-        <v>46073.57441814815</v>
+        <v>46073.407751481485</v>
       </c>
       <c r="C23" s="9">
-        <v>46114.78104996528</v>
+        <v>46114.61438329861</v>
       </c>
       <c r="D23" s="9">
-        <v>46114.78105144676</v>
+        <v>46114.61438478009</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>96</v>
@@ -2631,13 +2631,13 @@
         <v>98</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.57441936343</v>
+        <v>46073.40775269676</v>
       </c>
       <c r="C24" s="5">
-        <v>46133.89757971065</v>
+        <v>46133.73091304398</v>
       </c>
       <c r="D24" s="5">
-        <v>46133.8975922338</v>
+        <v>46133.73092556713</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>99</v>
@@ -2696,13 +2696,13 @@
         <v>101</v>
       </c>
       <c r="B25" s="9">
-        <v>46073.57441965278</v>
+        <v>46073.40775298611</v>
       </c>
       <c r="C25" s="9">
-        <v>46122.7044230787</v>
+        <v>46122.537756412035</v>
       </c>
       <c r="D25" s="9">
-        <v>46122.70442476852</v>
+        <v>46122.537758101855</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>102</v>
@@ -2757,13 +2757,13 @@
         <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.574416469906</v>
+        <v>46073.40774980324</v>
       </c>
       <c r="C26" s="5">
-        <v>46133.897566134256</v>
+        <v>46133.73089946759</v>
       </c>
       <c r="D26" s="5">
-        <v>46133.897567673615</v>
+        <v>46133.730901006944</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -2818,13 +2818,13 @@
         <v>107</v>
       </c>
       <c r="B27" s="9">
-        <v>46073.574416840274</v>
+        <v>46073.40775017361</v>
       </c>
       <c r="C27" s="9">
-        <v>46097.55136633102</v>
+        <v>46097.384699664355</v>
       </c>
       <c r="D27" s="9">
-        <v>46097.55137980324</v>
+        <v>46097.38471313658</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>108</v>
@@ -2883,13 +2883,13 @@
         <v>110</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.574417129625</v>
+        <v>46073.40775046297</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.551280127314</v>
+        <v>46097.38461346064</v>
       </c>
       <c r="D28" s="5">
-        <v>46097.55128159722</v>
+        <v>46097.38461493056</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>111</v>
@@ -2944,13 +2944,13 @@
         <v>113</v>
       </c>
       <c r="B29" s="9">
-        <v>46073.57441739584</v>
+        <v>46073.407750729166</v>
       </c>
       <c r="C29" s="9">
-        <v>46097.55131481482</v>
+        <v>46097.384648148145</v>
       </c>
       <c r="D29" s="9">
-        <v>46097.55131616898</v>
+        <v>46097.38464950232</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>114</v>
@@ -3005,13 +3005,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.57441769676</v>
+        <v>46073.40775103009</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.55135113426</v>
+        <v>46097.38468446759</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.55135262731</v>
+        <v>46097.38468596065</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>117</v>
@@ -3066,13 +3066,13 @@
         <v>119</v>
       </c>
       <c r="B31" s="9">
-        <v>46073.574417951386</v>
+        <v>46073.40775128472</v>
       </c>
       <c r="C31" s="9">
-        <v>46111.79875103009</v>
+        <v>46111.63208436343</v>
       </c>
       <c r="D31" s="9">
-        <v>46111.79876402778</v>
+        <v>46111.632097361115</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>120</v>
@@ -3131,13 +3131,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.57441821759</v>
+        <v>46073.40775155093</v>
       </c>
       <c r="C32" s="5">
-        <v>46097.551927002314</v>
+        <v>46097.38526033565</v>
       </c>
       <c r="D32" s="5">
-        <v>46097.551928483794</v>
+        <v>46097.38526181713</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3192,13 +3192,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="9">
-        <v>46073.57441847222</v>
+        <v>46073.40775180556</v>
       </c>
       <c r="C33" s="9">
-        <v>46111.798736655095</v>
+        <v>46111.63206998842</v>
       </c>
       <c r="D33" s="9">
-        <v>46111.798738171296</v>
+        <v>46111.63207150463</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>128</v>
@@ -3253,13 +3253,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.574418749995</v>
+        <v>46073.40775208334</v>
       </c>
       <c r="C34" s="5">
-        <v>46198.565049375</v>
+        <v>46198.39838270833</v>
       </c>
       <c r="D34" s="5">
-        <v>46198.565061875</v>
+        <v>46198.398395208336</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3306,13 +3306,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="9">
-        <v>46073.57441901621</v>
+        <v>46073.407752349536</v>
       </c>
       <c r="C35" s="9">
-        <v>46108.76774940972</v>
+        <v>46108.60108274306</v>
       </c>
       <c r="D35" s="9">
-        <v>46197.70911202546</v>
+        <v>46197.54244535879</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>134</v>
@@ -3371,13 +3371,13 @@
         <v>138</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.57441695602</v>
+        <v>46073.40775028935</v>
       </c>
       <c r="C36" s="5">
-        <v>46108.76784886574</v>
+        <v>46108.60118219907</v>
       </c>
       <c r="D36" s="5">
-        <v>46197.70914525463</v>
+        <v>46197.54247858796</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>139</v>
@@ -3436,13 +3436,13 @@
         <v>142</v>
       </c>
       <c r="B37" s="9">
-        <v>46090.69622997685</v>
+        <v>46090.529563310185</v>
       </c>
       <c r="C37" s="9">
-        <v>46108.76808303241</v>
+        <v>46108.60141636574</v>
       </c>
       <c r="D37" s="9">
-        <v>46108.76809931713</v>
+        <v>46108.60143265047</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>143</v>
@@ -3501,13 +3501,13 @@
         <v>147</v>
       </c>
       <c r="B38" s="5">
-        <v>46090.69645336806</v>
+        <v>46090.52978670139</v>
       </c>
       <c r="C38" s="5">
-        <v>46198.565030763886</v>
+        <v>46198.39836409722</v>
       </c>
       <c r="D38" s="5">
-        <v>46198.565049791665</v>
+        <v>46198.398383125</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>148</v>
@@ -3566,13 +3566,13 @@
         <v>153</v>
       </c>
       <c r="B39" s="9">
-        <v>46073.57441724537</v>
+        <v>46073.4077505787</v>
       </c>
       <c r="C39" s="9">
-        <v>46111.7988809838</v>
+        <v>46111.63221431713</v>
       </c>
       <c r="D39" s="9">
-        <v>46111.79889361111</v>
+        <v>46111.63222694444</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>154</v>
@@ -3619,13 +3619,13 @@
         <v>156</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.57441746528</v>
+        <v>46073.40775079861</v>
       </c>
       <c r="C40" s="5">
-        <v>46111.79882116898</v>
+        <v>46111.63215450232</v>
       </c>
       <c r="D40" s="5">
-        <v>46111.798837326394</v>
+        <v>46111.63217065972</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>157</v>
@@ -3684,13 +3684,13 @@
         <v>161</v>
       </c>
       <c r="B41" s="9">
-        <v>46073.57441769676</v>
+        <v>46073.40775103009</v>
       </c>
       <c r="C41" s="9">
-        <v>46111.7988649537</v>
+        <v>46111.632198287036</v>
       </c>
       <c r="D41" s="9">
-        <v>46111.79888084491</v>
+        <v>46111.632214178244</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>162</v>
@@ -3749,13 +3749,13 @@
         <v>165</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.57441792824</v>
+        <v>46073.40775126158</v>
       </c>
       <c r="C42" s="5">
-        <v>46195.91189378472</v>
+        <v>46195.74522711805</v>
       </c>
       <c r="D42" s="5">
-        <v>46196.8510114699</v>
+        <v>46196.684344803245</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>166</v>
@@ -3798,13 +3798,13 @@
         <v>168</v>
       </c>
       <c r="B43" s="9">
-        <v>46073.574418159726</v>
+        <v>46073.407751493054</v>
       </c>
       <c r="C43" s="9">
-        <v>46107.72750388889</v>
+        <v>46107.56083722222</v>
       </c>
       <c r="D43" s="9">
-        <v>46196.850968819446</v>
+        <v>46196.684302152775</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>169</v>
@@ -3863,13 +3863,13 @@
         <v>173</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.574418379634</v>
+        <v>46073.40775171296</v>
       </c>
       <c r="C44" s="5">
-        <v>46146.563449814814</v>
+        <v>46146.39678314815</v>
       </c>
       <c r="D44" s="5">
-        <v>46195.911566111114</v>
+        <v>46195.74489944444</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>174</v>
@@ -3928,13 +3928,13 @@
         <v>177</v>
       </c>
       <c r="B45" s="9">
-        <v>46073.57441861111</v>
+        <v>46073.40775194444</v>
       </c>
       <c r="C45" s="9">
-        <v>46195.91187329861</v>
+        <v>46195.745206631946</v>
       </c>
       <c r="D45" s="9">
-        <v>46196.91052092593</v>
+        <v>46196.74385425926</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>178</v>
@@ -3993,13 +3993,13 @@
         <v>181</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.57441885417</v>
+        <v>46073.4077521875</v>
       </c>
       <c r="C46" s="5">
-        <v>46195.60707819444</v>
+        <v>46195.44041152778</v>
       </c>
       <c r="D46" s="5">
-        <v>46195.607089745376</v>
+        <v>46195.440423078704</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>154</v>
@@ -4046,13 +4046,13 @@
         <v>183</v>
       </c>
       <c r="B47" s="9">
-        <v>46073.574416724536</v>
+        <v>46073.40775005787</v>
       </c>
       <c r="C47" s="9">
-        <v>46127.65026820602</v>
+        <v>46127.48360153935</v>
       </c>
       <c r="D47" s="9">
-        <v>46127.65040571759</v>
+        <v>46127.48373905093</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>184</v>
@@ -4111,13 +4111,13 @@
         <v>186</v>
       </c>
       <c r="B48" s="5">
-        <v>46073.5744191088</v>
+        <v>46073.40775244213</v>
       </c>
       <c r="C48" s="5">
-        <v>46195.607060462964</v>
+        <v>46195.44039379629</v>
       </c>
       <c r="D48" s="5">
-        <v>46195.607078368055</v>
+        <v>46195.44041170139</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>187</v>
@@ -4176,13 +4176,13 @@
         <v>189</v>
       </c>
       <c r="B49" s="9">
-        <v>46073.57441700231</v>
+        <v>46073.40775033565</v>
       </c>
       <c r="C49" s="9">
-        <v>46122.654781053236</v>
+        <v>46122.48811438658</v>
       </c>
       <c r="D49" s="9">
-        <v>46122.65480131944</v>
+        <v>46122.488134652776</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>190</v>
@@ -4241,11 +4241,11 @@
         <v>192</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.57441726852</v>
+        <v>46073.40775060185</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46197.505966261575</v>
+        <v>46197.33929959491</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>193</v>
@@ -4288,13 +4288,13 @@
         <v>195</v>
       </c>
       <c r="B51" s="9">
-        <v>46073.57441785879</v>
+        <v>46073.407751192135</v>
       </c>
       <c r="C51" s="9">
-        <v>46197.50546392361</v>
+        <v>46197.33879725695</v>
       </c>
       <c r="D51" s="9">
-        <v>46197.50548082176</v>
+        <v>46197.3388141551</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>196</v>
@@ -4353,13 +4353,13 @@
         <v>198</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.57441813657</v>
+        <v>46073.4077514699</v>
       </c>
       <c r="C52" s="5">
-        <v>46197.50555307871</v>
+        <v>46197.338886412035</v>
       </c>
       <c r="D52" s="5">
-        <v>46197.50556809027</v>
+        <v>46197.338901423616</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>199</v>
@@ -4418,13 +4418,13 @@
         <v>202</v>
       </c>
       <c r="B53" s="9">
-        <v>46073.574418379634</v>
+        <v>46073.40775171296</v>
       </c>
       <c r="C53" s="9">
-        <v>46197.50557114583</v>
+        <v>46197.33890447917</v>
       </c>
       <c r="D53" s="9">
-        <v>46197.50558877314</v>
+        <v>46197.338922106486</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>203</v>
@@ -4483,13 +4483,13 @@
         <v>205</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.57441863426</v>
+        <v>46073.40775196759</v>
       </c>
       <c r="C54" s="5">
-        <v>46197.505863240745</v>
+        <v>46197.339196574074</v>
       </c>
       <c r="D54" s="5">
-        <v>46197.5058797338</v>
+        <v>46197.33921306713</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>206</v>
@@ -4548,13 +4548,13 @@
         <v>208</v>
       </c>
       <c r="B55" s="9">
-        <v>46073.57441893518</v>
+        <v>46073.40775226852</v>
       </c>
       <c r="C55" s="9">
-        <v>46197.505959166665</v>
+        <v>46197.3392925</v>
       </c>
       <c r="D55" s="9">
-        <v>46197.50597680555</v>
+        <v>46197.339310138894</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>151</v>
@@ -4611,11 +4611,11 @@
         <v>211</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.57441920139</v>
+        <v>46073.407752534724</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46198.565050185185</v>
+        <v>46198.39838351852</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>212</v>
@@ -4672,11 +4672,11 @@
         <v>215</v>
       </c>
       <c r="B57" s="9">
-        <v>46073.574416874995</v>
+        <v>46073.40775020834</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46090.70182162037</v>
+        <v>46090.5351549537</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>216</v>
@@ -4719,11 +4719,11 @@
         <v>218</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.57441722222</v>
+        <v>46073.407750555554</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46133.89848171297</v>
+        <v>46133.731815046296</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>219</v>
@@ -4780,11 +4780,11 @@
         <v>222</v>
       </c>
       <c r="B59" s="9">
-        <v>46073.57441747685</v>
+        <v>46073.407750810184</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46108.16463834491</v>
+        <v>46107.99797167824</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>223</v>
@@ -4841,11 +4841,11 @@
         <v>225</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.57441775463</v>
+        <v>46073.40775108796</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46108.250995821756</v>
+        <v>46108.08432915509</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>226</v>
@@ -4904,11 +4904,11 @@
         <v>228</v>
       </c>
       <c r="B61" s="9">
-        <v>46073.57441800926</v>
+        <v>46073.40775134259</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46112.13024083333</v>
+        <v>46111.96357416667</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>229</v>
@@ -4967,11 +4967,11 @@
         <v>231</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.574418275464</v>
+        <v>46073.4077516088</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46090.70182164352</v>
+        <v>46090.53515497685</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>232</v>
@@ -5014,11 +5014,11 @@
         <v>234</v>
       </c>
       <c r="B63" s="9">
-        <v>46073.57441857639</v>
+        <v>46073.40775190972</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46121.167010115736</v>
+        <v>46121.00034344908</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>235</v>
@@ -5077,11 +5077,11 @@
         <v>238</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.57441884259</v>
+        <v>46073.407752175925</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46121.16701012732</v>
+        <v>46121.00034346065</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>239</v>

--- a/data/50001508 - XEMORTIZ STOCK.xlsx
+++ b/data/50001508 - XEMORTIZ STOCK.xlsx
@@ -1401,13 +1401,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.407749907405</v>
+        <v>46073.574416574076</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55430670139</v>
+        <v>46092.72097336805</v>
       </c>
       <c r="D4" s="5">
-        <v>46092.55432038194</v>
+        <v>46092.72098704861</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1454,13 +1454,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46073.40775033565</v>
+        <v>46073.57441700231</v>
       </c>
       <c r="C5" s="9">
-        <v>46092.554275752314</v>
+        <v>46092.72094241898</v>
       </c>
       <c r="D5" s="9">
-        <v>46092.554307094906</v>
+        <v>46092.72097376158</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1517,13 +1517,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.40775064815</v>
+        <v>46073.57441731481</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55427634259</v>
+        <v>46092.72094300926</v>
       </c>
       <c r="D6" s="5">
-        <v>46133.72324875</v>
+        <v>46133.88991541667</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1580,13 +1580,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="9">
-        <v>46073.407750949074</v>
+        <v>46073.574417615746</v>
       </c>
       <c r="C7" s="9">
-        <v>46092.55427680556</v>
+        <v>46092.72094347222</v>
       </c>
       <c r="D7" s="9">
-        <v>46133.723297847224</v>
+        <v>46133.88996451389</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>39</v>
@@ -1643,13 +1643,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.40775128472</v>
+        <v>46073.574417951386</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.554277268515</v>
+        <v>46092.72094393519</v>
       </c>
       <c r="D8" s="5">
-        <v>46133.724536319445</v>
+        <v>46133.89120298611</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1706,13 +1706,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46073.40775158565</v>
+        <v>46073.57441825232</v>
       </c>
       <c r="C9" s="9">
-        <v>46092.55427813657</v>
+        <v>46092.72094480324</v>
       </c>
       <c r="D9" s="9">
-        <v>46133.72464994213</v>
+        <v>46133.891316608795</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -1769,13 +1769,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.40775292824</v>
+        <v>46073.57441959491</v>
       </c>
       <c r="C10" s="5">
-        <v>46114.352509131946</v>
+        <v>46114.51917579861</v>
       </c>
       <c r="D10" s="5">
-        <v>46139.37187028935</v>
+        <v>46139.53853695602</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -1818,13 +1818,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="9">
-        <v>46073.40775053241</v>
+        <v>46073.574417199074</v>
       </c>
       <c r="C11" s="9">
-        <v>46097.38446746528</v>
+        <v>46097.55113413194</v>
       </c>
       <c r="D11" s="9">
-        <v>46097.38448552083</v>
+        <v>46097.5511521875</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -1883,13 +1883,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.40775118055</v>
+        <v>46073.57441784722</v>
       </c>
       <c r="C12" s="5">
-        <v>46114.35229440972</v>
+        <v>46114.51896107639</v>
       </c>
       <c r="D12" s="5">
-        <v>46133.73070047454</v>
+        <v>46133.8973671412</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -1948,13 +1948,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="9">
-        <v>46073.407751446764</v>
+        <v>46073.57441811342</v>
       </c>
       <c r="C13" s="9">
-        <v>46097.38480086805</v>
+        <v>46097.55146753472</v>
       </c>
       <c r="D13" s="9">
-        <v>46097.384814907404</v>
+        <v>46097.551481574075</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>58</v>
@@ -2013,13 +2013,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.407751736115</v>
+        <v>46073.57441840278</v>
       </c>
       <c r="C14" s="5">
-        <v>46134.44046914352</v>
+        <v>46134.60713581018</v>
       </c>
       <c r="D14" s="5">
-        <v>46134.440470347225</v>
+        <v>46134.60713701389</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2078,13 +2078,13 @@
         <v>62</v>
       </c>
       <c r="B15" s="9">
-        <v>46073.40775200231</v>
+        <v>46073.574418668984</v>
       </c>
       <c r="C15" s="9">
-        <v>46114.35522046297</v>
+        <v>46114.52188712963</v>
       </c>
       <c r="D15" s="9">
-        <v>46114.355231180554</v>
+        <v>46114.521897847226</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>63</v>
@@ -2131,13 +2131,13 @@
         <v>65</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.40775229166</v>
+        <v>46073.574418958335</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.35517708333</v>
+        <v>46114.52184375</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.35535027778</v>
+        <v>46114.522016944444</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>66</v>
@@ -2196,13 +2196,13 @@
         <v>68</v>
       </c>
       <c r="B17" s="9">
-        <v>46073.407753125</v>
+        <v>46073.574419791665</v>
       </c>
       <c r="C17" s="9">
-        <v>46114.35520486112</v>
+        <v>46114.52187152777</v>
       </c>
       <c r="D17" s="9">
-        <v>46133.72593783565</v>
+        <v>46133.89260450231</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>69</v>
@@ -2261,13 +2261,13 @@
         <v>73</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.407752569445</v>
+        <v>46073.574419236116</v>
       </c>
       <c r="C18" s="5">
-        <v>46097.38451211806</v>
+        <v>46097.55117878472</v>
       </c>
       <c r="D18" s="5">
-        <v>46133.72968005787</v>
+        <v>46133.896346724534</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>74</v>
@@ -2326,13 +2326,13 @@
         <v>77</v>
       </c>
       <c r="B19" s="9">
-        <v>46073.40774984953</v>
+        <v>46073.5744165162</v>
       </c>
       <c r="C19" s="9">
-        <v>46097.38483890046</v>
+        <v>46097.55150556713</v>
       </c>
       <c r="D19" s="9">
-        <v>46100.6192175926</v>
+        <v>46100.785884259254</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>78</v>
@@ -2391,13 +2391,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.40775021991</v>
+        <v>46073.57441688658</v>
       </c>
       <c r="C20" s="5">
-        <v>46134.440416412035</v>
+        <v>46134.60708307871</v>
       </c>
       <c r="D20" s="5">
-        <v>46134.440435219905</v>
+        <v>46134.60710188658</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2444,13 +2444,13 @@
         <v>85</v>
       </c>
       <c r="B21" s="9">
-        <v>46073.4077508912</v>
+        <v>46073.57441755787</v>
       </c>
       <c r="C21" s="9">
-        <v>46114.61439836805</v>
+        <v>46114.781065034724</v>
       </c>
       <c r="D21" s="9">
-        <v>46133.725540451385</v>
+        <v>46133.89220711806</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>86</v>
@@ -2509,13 +2509,13 @@
         <v>90</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.407751192135</v>
+        <v>46073.57441785879</v>
       </c>
       <c r="C22" s="5">
-        <v>46114.614341319444</v>
+        <v>46114.78100798611</v>
       </c>
       <c r="D22" s="5">
-        <v>46114.61434273148</v>
+        <v>46114.78100939815</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -2570,13 +2570,13 @@
         <v>95</v>
       </c>
       <c r="B23" s="9">
-        <v>46073.407751481485</v>
+        <v>46073.57441814815</v>
       </c>
       <c r="C23" s="9">
-        <v>46114.61438329861</v>
+        <v>46114.78104996528</v>
       </c>
       <c r="D23" s="9">
-        <v>46114.61438478009</v>
+        <v>46114.78105144676</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>96</v>
@@ -2631,13 +2631,13 @@
         <v>98</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.40775269676</v>
+        <v>46073.57441936343</v>
       </c>
       <c r="C24" s="5">
-        <v>46133.73091304398</v>
+        <v>46133.89757971065</v>
       </c>
       <c r="D24" s="5">
-        <v>46133.73092556713</v>
+        <v>46133.8975922338</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>99</v>
@@ -2696,13 +2696,13 @@
         <v>101</v>
       </c>
       <c r="B25" s="9">
-        <v>46073.40775298611</v>
+        <v>46073.57441965278</v>
       </c>
       <c r="C25" s="9">
-        <v>46122.537756412035</v>
+        <v>46122.7044230787</v>
       </c>
       <c r="D25" s="9">
-        <v>46122.537758101855</v>
+        <v>46122.70442476852</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>102</v>
@@ -2757,13 +2757,13 @@
         <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.40774980324</v>
+        <v>46073.574416469906</v>
       </c>
       <c r="C26" s="5">
-        <v>46133.73089946759</v>
+        <v>46133.897566134256</v>
       </c>
       <c r="D26" s="5">
-        <v>46133.730901006944</v>
+        <v>46133.897567673615</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -2818,13 +2818,13 @@
         <v>107</v>
       </c>
       <c r="B27" s="9">
-        <v>46073.40775017361</v>
+        <v>46073.574416840274</v>
       </c>
       <c r="C27" s="9">
-        <v>46097.384699664355</v>
+        <v>46097.55136633102</v>
       </c>
       <c r="D27" s="9">
-        <v>46097.38471313658</v>
+        <v>46097.55137980324</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>108</v>
@@ -2883,13 +2883,13 @@
         <v>110</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.40775046297</v>
+        <v>46073.574417129625</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.38461346064</v>
+        <v>46097.551280127314</v>
       </c>
       <c r="D28" s="5">
-        <v>46097.38461493056</v>
+        <v>46097.55128159722</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>111</v>
@@ -2944,13 +2944,13 @@
         <v>113</v>
       </c>
       <c r="B29" s="9">
-        <v>46073.407750729166</v>
+        <v>46073.57441739584</v>
       </c>
       <c r="C29" s="9">
-        <v>46097.384648148145</v>
+        <v>46097.55131481482</v>
       </c>
       <c r="D29" s="9">
-        <v>46097.38464950232</v>
+        <v>46097.55131616898</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>114</v>
@@ -3005,13 +3005,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.40775103009</v>
+        <v>46073.57441769676</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.38468446759</v>
+        <v>46097.55135113426</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.38468596065</v>
+        <v>46097.55135262731</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>117</v>
@@ -3066,13 +3066,13 @@
         <v>119</v>
       </c>
       <c r="B31" s="9">
-        <v>46073.40775128472</v>
+        <v>46073.574417951386</v>
       </c>
       <c r="C31" s="9">
-        <v>46111.63208436343</v>
+        <v>46111.79875103009</v>
       </c>
       <c r="D31" s="9">
-        <v>46111.632097361115</v>
+        <v>46111.79876402778</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>120</v>
@@ -3131,13 +3131,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.40775155093</v>
+        <v>46073.57441821759</v>
       </c>
       <c r="C32" s="5">
-        <v>46097.38526033565</v>
+        <v>46097.551927002314</v>
       </c>
       <c r="D32" s="5">
-        <v>46097.38526181713</v>
+        <v>46097.551928483794</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3192,13 +3192,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="9">
-        <v>46073.40775180556</v>
+        <v>46073.57441847222</v>
       </c>
       <c r="C33" s="9">
-        <v>46111.63206998842</v>
+        <v>46111.798736655095</v>
       </c>
       <c r="D33" s="9">
-        <v>46111.63207150463</v>
+        <v>46111.798738171296</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>128</v>
@@ -3253,13 +3253,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.40775208334</v>
+        <v>46073.574418749995</v>
       </c>
       <c r="C34" s="5">
-        <v>46198.39838270833</v>
+        <v>46198.565049375</v>
       </c>
       <c r="D34" s="5">
-        <v>46198.398395208336</v>
+        <v>46198.565061875</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3306,13 +3306,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="9">
-        <v>46073.407752349536</v>
+        <v>46073.57441901621</v>
       </c>
       <c r="C35" s="9">
-        <v>46108.60108274306</v>
+        <v>46108.76774940972</v>
       </c>
       <c r="D35" s="9">
-        <v>46197.54244535879</v>
+        <v>46197.70911202546</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>134</v>
@@ -3371,13 +3371,13 @@
         <v>138</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.40775028935</v>
+        <v>46073.57441695602</v>
       </c>
       <c r="C36" s="5">
-        <v>46108.60118219907</v>
+        <v>46108.76784886574</v>
       </c>
       <c r="D36" s="5">
-        <v>46197.54247858796</v>
+        <v>46197.70914525463</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>139</v>
@@ -3436,13 +3436,13 @@
         <v>142</v>
       </c>
       <c r="B37" s="9">
-        <v>46090.529563310185</v>
+        <v>46090.69622997685</v>
       </c>
       <c r="C37" s="9">
-        <v>46108.60141636574</v>
+        <v>46108.76808303241</v>
       </c>
       <c r="D37" s="9">
-        <v>46108.60143265047</v>
+        <v>46108.76809931713</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>143</v>
@@ -3501,13 +3501,13 @@
         <v>147</v>
       </c>
       <c r="B38" s="5">
-        <v>46090.52978670139</v>
+        <v>46090.69645336806</v>
       </c>
       <c r="C38" s="5">
-        <v>46198.39836409722</v>
+        <v>46198.565030763886</v>
       </c>
       <c r="D38" s="5">
-        <v>46198.398383125</v>
+        <v>46198.565049791665</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>148</v>
@@ -3566,13 +3566,13 @@
         <v>153</v>
       </c>
       <c r="B39" s="9">
-        <v>46073.4077505787</v>
+        <v>46073.57441724537</v>
       </c>
       <c r="C39" s="9">
-        <v>46111.63221431713</v>
+        <v>46111.7988809838</v>
       </c>
       <c r="D39" s="9">
-        <v>46111.63222694444</v>
+        <v>46111.79889361111</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>154</v>
@@ -3619,13 +3619,13 @@
         <v>156</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.40775079861</v>
+        <v>46073.57441746528</v>
       </c>
       <c r="C40" s="5">
-        <v>46111.63215450232</v>
+        <v>46111.79882116898</v>
       </c>
       <c r="D40" s="5">
-        <v>46111.63217065972</v>
+        <v>46111.798837326394</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>157</v>
@@ -3684,13 +3684,13 @@
         <v>161</v>
       </c>
       <c r="B41" s="9">
-        <v>46073.40775103009</v>
+        <v>46073.57441769676</v>
       </c>
       <c r="C41" s="9">
-        <v>46111.632198287036</v>
+        <v>46111.7988649537</v>
       </c>
       <c r="D41" s="9">
-        <v>46111.632214178244</v>
+        <v>46111.79888084491</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>162</v>
@@ -3749,13 +3749,13 @@
         <v>165</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.40775126158</v>
+        <v>46073.57441792824</v>
       </c>
       <c r="C42" s="5">
-        <v>46195.74522711805</v>
+        <v>46195.91189378472</v>
       </c>
       <c r="D42" s="5">
-        <v>46196.684344803245</v>
+        <v>46196.8510114699</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>166</v>
@@ -3798,13 +3798,13 @@
         <v>168</v>
       </c>
       <c r="B43" s="9">
-        <v>46073.407751493054</v>
+        <v>46073.574418159726</v>
       </c>
       <c r="C43" s="9">
-        <v>46107.56083722222</v>
+        <v>46107.72750388889</v>
       </c>
       <c r="D43" s="9">
-        <v>46196.684302152775</v>
+        <v>46196.850968819446</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>169</v>
@@ -3863,13 +3863,13 @@
         <v>173</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.40775171296</v>
+        <v>46073.574418379634</v>
       </c>
       <c r="C44" s="5">
-        <v>46146.39678314815</v>
+        <v>46146.563449814814</v>
       </c>
       <c r="D44" s="5">
-        <v>46195.74489944444</v>
+        <v>46195.911566111114</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>174</v>
@@ -3928,13 +3928,13 @@
         <v>177</v>
       </c>
       <c r="B45" s="9">
-        <v>46073.40775194444</v>
+        <v>46073.57441861111</v>
       </c>
       <c r="C45" s="9">
-        <v>46195.745206631946</v>
+        <v>46195.91187329861</v>
       </c>
       <c r="D45" s="9">
-        <v>46196.74385425926</v>
+        <v>46196.91052092593</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>178</v>
@@ -3993,13 +3993,13 @@
         <v>181</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.4077521875</v>
+        <v>46073.57441885417</v>
       </c>
       <c r="C46" s="5">
-        <v>46195.44041152778</v>
+        <v>46195.60707819444</v>
       </c>
       <c r="D46" s="5">
-        <v>46195.440423078704</v>
+        <v>46195.607089745376</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>154</v>
@@ -4046,13 +4046,13 @@
         <v>183</v>
       </c>
       <c r="B47" s="9">
-        <v>46073.40775005787</v>
+        <v>46073.574416724536</v>
       </c>
       <c r="C47" s="9">
-        <v>46127.48360153935</v>
+        <v>46127.65026820602</v>
       </c>
       <c r="D47" s="9">
-        <v>46127.48373905093</v>
+        <v>46127.65040571759</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>184</v>
@@ -4111,13 +4111,13 @@
         <v>186</v>
       </c>
       <c r="B48" s="5">
-        <v>46073.40775244213</v>
+        <v>46073.5744191088</v>
       </c>
       <c r="C48" s="5">
-        <v>46195.44039379629</v>
+        <v>46195.607060462964</v>
       </c>
       <c r="D48" s="5">
-        <v>46195.44041170139</v>
+        <v>46195.607078368055</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>187</v>
@@ -4176,13 +4176,13 @@
         <v>189</v>
       </c>
       <c r="B49" s="9">
-        <v>46073.40775033565</v>
+        <v>46073.57441700231</v>
       </c>
       <c r="C49" s="9">
-        <v>46122.48811438658</v>
+        <v>46122.654781053236</v>
       </c>
       <c r="D49" s="9">
-        <v>46122.488134652776</v>
+        <v>46122.65480131944</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>190</v>
@@ -4241,11 +4241,11 @@
         <v>192</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.40775060185</v>
+        <v>46073.57441726852</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46197.33929959491</v>
+        <v>46197.505966261575</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>193</v>
@@ -4288,13 +4288,13 @@
         <v>195</v>
       </c>
       <c r="B51" s="9">
-        <v>46073.407751192135</v>
+        <v>46073.57441785879</v>
       </c>
       <c r="C51" s="9">
-        <v>46197.33879725695</v>
+        <v>46197.50546392361</v>
       </c>
       <c r="D51" s="9">
-        <v>46197.3388141551</v>
+        <v>46197.50548082176</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>196</v>
@@ -4353,13 +4353,13 @@
         <v>198</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.4077514699</v>
+        <v>46073.57441813657</v>
       </c>
       <c r="C52" s="5">
-        <v>46197.338886412035</v>
+        <v>46197.50555307871</v>
       </c>
       <c r="D52" s="5">
-        <v>46197.338901423616</v>
+        <v>46197.50556809027</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>199</v>
@@ -4418,13 +4418,13 @@
         <v>202</v>
       </c>
       <c r="B53" s="9">
-        <v>46073.40775171296</v>
+        <v>46073.574418379634</v>
       </c>
       <c r="C53" s="9">
-        <v>46197.33890447917</v>
+        <v>46197.50557114583</v>
       </c>
       <c r="D53" s="9">
-        <v>46197.338922106486</v>
+        <v>46197.50558877314</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>203</v>
@@ -4483,13 +4483,13 @@
         <v>205</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.40775196759</v>
+        <v>46073.57441863426</v>
       </c>
       <c r="C54" s="5">
-        <v>46197.339196574074</v>
+        <v>46197.505863240745</v>
       </c>
       <c r="D54" s="5">
-        <v>46197.33921306713</v>
+        <v>46197.5058797338</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>206</v>
@@ -4548,13 +4548,13 @@
         <v>208</v>
       </c>
       <c r="B55" s="9">
-        <v>46073.40775226852</v>
+        <v>46073.57441893518</v>
       </c>
       <c r="C55" s="9">
-        <v>46197.3392925</v>
+        <v>46197.505959166665</v>
       </c>
       <c r="D55" s="9">
-        <v>46197.339310138894</v>
+        <v>46197.50597680555</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>151</v>
@@ -4611,11 +4611,11 @@
         <v>211</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.407752534724</v>
+        <v>46073.57441920139</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46198.39838351852</v>
+        <v>46198.565050185185</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>212</v>
@@ -4672,11 +4672,11 @@
         <v>215</v>
       </c>
       <c r="B57" s="9">
-        <v>46073.40775020834</v>
+        <v>46073.574416874995</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46090.5351549537</v>
+        <v>46090.70182162037</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>216</v>
@@ -4719,11 +4719,11 @@
         <v>218</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.407750555554</v>
+        <v>46073.57441722222</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46133.731815046296</v>
+        <v>46133.89848171297</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>219</v>
@@ -4780,11 +4780,11 @@
         <v>222</v>
       </c>
       <c r="B59" s="9">
-        <v>46073.407750810184</v>
+        <v>46073.57441747685</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46107.99797167824</v>
+        <v>46108.16463834491</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>223</v>
@@ -4841,11 +4841,11 @@
         <v>225</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.40775108796</v>
+        <v>46073.57441775463</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46108.08432915509</v>
+        <v>46108.250995821756</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>226</v>
@@ -4904,11 +4904,11 @@
         <v>228</v>
       </c>
       <c r="B61" s="9">
-        <v>46073.40775134259</v>
+        <v>46073.57441800926</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46111.96357416667</v>
+        <v>46112.13024083333</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>229</v>
@@ -4967,11 +4967,11 @@
         <v>231</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.4077516088</v>
+        <v>46073.574418275464</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46090.53515497685</v>
+        <v>46090.70182164352</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>232</v>
@@ -5014,11 +5014,11 @@
         <v>234</v>
       </c>
       <c r="B63" s="9">
-        <v>46073.40775190972</v>
+        <v>46073.57441857639</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46121.00034344908</v>
+        <v>46121.167010115736</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>235</v>
@@ -5077,11 +5077,11 @@
         <v>238</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.407752175925</v>
+        <v>46073.57441884259</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46121.00034346065</v>
+        <v>46121.16701012732</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>239</v>

--- a/data/50001508 - XEMORTIZ STOCK.xlsx
+++ b/data/50001508 - XEMORTIZ STOCK.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="242">
   <si>
     <t>50001508 - XEMORTIZ STOCK</t>
   </si>
@@ -715,6 +715,12 @@
   </si>
   <si>
     <t>Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>Karin Pinto</t>
+  </si>
+  <si>
+    <t>kpinto@zitron.com</t>
   </si>
   <si>
     <t>El siguiente pedido será enviado a Mexico junto a los pedido 50001520 + 50001532</t>
@@ -4723,7 +4729,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46133.89848171297</v>
+        <v>46204.70881619213</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>219</v>
@@ -4732,10 +4738,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>35</v>
+        <v>220</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>36</v>
+        <v>221</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
@@ -4745,7 +4751,7 @@
         <v>26</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="M58" s="6" t="s">
         <v>26</v>
@@ -4757,7 +4763,7 @@
         <v>212</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q58" s="5">
         <v>46106</v>
@@ -4777,7 +4783,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B59" s="9">
         <v>46073.57441747685</v>
@@ -4787,7 +4793,7 @@
         <v>46108.16463834491</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -4818,7 +4824,7 @@
         <v>219</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q59" s="9">
         <v>46107</v>
@@ -4838,7 +4844,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B60" s="5">
         <v>46073.57441775463</v>
@@ -4848,7 +4854,7 @@
         <v>46108.250995821756</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -4878,10 +4884,10 @@
         <v>216</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q60" s="5">
         <v>46080</v>
@@ -4901,7 +4907,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B61" s="9">
         <v>46073.57441800926</v>
@@ -4911,7 +4917,7 @@
         <v>46112.13024083333</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
@@ -4941,10 +4947,10 @@
         <v>216</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q61" s="9">
         <v>46111</v>
@@ -4964,7 +4970,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B62" s="5">
         <v>46073.574418275464</v>
@@ -4974,7 +4980,7 @@
         <v>46090.70182164352</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -4998,7 +5004,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5011,7 +5017,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B63" s="9">
         <v>46073.57441857639</v>
@@ -5021,16 +5027,16 @@
         <v>46121.167010115736</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I63" s="9">
         <v>46112</v>
@@ -5048,13 +5054,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q63" s="9">
         <v>46120</v>
@@ -5074,7 +5080,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B64" s="5">
         <v>46073.57441884259</v>
@@ -5084,16 +5090,16 @@
         <v>46121.16701012732</v>
       </c>
       <c r="E64" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>239</v>
-      </c>
-      <c r="F64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G64" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="I64" s="5">
         <v>46112</v>
@@ -5111,13 +5117,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q64" s="5">
         <v>46120</v>

--- a/data/50001508 - XEMORTIZ STOCK.xlsx
+++ b/data/50001508 - XEMORTIZ STOCK.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="242">
   <si>
     <t>50001508 - XEMORTIZ STOCK</t>
   </si>
@@ -699,34 +699,34 @@
     <t>Montaje:,Coordinacion Entrega con Cliente</t>
   </si>
   <si>
+    <t>1213333053701062</t>
+  </si>
+  <si>
+    <t>Logistica:</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,Embalaje,PACKING LIST,Despacho</t>
+  </si>
+  <si>
+    <t>1213333053701063</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>Karin Pinto</t>
+  </si>
+  <si>
+    <t>kpinto@zitron.com</t>
+  </si>
+  <si>
+    <t>El siguiente pedido será enviado a Mexico junto a los pedido 50001520 + 50001532</t>
+  </si>
+  <si>
+    <t>Embalaje,Logistica:</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1213333053701062</t>
-  </si>
-  <si>
-    <t>Logistica:</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,Embalaje,PACKING LIST,Despacho</t>
-  </si>
-  <si>
-    <t>1213333053701063</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>Karin Pinto</t>
-  </si>
-  <si>
-    <t>kpinto@zitron.com</t>
-  </si>
-  <si>
-    <t>El siguiente pedido será enviado a Mexico junto a los pedido 50001520 + 50001532</t>
-  </si>
-  <si>
-    <t>Embalaje,Logistica:</t>
   </si>
   <si>
     <t>1213333053701064</t>
@@ -1407,13 +1407,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.574416574076</v>
+        <v>46073.407749907405</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.72097336805</v>
+        <v>46092.55430670139</v>
       </c>
       <c r="D4" s="5">
-        <v>46092.72098704861</v>
+        <v>46092.55432038194</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1460,13 +1460,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46073.57441700231</v>
+        <v>46073.40775033565</v>
       </c>
       <c r="C5" s="9">
-        <v>46092.72094241898</v>
+        <v>46092.554275752314</v>
       </c>
       <c r="D5" s="9">
-        <v>46092.72097376158</v>
+        <v>46092.554307094906</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1523,13 +1523,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.57441731481</v>
+        <v>46073.40775064815</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.72094300926</v>
+        <v>46092.55427634259</v>
       </c>
       <c r="D6" s="5">
-        <v>46133.88991541667</v>
+        <v>46133.72324875</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1586,13 +1586,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="9">
-        <v>46073.574417615746</v>
+        <v>46073.407750949074</v>
       </c>
       <c r="C7" s="9">
-        <v>46092.72094347222</v>
+        <v>46092.55427680556</v>
       </c>
       <c r="D7" s="9">
-        <v>46133.88996451389</v>
+        <v>46133.723297847224</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>39</v>
@@ -1649,13 +1649,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.574417951386</v>
+        <v>46073.40775128472</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.72094393519</v>
+        <v>46092.554277268515</v>
       </c>
       <c r="D8" s="5">
-        <v>46133.89120298611</v>
+        <v>46133.724536319445</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1712,13 +1712,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46073.57441825232</v>
+        <v>46073.40775158565</v>
       </c>
       <c r="C9" s="9">
-        <v>46092.72094480324</v>
+        <v>46092.55427813657</v>
       </c>
       <c r="D9" s="9">
-        <v>46133.891316608795</v>
+        <v>46133.72464994213</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -1775,13 +1775,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.57441959491</v>
+        <v>46073.40775292824</v>
       </c>
       <c r="C10" s="5">
-        <v>46114.51917579861</v>
+        <v>46114.352509131946</v>
       </c>
       <c r="D10" s="5">
-        <v>46139.53853695602</v>
+        <v>46139.37187028935</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -1824,13 +1824,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="9">
-        <v>46073.574417199074</v>
+        <v>46073.40775053241</v>
       </c>
       <c r="C11" s="9">
-        <v>46097.55113413194</v>
+        <v>46097.38446746528</v>
       </c>
       <c r="D11" s="9">
-        <v>46097.5511521875</v>
+        <v>46097.38448552083</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -1889,13 +1889,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.57441784722</v>
+        <v>46073.40775118055</v>
       </c>
       <c r="C12" s="5">
-        <v>46114.51896107639</v>
+        <v>46114.35229440972</v>
       </c>
       <c r="D12" s="5">
-        <v>46133.8973671412</v>
+        <v>46133.73070047454</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -1954,13 +1954,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="9">
-        <v>46073.57441811342</v>
+        <v>46073.407751446764</v>
       </c>
       <c r="C13" s="9">
-        <v>46097.55146753472</v>
+        <v>46097.38480086805</v>
       </c>
       <c r="D13" s="9">
-        <v>46097.551481574075</v>
+        <v>46097.384814907404</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>58</v>
@@ -2019,13 +2019,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.57441840278</v>
+        <v>46073.407751736115</v>
       </c>
       <c r="C14" s="5">
-        <v>46134.60713581018</v>
+        <v>46134.44046914352</v>
       </c>
       <c r="D14" s="5">
-        <v>46134.60713701389</v>
+        <v>46134.440470347225</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2084,13 +2084,13 @@
         <v>62</v>
       </c>
       <c r="B15" s="9">
-        <v>46073.574418668984</v>
+        <v>46073.40775200231</v>
       </c>
       <c r="C15" s="9">
-        <v>46114.52188712963</v>
+        <v>46114.35522046297</v>
       </c>
       <c r="D15" s="9">
-        <v>46114.521897847226</v>
+        <v>46114.355231180554</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>63</v>
@@ -2137,13 +2137,13 @@
         <v>65</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.574418958335</v>
+        <v>46073.40775229166</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.52184375</v>
+        <v>46114.35517708333</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.522016944444</v>
+        <v>46114.35535027778</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>66</v>
@@ -2202,13 +2202,13 @@
         <v>68</v>
       </c>
       <c r="B17" s="9">
-        <v>46073.574419791665</v>
+        <v>46073.407753125</v>
       </c>
       <c r="C17" s="9">
-        <v>46114.52187152777</v>
+        <v>46114.35520486112</v>
       </c>
       <c r="D17" s="9">
-        <v>46133.89260450231</v>
+        <v>46133.72593783565</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>69</v>
@@ -2267,13 +2267,13 @@
         <v>73</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.574419236116</v>
+        <v>46073.407752569445</v>
       </c>
       <c r="C18" s="5">
-        <v>46097.55117878472</v>
+        <v>46097.38451211806</v>
       </c>
       <c r="D18" s="5">
-        <v>46133.896346724534</v>
+        <v>46133.72968005787</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>74</v>
@@ -2332,13 +2332,13 @@
         <v>77</v>
       </c>
       <c r="B19" s="9">
-        <v>46073.5744165162</v>
+        <v>46073.40774984953</v>
       </c>
       <c r="C19" s="9">
-        <v>46097.55150556713</v>
+        <v>46097.38483890046</v>
       </c>
       <c r="D19" s="9">
-        <v>46100.785884259254</v>
+        <v>46100.6192175926</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>78</v>
@@ -2397,13 +2397,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.57441688658</v>
+        <v>46073.40775021991</v>
       </c>
       <c r="C20" s="5">
-        <v>46134.60708307871</v>
+        <v>46134.440416412035</v>
       </c>
       <c r="D20" s="5">
-        <v>46134.60710188658</v>
+        <v>46134.440435219905</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2450,13 +2450,13 @@
         <v>85</v>
       </c>
       <c r="B21" s="9">
-        <v>46073.57441755787</v>
+        <v>46073.4077508912</v>
       </c>
       <c r="C21" s="9">
-        <v>46114.781065034724</v>
+        <v>46114.61439836805</v>
       </c>
       <c r="D21" s="9">
-        <v>46133.89220711806</v>
+        <v>46133.725540451385</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>86</v>
@@ -2515,13 +2515,13 @@
         <v>90</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.57441785879</v>
+        <v>46073.407751192135</v>
       </c>
       <c r="C22" s="5">
-        <v>46114.78100798611</v>
+        <v>46114.614341319444</v>
       </c>
       <c r="D22" s="5">
-        <v>46114.78100939815</v>
+        <v>46114.61434273148</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -2576,13 +2576,13 @@
         <v>95</v>
       </c>
       <c r="B23" s="9">
-        <v>46073.57441814815</v>
+        <v>46073.407751481485</v>
       </c>
       <c r="C23" s="9">
-        <v>46114.78104996528</v>
+        <v>46114.61438329861</v>
       </c>
       <c r="D23" s="9">
-        <v>46114.78105144676</v>
+        <v>46114.61438478009</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>96</v>
@@ -2637,13 +2637,13 @@
         <v>98</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.57441936343</v>
+        <v>46073.40775269676</v>
       </c>
       <c r="C24" s="5">
-        <v>46133.89757971065</v>
+        <v>46133.73091304398</v>
       </c>
       <c r="D24" s="5">
-        <v>46133.8975922338</v>
+        <v>46133.73092556713</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>99</v>
@@ -2702,13 +2702,13 @@
         <v>101</v>
       </c>
       <c r="B25" s="9">
-        <v>46073.57441965278</v>
+        <v>46073.40775298611</v>
       </c>
       <c r="C25" s="9">
-        <v>46122.7044230787</v>
+        <v>46122.537756412035</v>
       </c>
       <c r="D25" s="9">
-        <v>46122.70442476852</v>
+        <v>46122.537758101855</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>102</v>
@@ -2763,13 +2763,13 @@
         <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.574416469906</v>
+        <v>46073.40774980324</v>
       </c>
       <c r="C26" s="5">
-        <v>46133.897566134256</v>
+        <v>46133.73089946759</v>
       </c>
       <c r="D26" s="5">
-        <v>46133.897567673615</v>
+        <v>46133.730901006944</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -2824,13 +2824,13 @@
         <v>107</v>
       </c>
       <c r="B27" s="9">
-        <v>46073.574416840274</v>
+        <v>46073.40775017361</v>
       </c>
       <c r="C27" s="9">
-        <v>46097.55136633102</v>
+        <v>46097.384699664355</v>
       </c>
       <c r="D27" s="9">
-        <v>46097.55137980324</v>
+        <v>46097.38471313658</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>108</v>
@@ -2889,13 +2889,13 @@
         <v>110</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.574417129625</v>
+        <v>46073.40775046297</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.551280127314</v>
+        <v>46097.38461346064</v>
       </c>
       <c r="D28" s="5">
-        <v>46097.55128159722</v>
+        <v>46097.38461493056</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>111</v>
@@ -2950,13 +2950,13 @@
         <v>113</v>
       </c>
       <c r="B29" s="9">
-        <v>46073.57441739584</v>
+        <v>46073.407750729166</v>
       </c>
       <c r="C29" s="9">
-        <v>46097.55131481482</v>
+        <v>46097.384648148145</v>
       </c>
       <c r="D29" s="9">
-        <v>46097.55131616898</v>
+        <v>46097.38464950232</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>114</v>
@@ -3011,13 +3011,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.57441769676</v>
+        <v>46073.40775103009</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.55135113426</v>
+        <v>46097.38468446759</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.55135262731</v>
+        <v>46097.38468596065</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>117</v>
@@ -3072,13 +3072,13 @@
         <v>119</v>
       </c>
       <c r="B31" s="9">
-        <v>46073.574417951386</v>
+        <v>46073.40775128472</v>
       </c>
       <c r="C31" s="9">
-        <v>46111.79875103009</v>
+        <v>46111.63208436343</v>
       </c>
       <c r="D31" s="9">
-        <v>46111.79876402778</v>
+        <v>46111.632097361115</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>120</v>
@@ -3137,13 +3137,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.57441821759</v>
+        <v>46073.40775155093</v>
       </c>
       <c r="C32" s="5">
-        <v>46097.551927002314</v>
+        <v>46097.38526033565</v>
       </c>
       <c r="D32" s="5">
-        <v>46097.551928483794</v>
+        <v>46097.38526181713</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3198,13 +3198,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="9">
-        <v>46073.57441847222</v>
+        <v>46073.40775180556</v>
       </c>
       <c r="C33" s="9">
-        <v>46111.798736655095</v>
+        <v>46111.63206998842</v>
       </c>
       <c r="D33" s="9">
-        <v>46111.798738171296</v>
+        <v>46111.63207150463</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>128</v>
@@ -3259,13 +3259,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.574418749995</v>
+        <v>46073.40775208334</v>
       </c>
       <c r="C34" s="5">
-        <v>46198.565049375</v>
+        <v>46198.39838270833</v>
       </c>
       <c r="D34" s="5">
-        <v>46198.565061875</v>
+        <v>46198.398395208336</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3312,13 +3312,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="9">
-        <v>46073.57441901621</v>
+        <v>46073.407752349536</v>
       </c>
       <c r="C35" s="9">
-        <v>46108.76774940972</v>
+        <v>46108.60108274306</v>
       </c>
       <c r="D35" s="9">
-        <v>46197.70911202546</v>
+        <v>46197.54244535879</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>134</v>
@@ -3377,13 +3377,13 @@
         <v>138</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.57441695602</v>
+        <v>46073.40775028935</v>
       </c>
       <c r="C36" s="5">
-        <v>46108.76784886574</v>
+        <v>46108.60118219907</v>
       </c>
       <c r="D36" s="5">
-        <v>46197.70914525463</v>
+        <v>46197.54247858796</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>139</v>
@@ -3442,13 +3442,13 @@
         <v>142</v>
       </c>
       <c r="B37" s="9">
-        <v>46090.69622997685</v>
+        <v>46090.529563310185</v>
       </c>
       <c r="C37" s="9">
-        <v>46108.76808303241</v>
+        <v>46108.60141636574</v>
       </c>
       <c r="D37" s="9">
-        <v>46108.76809931713</v>
+        <v>46108.60143265047</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>143</v>
@@ -3507,13 +3507,13 @@
         <v>147</v>
       </c>
       <c r="B38" s="5">
-        <v>46090.69645336806</v>
+        <v>46090.52978670139</v>
       </c>
       <c r="C38" s="5">
-        <v>46198.565030763886</v>
+        <v>46198.39836409722</v>
       </c>
       <c r="D38" s="5">
-        <v>46198.565049791665</v>
+        <v>46198.398383125</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>148</v>
@@ -3572,13 +3572,13 @@
         <v>153</v>
       </c>
       <c r="B39" s="9">
-        <v>46073.57441724537</v>
+        <v>46073.4077505787</v>
       </c>
       <c r="C39" s="9">
-        <v>46111.7988809838</v>
+        <v>46111.63221431713</v>
       </c>
       <c r="D39" s="9">
-        <v>46111.79889361111</v>
+        <v>46111.63222694444</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>154</v>
@@ -3625,13 +3625,13 @@
         <v>156</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.57441746528</v>
+        <v>46073.40775079861</v>
       </c>
       <c r="C40" s="5">
-        <v>46111.79882116898</v>
+        <v>46111.63215450232</v>
       </c>
       <c r="D40" s="5">
-        <v>46111.798837326394</v>
+        <v>46111.63217065972</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>157</v>
@@ -3690,13 +3690,13 @@
         <v>161</v>
       </c>
       <c r="B41" s="9">
-        <v>46073.57441769676</v>
+        <v>46073.40775103009</v>
       </c>
       <c r="C41" s="9">
-        <v>46111.7988649537</v>
+        <v>46111.632198287036</v>
       </c>
       <c r="D41" s="9">
-        <v>46111.79888084491</v>
+        <v>46111.632214178244</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>162</v>
@@ -3755,13 +3755,13 @@
         <v>165</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.57441792824</v>
+        <v>46073.40775126158</v>
       </c>
       <c r="C42" s="5">
-        <v>46195.91189378472</v>
+        <v>46195.74522711805</v>
       </c>
       <c r="D42" s="5">
-        <v>46196.8510114699</v>
+        <v>46196.684344803245</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>166</v>
@@ -3804,13 +3804,13 @@
         <v>168</v>
       </c>
       <c r="B43" s="9">
-        <v>46073.574418159726</v>
+        <v>46073.407751493054</v>
       </c>
       <c r="C43" s="9">
-        <v>46107.72750388889</v>
+        <v>46107.56083722222</v>
       </c>
       <c r="D43" s="9">
-        <v>46196.850968819446</v>
+        <v>46196.684302152775</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>169</v>
@@ -3869,13 +3869,13 @@
         <v>173</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.574418379634</v>
+        <v>46073.40775171296</v>
       </c>
       <c r="C44" s="5">
-        <v>46146.563449814814</v>
+        <v>46146.39678314815</v>
       </c>
       <c r="D44" s="5">
-        <v>46195.911566111114</v>
+        <v>46195.74489944444</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>174</v>
@@ -3934,13 +3934,13 @@
         <v>177</v>
       </c>
       <c r="B45" s="9">
-        <v>46073.57441861111</v>
+        <v>46073.40775194444</v>
       </c>
       <c r="C45" s="9">
-        <v>46195.91187329861</v>
+        <v>46195.745206631946</v>
       </c>
       <c r="D45" s="9">
-        <v>46196.91052092593</v>
+        <v>46196.74385425926</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>178</v>
@@ -3999,13 +3999,13 @@
         <v>181</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.57441885417</v>
+        <v>46073.4077521875</v>
       </c>
       <c r="C46" s="5">
-        <v>46195.60707819444</v>
+        <v>46195.44041152778</v>
       </c>
       <c r="D46" s="5">
-        <v>46195.607089745376</v>
+        <v>46195.440423078704</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>154</v>
@@ -4052,13 +4052,13 @@
         <v>183</v>
       </c>
       <c r="B47" s="9">
-        <v>46073.574416724536</v>
+        <v>46073.40775005787</v>
       </c>
       <c r="C47" s="9">
-        <v>46127.65026820602</v>
+        <v>46127.48360153935</v>
       </c>
       <c r="D47" s="9">
-        <v>46127.65040571759</v>
+        <v>46127.48373905093</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>184</v>
@@ -4117,13 +4117,13 @@
         <v>186</v>
       </c>
       <c r="B48" s="5">
-        <v>46073.5744191088</v>
+        <v>46073.40775244213</v>
       </c>
       <c r="C48" s="5">
-        <v>46195.607060462964</v>
+        <v>46195.44039379629</v>
       </c>
       <c r="D48" s="5">
-        <v>46195.607078368055</v>
+        <v>46195.44041170139</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>187</v>
@@ -4182,13 +4182,13 @@
         <v>189</v>
       </c>
       <c r="B49" s="9">
-        <v>46073.57441700231</v>
+        <v>46073.40775033565</v>
       </c>
       <c r="C49" s="9">
-        <v>46122.654781053236</v>
+        <v>46122.48811438658</v>
       </c>
       <c r="D49" s="9">
-        <v>46122.65480131944</v>
+        <v>46122.488134652776</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>190</v>
@@ -4247,11 +4247,13 @@
         <v>192</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.57441726852</v>
-      </c>
-      <c r="C50" s="6"/>
+        <v>46073.40775060185</v>
+      </c>
+      <c r="C50" s="5">
+        <v>46205.32204649306</v>
+      </c>
       <c r="D50" s="5">
-        <v>46197.505966261575</v>
+        <v>46205.3220575</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>193</v>
@@ -4286,21 +4288,25 @@
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
       <c r="S50" s="6"/>
-      <c r="T50" s="6"/>
-      <c r="U50" s="6"/>
+      <c r="T50" s="6">
+        <v>1</v>
+      </c>
+      <c r="U50" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
         <v>195</v>
       </c>
       <c r="B51" s="9">
-        <v>46073.57441785879</v>
+        <v>46073.407751192135</v>
       </c>
       <c r="C51" s="9">
-        <v>46197.50546392361</v>
+        <v>46197.33879725695</v>
       </c>
       <c r="D51" s="9">
-        <v>46197.50548082176</v>
+        <v>46197.3388141551</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>196</v>
@@ -4359,13 +4365,13 @@
         <v>198</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.57441813657</v>
+        <v>46073.4077514699</v>
       </c>
       <c r="C52" s="5">
-        <v>46197.50555307871</v>
+        <v>46197.338886412035</v>
       </c>
       <c r="D52" s="5">
-        <v>46197.50556809027</v>
+        <v>46197.338901423616</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>199</v>
@@ -4424,13 +4430,13 @@
         <v>202</v>
       </c>
       <c r="B53" s="9">
-        <v>46073.574418379634</v>
+        <v>46073.40775171296</v>
       </c>
       <c r="C53" s="9">
-        <v>46197.50557114583</v>
+        <v>46197.33890447917</v>
       </c>
       <c r="D53" s="9">
-        <v>46197.50558877314</v>
+        <v>46197.338922106486</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>203</v>
@@ -4489,13 +4495,13 @@
         <v>205</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.57441863426</v>
+        <v>46073.40775196759</v>
       </c>
       <c r="C54" s="5">
-        <v>46197.505863240745</v>
+        <v>46197.339196574074</v>
       </c>
       <c r="D54" s="5">
-        <v>46197.5058797338</v>
+        <v>46197.33921306713</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>206</v>
@@ -4554,13 +4560,13 @@
         <v>208</v>
       </c>
       <c r="B55" s="9">
-        <v>46073.57441893518</v>
+        <v>46073.40775226852</v>
       </c>
       <c r="C55" s="9">
-        <v>46197.505959166665</v>
+        <v>46197.3392925</v>
       </c>
       <c r="D55" s="9">
-        <v>46197.50597680555</v>
+        <v>46197.339310138894</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>151</v>
@@ -4617,11 +4623,13 @@
         <v>211</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.57441920139</v>
-      </c>
-      <c r="C56" s="6"/>
+        <v>46073.407752534724</v>
+      </c>
+      <c r="C56" s="5">
+        <v>46205.322026145834</v>
+      </c>
       <c r="D56" s="5">
-        <v>46198.565050185185</v>
+        <v>46205.32204734954</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>212</v>
@@ -4667,25 +4675,25 @@
         <v>32</v>
       </c>
       <c r="T56" s="6">
-        <v>0</v>
-      </c>
-      <c r="U56" s="12" t="s">
-        <v>214</v>
+        <v>1</v>
+      </c>
+      <c r="U56" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B57" s="9">
-        <v>46073.574416874995</v>
+        <v>46073.40775020834</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46090.70182162037</v>
+        <v>46090.5351549537</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>25</v>
@@ -4709,7 +4717,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -4722,26 +4730,26 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.57441722222</v>
+        <v>46073.407750555554</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46204.70881619213</v>
+        <v>46205.32204747685</v>
       </c>
       <c r="E58" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G58" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="F58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G58" s="6" t="s">
+      <c r="H58" s="6" t="s">
         <v>220</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>221</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
@@ -4751,19 +4759,19 @@
         <v>26</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>212</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q58" s="5">
         <v>46106</v>
@@ -4777,8 +4785,8 @@
       <c r="T58" s="6">
         <v>0</v>
       </c>
-      <c r="U58" s="11" t="s">
-        <v>94</v>
+      <c r="U58" s="12" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -4786,11 +4794,11 @@
         <v>224</v>
       </c>
       <c r="B59" s="9">
-        <v>46073.57441747685</v>
+        <v>46073.407750810184</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46108.16463834491</v>
+        <v>46107.99797167824</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>225</v>
@@ -4818,10 +4826,10 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P59" s="10" t="s">
         <v>226</v>
@@ -4847,11 +4855,11 @@
         <v>227</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.57441775463</v>
+        <v>46073.40775108796</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46108.250995821756</v>
+        <v>46108.08432915509</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>228</v>
@@ -4881,7 +4889,7 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>225</v>
@@ -4910,11 +4918,11 @@
         <v>230</v>
       </c>
       <c r="B61" s="9">
-        <v>46073.57441800926</v>
+        <v>46073.40775134259</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46112.13024083333</v>
+        <v>46111.96357416667</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>231</v>
@@ -4944,7 +4952,7 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O61" s="10" t="s">
         <v>228</v>
@@ -4973,11 +4981,11 @@
         <v>233</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.574418275464</v>
+        <v>46073.4077516088</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46090.70182164352</v>
+        <v>46090.53515497685</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>234</v>
@@ -5020,11 +5028,11 @@
         <v>236</v>
       </c>
       <c r="B63" s="9">
-        <v>46073.57441857639</v>
+        <v>46073.40775190972</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46121.167010115736</v>
+        <v>46121.00034344908</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>237</v>
@@ -5083,11 +5091,11 @@
         <v>240</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.57441884259</v>
+        <v>46073.407752175925</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46121.16701012732</v>
+        <v>46121.00034346065</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>241</v>

--- a/data/50001508 - XEMORTIZ STOCK.xlsx
+++ b/data/50001508 - XEMORTIZ STOCK.xlsx
@@ -1407,13 +1407,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.407749907405</v>
+        <v>46073.574416574076</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55430670139</v>
+        <v>46092.72097336805</v>
       </c>
       <c r="D4" s="5">
-        <v>46092.55432038194</v>
+        <v>46092.72098704861</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1460,13 +1460,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46073.40775033565</v>
+        <v>46073.57441700231</v>
       </c>
       <c r="C5" s="9">
-        <v>46092.554275752314</v>
+        <v>46092.72094241898</v>
       </c>
       <c r="D5" s="9">
-        <v>46092.554307094906</v>
+        <v>46092.72097376158</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1523,13 +1523,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.40775064815</v>
+        <v>46073.57441731481</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55427634259</v>
+        <v>46092.72094300926</v>
       </c>
       <c r="D6" s="5">
-        <v>46133.72324875</v>
+        <v>46133.88991541667</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1586,13 +1586,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="9">
-        <v>46073.407750949074</v>
+        <v>46073.574417615746</v>
       </c>
       <c r="C7" s="9">
-        <v>46092.55427680556</v>
+        <v>46092.72094347222</v>
       </c>
       <c r="D7" s="9">
-        <v>46133.723297847224</v>
+        <v>46133.88996451389</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>39</v>
@@ -1649,13 +1649,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.40775128472</v>
+        <v>46073.574417951386</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.554277268515</v>
+        <v>46092.72094393519</v>
       </c>
       <c r="D8" s="5">
-        <v>46133.724536319445</v>
+        <v>46133.89120298611</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1712,13 +1712,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46073.40775158565</v>
+        <v>46073.57441825232</v>
       </c>
       <c r="C9" s="9">
-        <v>46092.55427813657</v>
+        <v>46092.72094480324</v>
       </c>
       <c r="D9" s="9">
-        <v>46133.72464994213</v>
+        <v>46133.891316608795</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -1775,13 +1775,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.40775292824</v>
+        <v>46073.57441959491</v>
       </c>
       <c r="C10" s="5">
-        <v>46114.352509131946</v>
+        <v>46114.51917579861</v>
       </c>
       <c r="D10" s="5">
-        <v>46139.37187028935</v>
+        <v>46139.53853695602</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -1824,13 +1824,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="9">
-        <v>46073.40775053241</v>
+        <v>46073.574417199074</v>
       </c>
       <c r="C11" s="9">
-        <v>46097.38446746528</v>
+        <v>46097.55113413194</v>
       </c>
       <c r="D11" s="9">
-        <v>46097.38448552083</v>
+        <v>46097.5511521875</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -1889,13 +1889,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.40775118055</v>
+        <v>46073.57441784722</v>
       </c>
       <c r="C12" s="5">
-        <v>46114.35229440972</v>
+        <v>46114.51896107639</v>
       </c>
       <c r="D12" s="5">
-        <v>46133.73070047454</v>
+        <v>46133.8973671412</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -1954,13 +1954,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="9">
-        <v>46073.407751446764</v>
+        <v>46073.57441811342</v>
       </c>
       <c r="C13" s="9">
-        <v>46097.38480086805</v>
+        <v>46097.55146753472</v>
       </c>
       <c r="D13" s="9">
-        <v>46097.384814907404</v>
+        <v>46097.551481574075</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>58</v>
@@ -2019,13 +2019,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.407751736115</v>
+        <v>46073.57441840278</v>
       </c>
       <c r="C14" s="5">
-        <v>46134.44046914352</v>
+        <v>46134.60713581018</v>
       </c>
       <c r="D14" s="5">
-        <v>46134.440470347225</v>
+        <v>46134.60713701389</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2084,13 +2084,13 @@
         <v>62</v>
       </c>
       <c r="B15" s="9">
-        <v>46073.40775200231</v>
+        <v>46073.574418668984</v>
       </c>
       <c r="C15" s="9">
-        <v>46114.35522046297</v>
+        <v>46114.52188712963</v>
       </c>
       <c r="D15" s="9">
-        <v>46114.355231180554</v>
+        <v>46114.521897847226</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>63</v>
@@ -2137,13 +2137,13 @@
         <v>65</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.40775229166</v>
+        <v>46073.574418958335</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.35517708333</v>
+        <v>46114.52184375</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.35535027778</v>
+        <v>46114.522016944444</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>66</v>
@@ -2202,13 +2202,13 @@
         <v>68</v>
       </c>
       <c r="B17" s="9">
-        <v>46073.407753125</v>
+        <v>46073.574419791665</v>
       </c>
       <c r="C17" s="9">
-        <v>46114.35520486112</v>
+        <v>46114.52187152777</v>
       </c>
       <c r="D17" s="9">
-        <v>46133.72593783565</v>
+        <v>46133.89260450231</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>69</v>
@@ -2267,13 +2267,13 @@
         <v>73</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.407752569445</v>
+        <v>46073.574419236116</v>
       </c>
       <c r="C18" s="5">
-        <v>46097.38451211806</v>
+        <v>46097.55117878472</v>
       </c>
       <c r="D18" s="5">
-        <v>46133.72968005787</v>
+        <v>46133.896346724534</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>74</v>
@@ -2332,13 +2332,13 @@
         <v>77</v>
       </c>
       <c r="B19" s="9">
-        <v>46073.40774984953</v>
+        <v>46073.5744165162</v>
       </c>
       <c r="C19" s="9">
-        <v>46097.38483890046</v>
+        <v>46097.55150556713</v>
       </c>
       <c r="D19" s="9">
-        <v>46100.6192175926</v>
+        <v>46100.785884259254</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>78</v>
@@ -2397,13 +2397,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.40775021991</v>
+        <v>46073.57441688658</v>
       </c>
       <c r="C20" s="5">
-        <v>46134.440416412035</v>
+        <v>46134.60708307871</v>
       </c>
       <c r="D20" s="5">
-        <v>46134.440435219905</v>
+        <v>46134.60710188658</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2450,13 +2450,13 @@
         <v>85</v>
       </c>
       <c r="B21" s="9">
-        <v>46073.4077508912</v>
+        <v>46073.57441755787</v>
       </c>
       <c r="C21" s="9">
-        <v>46114.61439836805</v>
+        <v>46114.781065034724</v>
       </c>
       <c r="D21" s="9">
-        <v>46133.725540451385</v>
+        <v>46133.89220711806</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>86</v>
@@ -2515,13 +2515,13 @@
         <v>90</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.407751192135</v>
+        <v>46073.57441785879</v>
       </c>
       <c r="C22" s="5">
-        <v>46114.614341319444</v>
+        <v>46114.78100798611</v>
       </c>
       <c r="D22" s="5">
-        <v>46114.61434273148</v>
+        <v>46114.78100939815</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -2576,13 +2576,13 @@
         <v>95</v>
       </c>
       <c r="B23" s="9">
-        <v>46073.407751481485</v>
+        <v>46073.57441814815</v>
       </c>
       <c r="C23" s="9">
-        <v>46114.61438329861</v>
+        <v>46114.78104996528</v>
       </c>
       <c r="D23" s="9">
-        <v>46114.61438478009</v>
+        <v>46114.78105144676</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>96</v>
@@ -2637,13 +2637,13 @@
         <v>98</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.40775269676</v>
+        <v>46073.57441936343</v>
       </c>
       <c r="C24" s="5">
-        <v>46133.73091304398</v>
+        <v>46133.89757971065</v>
       </c>
       <c r="D24" s="5">
-        <v>46133.73092556713</v>
+        <v>46133.8975922338</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>99</v>
@@ -2702,13 +2702,13 @@
         <v>101</v>
       </c>
       <c r="B25" s="9">
-        <v>46073.40775298611</v>
+        <v>46073.57441965278</v>
       </c>
       <c r="C25" s="9">
-        <v>46122.537756412035</v>
+        <v>46122.7044230787</v>
       </c>
       <c r="D25" s="9">
-        <v>46122.537758101855</v>
+        <v>46122.70442476852</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>102</v>
@@ -2763,13 +2763,13 @@
         <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.40774980324</v>
+        <v>46073.574416469906</v>
       </c>
       <c r="C26" s="5">
-        <v>46133.73089946759</v>
+        <v>46133.897566134256</v>
       </c>
       <c r="D26" s="5">
-        <v>46133.730901006944</v>
+        <v>46133.897567673615</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -2824,13 +2824,13 @@
         <v>107</v>
       </c>
       <c r="B27" s="9">
-        <v>46073.40775017361</v>
+        <v>46073.574416840274</v>
       </c>
       <c r="C27" s="9">
-        <v>46097.384699664355</v>
+        <v>46097.55136633102</v>
       </c>
       <c r="D27" s="9">
-        <v>46097.38471313658</v>
+        <v>46097.55137980324</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>108</v>
@@ -2889,13 +2889,13 @@
         <v>110</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.40775046297</v>
+        <v>46073.574417129625</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.38461346064</v>
+        <v>46097.551280127314</v>
       </c>
       <c r="D28" s="5">
-        <v>46097.38461493056</v>
+        <v>46097.55128159722</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>111</v>
@@ -2950,13 +2950,13 @@
         <v>113</v>
       </c>
       <c r="B29" s="9">
-        <v>46073.407750729166</v>
+        <v>46073.57441739584</v>
       </c>
       <c r="C29" s="9">
-        <v>46097.384648148145</v>
+        <v>46097.55131481482</v>
       </c>
       <c r="D29" s="9">
-        <v>46097.38464950232</v>
+        <v>46097.55131616898</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>114</v>
@@ -3011,13 +3011,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.40775103009</v>
+        <v>46073.57441769676</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.38468446759</v>
+        <v>46097.55135113426</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.38468596065</v>
+        <v>46097.55135262731</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>117</v>
@@ -3072,13 +3072,13 @@
         <v>119</v>
       </c>
       <c r="B31" s="9">
-        <v>46073.40775128472</v>
+        <v>46073.574417951386</v>
       </c>
       <c r="C31" s="9">
-        <v>46111.63208436343</v>
+        <v>46111.79875103009</v>
       </c>
       <c r="D31" s="9">
-        <v>46111.632097361115</v>
+        <v>46111.79876402778</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>120</v>
@@ -3137,13 +3137,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.40775155093</v>
+        <v>46073.57441821759</v>
       </c>
       <c r="C32" s="5">
-        <v>46097.38526033565</v>
+        <v>46097.551927002314</v>
       </c>
       <c r="D32" s="5">
-        <v>46097.38526181713</v>
+        <v>46097.551928483794</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3198,13 +3198,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="9">
-        <v>46073.40775180556</v>
+        <v>46073.57441847222</v>
       </c>
       <c r="C33" s="9">
-        <v>46111.63206998842</v>
+        <v>46111.798736655095</v>
       </c>
       <c r="D33" s="9">
-        <v>46111.63207150463</v>
+        <v>46111.798738171296</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>128</v>
@@ -3259,13 +3259,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.40775208334</v>
+        <v>46073.574418749995</v>
       </c>
       <c r="C34" s="5">
-        <v>46198.39838270833</v>
+        <v>46198.565049375</v>
       </c>
       <c r="D34" s="5">
-        <v>46198.398395208336</v>
+        <v>46198.565061875</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3312,13 +3312,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="9">
-        <v>46073.407752349536</v>
+        <v>46073.57441901621</v>
       </c>
       <c r="C35" s="9">
-        <v>46108.60108274306</v>
+        <v>46108.76774940972</v>
       </c>
       <c r="D35" s="9">
-        <v>46197.54244535879</v>
+        <v>46197.70911202546</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>134</v>
@@ -3377,13 +3377,13 @@
         <v>138</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.40775028935</v>
+        <v>46073.57441695602</v>
       </c>
       <c r="C36" s="5">
-        <v>46108.60118219907</v>
+        <v>46108.76784886574</v>
       </c>
       <c r="D36" s="5">
-        <v>46197.54247858796</v>
+        <v>46197.70914525463</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>139</v>
@@ -3442,13 +3442,13 @@
         <v>142</v>
       </c>
       <c r="B37" s="9">
-        <v>46090.529563310185</v>
+        <v>46090.69622997685</v>
       </c>
       <c r="C37" s="9">
-        <v>46108.60141636574</v>
+        <v>46108.76808303241</v>
       </c>
       <c r="D37" s="9">
-        <v>46108.60143265047</v>
+        <v>46108.76809931713</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>143</v>
@@ -3507,13 +3507,13 @@
         <v>147</v>
       </c>
       <c r="B38" s="5">
-        <v>46090.52978670139</v>
+        <v>46090.69645336806</v>
       </c>
       <c r="C38" s="5">
-        <v>46198.39836409722</v>
+        <v>46198.565030763886</v>
       </c>
       <c r="D38" s="5">
-        <v>46198.398383125</v>
+        <v>46198.565049791665</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>148</v>
@@ -3572,13 +3572,13 @@
         <v>153</v>
       </c>
       <c r="B39" s="9">
-        <v>46073.4077505787</v>
+        <v>46073.57441724537</v>
       </c>
       <c r="C39" s="9">
-        <v>46111.63221431713</v>
+        <v>46111.7988809838</v>
       </c>
       <c r="D39" s="9">
-        <v>46111.63222694444</v>
+        <v>46111.79889361111</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>154</v>
@@ -3625,13 +3625,13 @@
         <v>156</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.40775079861</v>
+        <v>46073.57441746528</v>
       </c>
       <c r="C40" s="5">
-        <v>46111.63215450232</v>
+        <v>46111.79882116898</v>
       </c>
       <c r="D40" s="5">
-        <v>46111.63217065972</v>
+        <v>46111.798837326394</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>157</v>
@@ -3690,13 +3690,13 @@
         <v>161</v>
       </c>
       <c r="B41" s="9">
-        <v>46073.40775103009</v>
+        <v>46073.57441769676</v>
       </c>
       <c r="C41" s="9">
-        <v>46111.632198287036</v>
+        <v>46111.7988649537</v>
       </c>
       <c r="D41" s="9">
-        <v>46111.632214178244</v>
+        <v>46111.79888084491</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>162</v>
@@ -3755,13 +3755,13 @@
         <v>165</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.40775126158</v>
+        <v>46073.57441792824</v>
       </c>
       <c r="C42" s="5">
-        <v>46195.74522711805</v>
+        <v>46195.91189378472</v>
       </c>
       <c r="D42" s="5">
-        <v>46196.684344803245</v>
+        <v>46196.8510114699</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>166</v>
@@ -3804,13 +3804,13 @@
         <v>168</v>
       </c>
       <c r="B43" s="9">
-        <v>46073.407751493054</v>
+        <v>46073.574418159726</v>
       </c>
       <c r="C43" s="9">
-        <v>46107.56083722222</v>
+        <v>46107.72750388889</v>
       </c>
       <c r="D43" s="9">
-        <v>46196.684302152775</v>
+        <v>46196.850968819446</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>169</v>
@@ -3869,13 +3869,13 @@
         <v>173</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.40775171296</v>
+        <v>46073.574418379634</v>
       </c>
       <c r="C44" s="5">
-        <v>46146.39678314815</v>
+        <v>46146.563449814814</v>
       </c>
       <c r="D44" s="5">
-        <v>46195.74489944444</v>
+        <v>46195.911566111114</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>174</v>
@@ -3934,13 +3934,13 @@
         <v>177</v>
       </c>
       <c r="B45" s="9">
-        <v>46073.40775194444</v>
+        <v>46073.57441861111</v>
       </c>
       <c r="C45" s="9">
-        <v>46195.745206631946</v>
+        <v>46195.91187329861</v>
       </c>
       <c r="D45" s="9">
-        <v>46196.74385425926</v>
+        <v>46196.91052092593</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>178</v>
@@ -3999,13 +3999,13 @@
         <v>181</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.4077521875</v>
+        <v>46073.57441885417</v>
       </c>
       <c r="C46" s="5">
-        <v>46195.44041152778</v>
+        <v>46195.60707819444</v>
       </c>
       <c r="D46" s="5">
-        <v>46195.440423078704</v>
+        <v>46195.607089745376</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>154</v>
@@ -4052,13 +4052,13 @@
         <v>183</v>
       </c>
       <c r="B47" s="9">
-        <v>46073.40775005787</v>
+        <v>46073.574416724536</v>
       </c>
       <c r="C47" s="9">
-        <v>46127.48360153935</v>
+        <v>46127.65026820602</v>
       </c>
       <c r="D47" s="9">
-        <v>46127.48373905093</v>
+        <v>46127.65040571759</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>184</v>
@@ -4117,13 +4117,13 @@
         <v>186</v>
       </c>
       <c r="B48" s="5">
-        <v>46073.40775244213</v>
+        <v>46073.5744191088</v>
       </c>
       <c r="C48" s="5">
-        <v>46195.44039379629</v>
+        <v>46195.607060462964</v>
       </c>
       <c r="D48" s="5">
-        <v>46195.44041170139</v>
+        <v>46195.607078368055</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>187</v>
@@ -4182,13 +4182,13 @@
         <v>189</v>
       </c>
       <c r="B49" s="9">
-        <v>46073.40775033565</v>
+        <v>46073.57441700231</v>
       </c>
       <c r="C49" s="9">
-        <v>46122.48811438658</v>
+        <v>46122.654781053236</v>
       </c>
       <c r="D49" s="9">
-        <v>46122.488134652776</v>
+        <v>46122.65480131944</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>190</v>
@@ -4247,13 +4247,13 @@
         <v>192</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.40775060185</v>
+        <v>46073.57441726852</v>
       </c>
       <c r="C50" s="5">
-        <v>46205.32204649306</v>
+        <v>46205.48871315972</v>
       </c>
       <c r="D50" s="5">
-        <v>46205.3220575</v>
+        <v>46205.488724166666</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>193</v>
@@ -4300,13 +4300,13 @@
         <v>195</v>
       </c>
       <c r="B51" s="9">
-        <v>46073.407751192135</v>
+        <v>46073.57441785879</v>
       </c>
       <c r="C51" s="9">
-        <v>46197.33879725695</v>
+        <v>46197.50546392361</v>
       </c>
       <c r="D51" s="9">
-        <v>46197.3388141551</v>
+        <v>46197.50548082176</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>196</v>
@@ -4365,13 +4365,13 @@
         <v>198</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.4077514699</v>
+        <v>46073.57441813657</v>
       </c>
       <c r="C52" s="5">
-        <v>46197.338886412035</v>
+        <v>46197.50555307871</v>
       </c>
       <c r="D52" s="5">
-        <v>46197.338901423616</v>
+        <v>46197.50556809027</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>199</v>
@@ -4430,13 +4430,13 @@
         <v>202</v>
       </c>
       <c r="B53" s="9">
-        <v>46073.40775171296</v>
+        <v>46073.574418379634</v>
       </c>
       <c r="C53" s="9">
-        <v>46197.33890447917</v>
+        <v>46197.50557114583</v>
       </c>
       <c r="D53" s="9">
-        <v>46197.338922106486</v>
+        <v>46197.50558877314</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>203</v>
@@ -4495,13 +4495,13 @@
         <v>205</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.40775196759</v>
+        <v>46073.57441863426</v>
       </c>
       <c r="C54" s="5">
-        <v>46197.339196574074</v>
+        <v>46197.505863240745</v>
       </c>
       <c r="D54" s="5">
-        <v>46197.33921306713</v>
+        <v>46197.5058797338</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>206</v>
@@ -4560,13 +4560,13 @@
         <v>208</v>
       </c>
       <c r="B55" s="9">
-        <v>46073.40775226852</v>
+        <v>46073.57441893518</v>
       </c>
       <c r="C55" s="9">
-        <v>46197.3392925</v>
+        <v>46197.505959166665</v>
       </c>
       <c r="D55" s="9">
-        <v>46197.339310138894</v>
+        <v>46197.50597680555</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>151</v>
@@ -4623,13 +4623,13 @@
         <v>211</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.407752534724</v>
+        <v>46073.57441920139</v>
       </c>
       <c r="C56" s="5">
-        <v>46205.322026145834</v>
+        <v>46205.488692812505</v>
       </c>
       <c r="D56" s="5">
-        <v>46205.32204734954</v>
+        <v>46205.4887140162</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>212</v>
@@ -4686,11 +4686,11 @@
         <v>214</v>
       </c>
       <c r="B57" s="9">
-        <v>46073.40775020834</v>
+        <v>46073.574416874995</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46090.5351549537</v>
+        <v>46090.70182162037</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>215</v>
@@ -4733,11 +4733,11 @@
         <v>217</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.407750555554</v>
+        <v>46073.57441722222</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46205.32204747685</v>
+        <v>46205.48871414352</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>218</v>
@@ -4794,11 +4794,11 @@
         <v>224</v>
       </c>
       <c r="B59" s="9">
-        <v>46073.407750810184</v>
+        <v>46073.57441747685</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46107.99797167824</v>
+        <v>46108.16463834491</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>225</v>
@@ -4855,11 +4855,11 @@
         <v>227</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.40775108796</v>
+        <v>46073.57441775463</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46108.08432915509</v>
+        <v>46108.250995821756</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>228</v>
@@ -4918,11 +4918,11 @@
         <v>230</v>
       </c>
       <c r="B61" s="9">
-        <v>46073.40775134259</v>
+        <v>46073.57441800926</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46111.96357416667</v>
+        <v>46112.13024083333</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>231</v>
@@ -4981,11 +4981,11 @@
         <v>233</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.4077516088</v>
+        <v>46073.574418275464</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46090.53515497685</v>
+        <v>46090.70182164352</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>234</v>
@@ -5028,11 +5028,11 @@
         <v>236</v>
       </c>
       <c r="B63" s="9">
-        <v>46073.40775190972</v>
+        <v>46073.57441857639</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46121.00034344908</v>
+        <v>46121.167010115736</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>237</v>
@@ -5091,11 +5091,11 @@
         <v>240</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.407752175925</v>
+        <v>46073.57441884259</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46121.00034346065</v>
+        <v>46121.16701012732</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>241</v>

--- a/data/50001508 - XEMORTIZ STOCK.xlsx
+++ b/data/50001508 - XEMORTIZ STOCK.xlsx
@@ -4690,7 +4690,7 @@
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46090.70182162037</v>
+        <v>46205.89694466435</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>215</v>
@@ -4857,9 +4857,11 @@
       <c r="B60" s="5">
         <v>46073.57441775463</v>
       </c>
-      <c r="C60" s="6"/>
+      <c r="C60" s="5">
+        <v>46205.89693434028</v>
+      </c>
       <c r="D60" s="5">
-        <v>46108.250995821756</v>
+        <v>46205.90100083333</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>228</v>
@@ -4907,10 +4909,10 @@
         <v>93</v>
       </c>
       <c r="T60" s="6">
-        <v>0</v>
-      </c>
-      <c r="U60" s="11" t="s">
-        <v>94</v>
+        <v>1</v>
+      </c>
+      <c r="U60" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -4922,7 +4924,7 @@
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46112.13024083333</v>
+        <v>46205.89695172454</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>231</v>
@@ -4972,8 +4974,8 @@
       <c r="T61" s="10">
         <v>0</v>
       </c>
-      <c r="U61" s="11" t="s">
-        <v>94</v>
+      <c r="U61" s="12" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001508 - XEMORTIZ STOCK.xlsx
+++ b/data/50001508 - XEMORTIZ STOCK.xlsx
@@ -1407,13 +1407,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.574416574076</v>
+        <v>46073.407749907405</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.72097336805</v>
+        <v>46092.55430670139</v>
       </c>
       <c r="D4" s="5">
-        <v>46092.72098704861</v>
+        <v>46092.55432038194</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1460,13 +1460,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46073.57441700231</v>
+        <v>46073.40775033565</v>
       </c>
       <c r="C5" s="9">
-        <v>46092.72094241898</v>
+        <v>46092.554275752314</v>
       </c>
       <c r="D5" s="9">
-        <v>46092.72097376158</v>
+        <v>46092.554307094906</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1523,13 +1523,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.57441731481</v>
+        <v>46073.40775064815</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.72094300926</v>
+        <v>46092.55427634259</v>
       </c>
       <c r="D6" s="5">
-        <v>46133.88991541667</v>
+        <v>46133.72324875</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1586,13 +1586,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="9">
-        <v>46073.574417615746</v>
+        <v>46073.407750949074</v>
       </c>
       <c r="C7" s="9">
-        <v>46092.72094347222</v>
+        <v>46092.55427680556</v>
       </c>
       <c r="D7" s="9">
-        <v>46133.88996451389</v>
+        <v>46133.723297847224</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>39</v>
@@ -1649,13 +1649,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.574417951386</v>
+        <v>46073.40775128472</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.72094393519</v>
+        <v>46092.554277268515</v>
       </c>
       <c r="D8" s="5">
-        <v>46133.89120298611</v>
+        <v>46133.724536319445</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1712,13 +1712,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46073.57441825232</v>
+        <v>46073.40775158565</v>
       </c>
       <c r="C9" s="9">
-        <v>46092.72094480324</v>
+        <v>46092.55427813657</v>
       </c>
       <c r="D9" s="9">
-        <v>46133.891316608795</v>
+        <v>46133.72464994213</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -1775,13 +1775,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.57441959491</v>
+        <v>46073.40775292824</v>
       </c>
       <c r="C10" s="5">
-        <v>46114.51917579861</v>
+        <v>46114.352509131946</v>
       </c>
       <c r="D10" s="5">
-        <v>46139.53853695602</v>
+        <v>46139.37187028935</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -1824,13 +1824,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="9">
-        <v>46073.574417199074</v>
+        <v>46073.40775053241</v>
       </c>
       <c r="C11" s="9">
-        <v>46097.55113413194</v>
+        <v>46097.38446746528</v>
       </c>
       <c r="D11" s="9">
-        <v>46097.5511521875</v>
+        <v>46097.38448552083</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -1889,13 +1889,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.57441784722</v>
+        <v>46073.40775118055</v>
       </c>
       <c r="C12" s="5">
-        <v>46114.51896107639</v>
+        <v>46114.35229440972</v>
       </c>
       <c r="D12" s="5">
-        <v>46133.8973671412</v>
+        <v>46133.73070047454</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -1954,13 +1954,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="9">
-        <v>46073.57441811342</v>
+        <v>46073.407751446764</v>
       </c>
       <c r="C13" s="9">
-        <v>46097.55146753472</v>
+        <v>46097.38480086805</v>
       </c>
       <c r="D13" s="9">
-        <v>46097.551481574075</v>
+        <v>46097.384814907404</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>58</v>
@@ -2019,13 +2019,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.57441840278</v>
+        <v>46073.407751736115</v>
       </c>
       <c r="C14" s="5">
-        <v>46134.60713581018</v>
+        <v>46134.44046914352</v>
       </c>
       <c r="D14" s="5">
-        <v>46134.60713701389</v>
+        <v>46134.440470347225</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2084,13 +2084,13 @@
         <v>62</v>
       </c>
       <c r="B15" s="9">
-        <v>46073.574418668984</v>
+        <v>46073.40775200231</v>
       </c>
       <c r="C15" s="9">
-        <v>46114.52188712963</v>
+        <v>46114.35522046297</v>
       </c>
       <c r="D15" s="9">
-        <v>46114.521897847226</v>
+        <v>46114.355231180554</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>63</v>
@@ -2137,13 +2137,13 @@
         <v>65</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.574418958335</v>
+        <v>46073.40775229166</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.52184375</v>
+        <v>46114.35517708333</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.522016944444</v>
+        <v>46114.35535027778</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>66</v>
@@ -2202,13 +2202,13 @@
         <v>68</v>
       </c>
       <c r="B17" s="9">
-        <v>46073.574419791665</v>
+        <v>46073.407753125</v>
       </c>
       <c r="C17" s="9">
-        <v>46114.52187152777</v>
+        <v>46114.35520486112</v>
       </c>
       <c r="D17" s="9">
-        <v>46133.89260450231</v>
+        <v>46133.72593783565</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>69</v>
@@ -2267,13 +2267,13 @@
         <v>73</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.574419236116</v>
+        <v>46073.407752569445</v>
       </c>
       <c r="C18" s="5">
-        <v>46097.55117878472</v>
+        <v>46097.38451211806</v>
       </c>
       <c r="D18" s="5">
-        <v>46133.896346724534</v>
+        <v>46133.72968005787</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>74</v>
@@ -2332,13 +2332,13 @@
         <v>77</v>
       </c>
       <c r="B19" s="9">
-        <v>46073.5744165162</v>
+        <v>46073.40774984953</v>
       </c>
       <c r="C19" s="9">
-        <v>46097.55150556713</v>
+        <v>46097.38483890046</v>
       </c>
       <c r="D19" s="9">
-        <v>46100.785884259254</v>
+        <v>46100.6192175926</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>78</v>
@@ -2397,13 +2397,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.57441688658</v>
+        <v>46073.40775021991</v>
       </c>
       <c r="C20" s="5">
-        <v>46134.60708307871</v>
+        <v>46134.440416412035</v>
       </c>
       <c r="D20" s="5">
-        <v>46134.60710188658</v>
+        <v>46134.440435219905</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2450,13 +2450,13 @@
         <v>85</v>
       </c>
       <c r="B21" s="9">
-        <v>46073.57441755787</v>
+        <v>46073.4077508912</v>
       </c>
       <c r="C21" s="9">
-        <v>46114.781065034724</v>
+        <v>46114.61439836805</v>
       </c>
       <c r="D21" s="9">
-        <v>46133.89220711806</v>
+        <v>46133.725540451385</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>86</v>
@@ -2515,13 +2515,13 @@
         <v>90</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.57441785879</v>
+        <v>46073.407751192135</v>
       </c>
       <c r="C22" s="5">
-        <v>46114.78100798611</v>
+        <v>46114.614341319444</v>
       </c>
       <c r="D22" s="5">
-        <v>46114.78100939815</v>
+        <v>46114.61434273148</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -2576,13 +2576,13 @@
         <v>95</v>
       </c>
       <c r="B23" s="9">
-        <v>46073.57441814815</v>
+        <v>46073.407751481485</v>
       </c>
       <c r="C23" s="9">
-        <v>46114.78104996528</v>
+        <v>46114.61438329861</v>
       </c>
       <c r="D23" s="9">
-        <v>46114.78105144676</v>
+        <v>46114.61438478009</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>96</v>
@@ -2637,13 +2637,13 @@
         <v>98</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.57441936343</v>
+        <v>46073.40775269676</v>
       </c>
       <c r="C24" s="5">
-        <v>46133.89757971065</v>
+        <v>46133.73091304398</v>
       </c>
       <c r="D24" s="5">
-        <v>46133.8975922338</v>
+        <v>46133.73092556713</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>99</v>
@@ -2702,13 +2702,13 @@
         <v>101</v>
       </c>
       <c r="B25" s="9">
-        <v>46073.57441965278</v>
+        <v>46073.40775298611</v>
       </c>
       <c r="C25" s="9">
-        <v>46122.7044230787</v>
+        <v>46122.537756412035</v>
       </c>
       <c r="D25" s="9">
-        <v>46122.70442476852</v>
+        <v>46122.537758101855</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>102</v>
@@ -2763,13 +2763,13 @@
         <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.574416469906</v>
+        <v>46073.40774980324</v>
       </c>
       <c r="C26" s="5">
-        <v>46133.897566134256</v>
+        <v>46133.73089946759</v>
       </c>
       <c r="D26" s="5">
-        <v>46133.897567673615</v>
+        <v>46133.730901006944</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -2824,13 +2824,13 @@
         <v>107</v>
       </c>
       <c r="B27" s="9">
-        <v>46073.574416840274</v>
+        <v>46073.40775017361</v>
       </c>
       <c r="C27" s="9">
-        <v>46097.55136633102</v>
+        <v>46097.384699664355</v>
       </c>
       <c r="D27" s="9">
-        <v>46097.55137980324</v>
+        <v>46097.38471313658</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>108</v>
@@ -2889,13 +2889,13 @@
         <v>110</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.574417129625</v>
+        <v>46073.40775046297</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.551280127314</v>
+        <v>46097.38461346064</v>
       </c>
       <c r="D28" s="5">
-        <v>46097.55128159722</v>
+        <v>46097.38461493056</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>111</v>
@@ -2950,13 +2950,13 @@
         <v>113</v>
       </c>
       <c r="B29" s="9">
-        <v>46073.57441739584</v>
+        <v>46073.407750729166</v>
       </c>
       <c r="C29" s="9">
-        <v>46097.55131481482</v>
+        <v>46097.384648148145</v>
       </c>
       <c r="D29" s="9">
-        <v>46097.55131616898</v>
+        <v>46097.38464950232</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>114</v>
@@ -3011,13 +3011,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.57441769676</v>
+        <v>46073.40775103009</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.55135113426</v>
+        <v>46097.38468446759</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.55135262731</v>
+        <v>46097.38468596065</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>117</v>
@@ -3072,13 +3072,13 @@
         <v>119</v>
       </c>
       <c r="B31" s="9">
-        <v>46073.574417951386</v>
+        <v>46073.40775128472</v>
       </c>
       <c r="C31" s="9">
-        <v>46111.79875103009</v>
+        <v>46111.63208436343</v>
       </c>
       <c r="D31" s="9">
-        <v>46111.79876402778</v>
+        <v>46111.632097361115</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>120</v>
@@ -3137,13 +3137,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.57441821759</v>
+        <v>46073.40775155093</v>
       </c>
       <c r="C32" s="5">
-        <v>46097.551927002314</v>
+        <v>46097.38526033565</v>
       </c>
       <c r="D32" s="5">
-        <v>46097.551928483794</v>
+        <v>46097.38526181713</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3198,13 +3198,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="9">
-        <v>46073.57441847222</v>
+        <v>46073.40775180556</v>
       </c>
       <c r="C33" s="9">
-        <v>46111.798736655095</v>
+        <v>46111.63206998842</v>
       </c>
       <c r="D33" s="9">
-        <v>46111.798738171296</v>
+        <v>46111.63207150463</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>128</v>
@@ -3259,13 +3259,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.574418749995</v>
+        <v>46073.40775208334</v>
       </c>
       <c r="C34" s="5">
-        <v>46198.565049375</v>
+        <v>46198.39838270833</v>
       </c>
       <c r="D34" s="5">
-        <v>46198.565061875</v>
+        <v>46198.398395208336</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3312,13 +3312,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="9">
-        <v>46073.57441901621</v>
+        <v>46073.407752349536</v>
       </c>
       <c r="C35" s="9">
-        <v>46108.76774940972</v>
+        <v>46108.60108274306</v>
       </c>
       <c r="D35" s="9">
-        <v>46197.70911202546</v>
+        <v>46197.54244535879</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>134</v>
@@ -3377,13 +3377,13 @@
         <v>138</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.57441695602</v>
+        <v>46073.40775028935</v>
       </c>
       <c r="C36" s="5">
-        <v>46108.76784886574</v>
+        <v>46108.60118219907</v>
       </c>
       <c r="D36" s="5">
-        <v>46197.70914525463</v>
+        <v>46197.54247858796</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>139</v>
@@ -3442,13 +3442,13 @@
         <v>142</v>
       </c>
       <c r="B37" s="9">
-        <v>46090.69622997685</v>
+        <v>46090.529563310185</v>
       </c>
       <c r="C37" s="9">
-        <v>46108.76808303241</v>
+        <v>46108.60141636574</v>
       </c>
       <c r="D37" s="9">
-        <v>46108.76809931713</v>
+        <v>46108.60143265047</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>143</v>
@@ -3507,13 +3507,13 @@
         <v>147</v>
       </c>
       <c r="B38" s="5">
-        <v>46090.69645336806</v>
+        <v>46090.52978670139</v>
       </c>
       <c r="C38" s="5">
-        <v>46198.565030763886</v>
+        <v>46198.39836409722</v>
       </c>
       <c r="D38" s="5">
-        <v>46198.565049791665</v>
+        <v>46198.398383125</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>148</v>
@@ -3572,13 +3572,13 @@
         <v>153</v>
       </c>
       <c r="B39" s="9">
-        <v>46073.57441724537</v>
+        <v>46073.4077505787</v>
       </c>
       <c r="C39" s="9">
-        <v>46111.7988809838</v>
+        <v>46111.63221431713</v>
       </c>
       <c r="D39" s="9">
-        <v>46111.79889361111</v>
+        <v>46111.63222694444</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>154</v>
@@ -3625,13 +3625,13 @@
         <v>156</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.57441746528</v>
+        <v>46073.40775079861</v>
       </c>
       <c r="C40" s="5">
-        <v>46111.79882116898</v>
+        <v>46111.63215450232</v>
       </c>
       <c r="D40" s="5">
-        <v>46111.798837326394</v>
+        <v>46111.63217065972</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>157</v>
@@ -3690,13 +3690,13 @@
         <v>161</v>
       </c>
       <c r="B41" s="9">
-        <v>46073.57441769676</v>
+        <v>46073.40775103009</v>
       </c>
       <c r="C41" s="9">
-        <v>46111.7988649537</v>
+        <v>46111.632198287036</v>
       </c>
       <c r="D41" s="9">
-        <v>46111.79888084491</v>
+        <v>46111.632214178244</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>162</v>
@@ -3755,13 +3755,13 @@
         <v>165</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.57441792824</v>
+        <v>46073.40775126158</v>
       </c>
       <c r="C42" s="5">
-        <v>46195.91189378472</v>
+        <v>46195.74522711805</v>
       </c>
       <c r="D42" s="5">
-        <v>46196.8510114699</v>
+        <v>46196.684344803245</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>166</v>
@@ -3804,13 +3804,13 @@
         <v>168</v>
       </c>
       <c r="B43" s="9">
-        <v>46073.574418159726</v>
+        <v>46073.407751493054</v>
       </c>
       <c r="C43" s="9">
-        <v>46107.72750388889</v>
+        <v>46107.56083722222</v>
       </c>
       <c r="D43" s="9">
-        <v>46196.850968819446</v>
+        <v>46196.684302152775</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>169</v>
@@ -3869,13 +3869,13 @@
         <v>173</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.574418379634</v>
+        <v>46073.40775171296</v>
       </c>
       <c r="C44" s="5">
-        <v>46146.563449814814</v>
+        <v>46146.39678314815</v>
       </c>
       <c r="D44" s="5">
-        <v>46195.911566111114</v>
+        <v>46195.74489944444</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>174</v>
@@ -3934,13 +3934,13 @@
         <v>177</v>
       </c>
       <c r="B45" s="9">
-        <v>46073.57441861111</v>
+        <v>46073.40775194444</v>
       </c>
       <c r="C45" s="9">
-        <v>46195.91187329861</v>
+        <v>46195.745206631946</v>
       </c>
       <c r="D45" s="9">
-        <v>46196.91052092593</v>
+        <v>46196.74385425926</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>178</v>
@@ -3999,13 +3999,13 @@
         <v>181</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.57441885417</v>
+        <v>46073.4077521875</v>
       </c>
       <c r="C46" s="5">
-        <v>46195.60707819444</v>
+        <v>46195.44041152778</v>
       </c>
       <c r="D46" s="5">
-        <v>46195.607089745376</v>
+        <v>46195.440423078704</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>154</v>
@@ -4052,13 +4052,13 @@
         <v>183</v>
       </c>
       <c r="B47" s="9">
-        <v>46073.574416724536</v>
+        <v>46073.40775005787</v>
       </c>
       <c r="C47" s="9">
-        <v>46127.65026820602</v>
+        <v>46127.48360153935</v>
       </c>
       <c r="D47" s="9">
-        <v>46127.65040571759</v>
+        <v>46127.48373905093</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>184</v>
@@ -4117,13 +4117,13 @@
         <v>186</v>
       </c>
       <c r="B48" s="5">
-        <v>46073.5744191088</v>
+        <v>46073.40775244213</v>
       </c>
       <c r="C48" s="5">
-        <v>46195.607060462964</v>
+        <v>46195.44039379629</v>
       </c>
       <c r="D48" s="5">
-        <v>46195.607078368055</v>
+        <v>46195.44041170139</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>187</v>
@@ -4182,13 +4182,13 @@
         <v>189</v>
       </c>
       <c r="B49" s="9">
-        <v>46073.57441700231</v>
+        <v>46073.40775033565</v>
       </c>
       <c r="C49" s="9">
-        <v>46122.654781053236</v>
+        <v>46122.48811438658</v>
       </c>
       <c r="D49" s="9">
-        <v>46122.65480131944</v>
+        <v>46122.488134652776</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>190</v>
@@ -4247,13 +4247,13 @@
         <v>192</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.57441726852</v>
+        <v>46073.40775060185</v>
       </c>
       <c r="C50" s="5">
-        <v>46205.48871315972</v>
+        <v>46205.32204649306</v>
       </c>
       <c r="D50" s="5">
-        <v>46205.488724166666</v>
+        <v>46205.3220575</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>193</v>
@@ -4300,13 +4300,13 @@
         <v>195</v>
       </c>
       <c r="B51" s="9">
-        <v>46073.57441785879</v>
+        <v>46073.407751192135</v>
       </c>
       <c r="C51" s="9">
-        <v>46197.50546392361</v>
+        <v>46197.33879725695</v>
       </c>
       <c r="D51" s="9">
-        <v>46197.50548082176</v>
+        <v>46197.3388141551</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>196</v>
@@ -4365,13 +4365,13 @@
         <v>198</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.57441813657</v>
+        <v>46073.4077514699</v>
       </c>
       <c r="C52" s="5">
-        <v>46197.50555307871</v>
+        <v>46197.338886412035</v>
       </c>
       <c r="D52" s="5">
-        <v>46197.50556809027</v>
+        <v>46197.338901423616</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>199</v>
@@ -4430,13 +4430,13 @@
         <v>202</v>
       </c>
       <c r="B53" s="9">
-        <v>46073.574418379634</v>
+        <v>46073.40775171296</v>
       </c>
       <c r="C53" s="9">
-        <v>46197.50557114583</v>
+        <v>46197.33890447917</v>
       </c>
       <c r="D53" s="9">
-        <v>46197.50558877314</v>
+        <v>46197.338922106486</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>203</v>
@@ -4495,13 +4495,13 @@
         <v>205</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.57441863426</v>
+        <v>46073.40775196759</v>
       </c>
       <c r="C54" s="5">
-        <v>46197.505863240745</v>
+        <v>46197.339196574074</v>
       </c>
       <c r="D54" s="5">
-        <v>46197.5058797338</v>
+        <v>46197.33921306713</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>206</v>
@@ -4560,13 +4560,13 @@
         <v>208</v>
       </c>
       <c r="B55" s="9">
-        <v>46073.57441893518</v>
+        <v>46073.40775226852</v>
       </c>
       <c r="C55" s="9">
-        <v>46197.505959166665</v>
+        <v>46197.3392925</v>
       </c>
       <c r="D55" s="9">
-        <v>46197.50597680555</v>
+        <v>46197.339310138894</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>151</v>
@@ -4623,13 +4623,13 @@
         <v>211</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.57441920139</v>
+        <v>46073.407752534724</v>
       </c>
       <c r="C56" s="5">
-        <v>46205.488692812505</v>
+        <v>46205.322026145834</v>
       </c>
       <c r="D56" s="5">
-        <v>46205.4887140162</v>
+        <v>46205.32204734954</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>212</v>
@@ -4686,11 +4686,11 @@
         <v>214</v>
       </c>
       <c r="B57" s="9">
-        <v>46073.574416874995</v>
+        <v>46073.40775020834</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46205.89694466435</v>
+        <v>46205.73027799769</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>215</v>
@@ -4733,11 +4733,11 @@
         <v>217</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.57441722222</v>
+        <v>46073.407750555554</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46205.48871414352</v>
+        <v>46205.32204747685</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>218</v>
@@ -4794,11 +4794,11 @@
         <v>224</v>
       </c>
       <c r="B59" s="9">
-        <v>46073.57441747685</v>
+        <v>46073.407750810184</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46108.16463834491</v>
+        <v>46107.99797167824</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>225</v>
@@ -4855,13 +4855,13 @@
         <v>227</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.57441775463</v>
+        <v>46073.40775108796</v>
       </c>
       <c r="C60" s="5">
-        <v>46205.89693434028</v>
+        <v>46205.730267673614</v>
       </c>
       <c r="D60" s="5">
-        <v>46205.90100083333</v>
+        <v>46205.73433416667</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>228</v>
@@ -4920,11 +4920,11 @@
         <v>230</v>
       </c>
       <c r="B61" s="9">
-        <v>46073.57441800926</v>
+        <v>46073.40775134259</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46205.89695172454</v>
+        <v>46205.73028505787</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>231</v>
@@ -4983,11 +4983,11 @@
         <v>233</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.574418275464</v>
+        <v>46073.4077516088</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46090.70182164352</v>
+        <v>46090.53515497685</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>234</v>
@@ -5030,11 +5030,11 @@
         <v>236</v>
       </c>
       <c r="B63" s="9">
-        <v>46073.57441857639</v>
+        <v>46073.40775190972</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46121.167010115736</v>
+        <v>46121.00034344908</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>237</v>
@@ -5093,11 +5093,11 @@
         <v>240</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.57441884259</v>
+        <v>46073.407752175925</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46121.16701012732</v>
+        <v>46121.00034346065</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>241</v>

--- a/data/50001508 - XEMORTIZ STOCK.xlsx
+++ b/data/50001508 - XEMORTIZ STOCK.xlsx
@@ -1407,13 +1407,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.407749907405</v>
+        <v>46073.574416574076</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55430670139</v>
+        <v>46092.72097336805</v>
       </c>
       <c r="D4" s="5">
-        <v>46092.55432038194</v>
+        <v>46092.72098704861</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1460,13 +1460,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46073.40775033565</v>
+        <v>46073.57441700231</v>
       </c>
       <c r="C5" s="9">
-        <v>46092.554275752314</v>
+        <v>46092.72094241898</v>
       </c>
       <c r="D5" s="9">
-        <v>46092.554307094906</v>
+        <v>46092.72097376158</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1523,13 +1523,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.40775064815</v>
+        <v>46073.57441731481</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55427634259</v>
+        <v>46092.72094300926</v>
       </c>
       <c r="D6" s="5">
-        <v>46133.72324875</v>
+        <v>46133.88991541667</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1586,13 +1586,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="9">
-        <v>46073.407750949074</v>
+        <v>46073.574417615746</v>
       </c>
       <c r="C7" s="9">
-        <v>46092.55427680556</v>
+        <v>46092.72094347222</v>
       </c>
       <c r="D7" s="9">
-        <v>46133.723297847224</v>
+        <v>46133.88996451389</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>39</v>
@@ -1649,13 +1649,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.40775128472</v>
+        <v>46073.574417951386</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.554277268515</v>
+        <v>46092.72094393519</v>
       </c>
       <c r="D8" s="5">
-        <v>46133.724536319445</v>
+        <v>46133.89120298611</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1712,13 +1712,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46073.40775158565</v>
+        <v>46073.57441825232</v>
       </c>
       <c r="C9" s="9">
-        <v>46092.55427813657</v>
+        <v>46092.72094480324</v>
       </c>
       <c r="D9" s="9">
-        <v>46133.72464994213</v>
+        <v>46133.891316608795</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -1775,13 +1775,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.40775292824</v>
+        <v>46073.57441959491</v>
       </c>
       <c r="C10" s="5">
-        <v>46114.352509131946</v>
+        <v>46114.51917579861</v>
       </c>
       <c r="D10" s="5">
-        <v>46139.37187028935</v>
+        <v>46139.53853695602</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -1824,13 +1824,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="9">
-        <v>46073.40775053241</v>
+        <v>46073.574417199074</v>
       </c>
       <c r="C11" s="9">
-        <v>46097.38446746528</v>
+        <v>46097.55113413194</v>
       </c>
       <c r="D11" s="9">
-        <v>46097.38448552083</v>
+        <v>46097.5511521875</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -1889,13 +1889,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.40775118055</v>
+        <v>46073.57441784722</v>
       </c>
       <c r="C12" s="5">
-        <v>46114.35229440972</v>
+        <v>46114.51896107639</v>
       </c>
       <c r="D12" s="5">
-        <v>46133.73070047454</v>
+        <v>46133.8973671412</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -1954,13 +1954,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="9">
-        <v>46073.407751446764</v>
+        <v>46073.57441811342</v>
       </c>
       <c r="C13" s="9">
-        <v>46097.38480086805</v>
+        <v>46097.55146753472</v>
       </c>
       <c r="D13" s="9">
-        <v>46097.384814907404</v>
+        <v>46097.551481574075</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>58</v>
@@ -2019,13 +2019,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.407751736115</v>
+        <v>46073.57441840278</v>
       </c>
       <c r="C14" s="5">
-        <v>46134.44046914352</v>
+        <v>46134.60713581018</v>
       </c>
       <c r="D14" s="5">
-        <v>46134.440470347225</v>
+        <v>46134.60713701389</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2084,13 +2084,13 @@
         <v>62</v>
       </c>
       <c r="B15" s="9">
-        <v>46073.40775200231</v>
+        <v>46073.574418668984</v>
       </c>
       <c r="C15" s="9">
-        <v>46114.35522046297</v>
+        <v>46114.52188712963</v>
       </c>
       <c r="D15" s="9">
-        <v>46114.355231180554</v>
+        <v>46114.521897847226</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>63</v>
@@ -2137,13 +2137,13 @@
         <v>65</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.40775229166</v>
+        <v>46073.574418958335</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.35517708333</v>
+        <v>46114.52184375</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.35535027778</v>
+        <v>46114.522016944444</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>66</v>
@@ -2202,13 +2202,13 @@
         <v>68</v>
       </c>
       <c r="B17" s="9">
-        <v>46073.407753125</v>
+        <v>46073.574419791665</v>
       </c>
       <c r="C17" s="9">
-        <v>46114.35520486112</v>
+        <v>46114.52187152777</v>
       </c>
       <c r="D17" s="9">
-        <v>46133.72593783565</v>
+        <v>46133.89260450231</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>69</v>
@@ -2267,13 +2267,13 @@
         <v>73</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.407752569445</v>
+        <v>46073.574419236116</v>
       </c>
       <c r="C18" s="5">
-        <v>46097.38451211806</v>
+        <v>46097.55117878472</v>
       </c>
       <c r="D18" s="5">
-        <v>46133.72968005787</v>
+        <v>46133.896346724534</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>74</v>
@@ -2332,13 +2332,13 @@
         <v>77</v>
       </c>
       <c r="B19" s="9">
-        <v>46073.40774984953</v>
+        <v>46073.5744165162</v>
       </c>
       <c r="C19" s="9">
-        <v>46097.38483890046</v>
+        <v>46097.55150556713</v>
       </c>
       <c r="D19" s="9">
-        <v>46100.6192175926</v>
+        <v>46100.785884259254</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>78</v>
@@ -2397,13 +2397,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.40775021991</v>
+        <v>46073.57441688658</v>
       </c>
       <c r="C20" s="5">
-        <v>46134.440416412035</v>
+        <v>46134.60708307871</v>
       </c>
       <c r="D20" s="5">
-        <v>46134.440435219905</v>
+        <v>46134.60710188658</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2450,13 +2450,13 @@
         <v>85</v>
       </c>
       <c r="B21" s="9">
-        <v>46073.4077508912</v>
+        <v>46073.57441755787</v>
       </c>
       <c r="C21" s="9">
-        <v>46114.61439836805</v>
+        <v>46114.781065034724</v>
       </c>
       <c r="D21" s="9">
-        <v>46133.725540451385</v>
+        <v>46133.89220711806</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>86</v>
@@ -2515,13 +2515,13 @@
         <v>90</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.407751192135</v>
+        <v>46073.57441785879</v>
       </c>
       <c r="C22" s="5">
-        <v>46114.614341319444</v>
+        <v>46114.78100798611</v>
       </c>
       <c r="D22" s="5">
-        <v>46114.61434273148</v>
+        <v>46114.78100939815</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -2576,13 +2576,13 @@
         <v>95</v>
       </c>
       <c r="B23" s="9">
-        <v>46073.407751481485</v>
+        <v>46073.57441814815</v>
       </c>
       <c r="C23" s="9">
-        <v>46114.61438329861</v>
+        <v>46114.78104996528</v>
       </c>
       <c r="D23" s="9">
-        <v>46114.61438478009</v>
+        <v>46114.78105144676</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>96</v>
@@ -2637,13 +2637,13 @@
         <v>98</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.40775269676</v>
+        <v>46073.57441936343</v>
       </c>
       <c r="C24" s="5">
-        <v>46133.73091304398</v>
+        <v>46133.89757971065</v>
       </c>
       <c r="D24" s="5">
-        <v>46133.73092556713</v>
+        <v>46133.8975922338</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>99</v>
@@ -2702,13 +2702,13 @@
         <v>101</v>
       </c>
       <c r="B25" s="9">
-        <v>46073.40775298611</v>
+        <v>46073.57441965278</v>
       </c>
       <c r="C25" s="9">
-        <v>46122.537756412035</v>
+        <v>46122.7044230787</v>
       </c>
       <c r="D25" s="9">
-        <v>46122.537758101855</v>
+        <v>46122.70442476852</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>102</v>
@@ -2763,13 +2763,13 @@
         <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.40774980324</v>
+        <v>46073.574416469906</v>
       </c>
       <c r="C26" s="5">
-        <v>46133.73089946759</v>
+        <v>46133.897566134256</v>
       </c>
       <c r="D26" s="5">
-        <v>46133.730901006944</v>
+        <v>46133.897567673615</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -2824,13 +2824,13 @@
         <v>107</v>
       </c>
       <c r="B27" s="9">
-        <v>46073.40775017361</v>
+        <v>46073.574416840274</v>
       </c>
       <c r="C27" s="9">
-        <v>46097.384699664355</v>
+        <v>46097.55136633102</v>
       </c>
       <c r="D27" s="9">
-        <v>46097.38471313658</v>
+        <v>46097.55137980324</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>108</v>
@@ -2889,13 +2889,13 @@
         <v>110</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.40775046297</v>
+        <v>46073.574417129625</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.38461346064</v>
+        <v>46097.551280127314</v>
       </c>
       <c r="D28" s="5">
-        <v>46097.38461493056</v>
+        <v>46097.55128159722</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>111</v>
@@ -2950,13 +2950,13 @@
         <v>113</v>
       </c>
       <c r="B29" s="9">
-        <v>46073.407750729166</v>
+        <v>46073.57441739584</v>
       </c>
       <c r="C29" s="9">
-        <v>46097.384648148145</v>
+        <v>46097.55131481482</v>
       </c>
       <c r="D29" s="9">
-        <v>46097.38464950232</v>
+        <v>46097.55131616898</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>114</v>
@@ -3011,13 +3011,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.40775103009</v>
+        <v>46073.57441769676</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.38468446759</v>
+        <v>46097.55135113426</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.38468596065</v>
+        <v>46097.55135262731</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>117</v>
@@ -3072,13 +3072,13 @@
         <v>119</v>
       </c>
       <c r="B31" s="9">
-        <v>46073.40775128472</v>
+        <v>46073.574417951386</v>
       </c>
       <c r="C31" s="9">
-        <v>46111.63208436343</v>
+        <v>46111.79875103009</v>
       </c>
       <c r="D31" s="9">
-        <v>46111.632097361115</v>
+        <v>46111.79876402778</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>120</v>
@@ -3137,13 +3137,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.40775155093</v>
+        <v>46073.57441821759</v>
       </c>
       <c r="C32" s="5">
-        <v>46097.38526033565</v>
+        <v>46097.551927002314</v>
       </c>
       <c r="D32" s="5">
-        <v>46097.38526181713</v>
+        <v>46097.551928483794</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3198,13 +3198,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="9">
-        <v>46073.40775180556</v>
+        <v>46073.57441847222</v>
       </c>
       <c r="C33" s="9">
-        <v>46111.63206998842</v>
+        <v>46111.798736655095</v>
       </c>
       <c r="D33" s="9">
-        <v>46111.63207150463</v>
+        <v>46111.798738171296</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>128</v>
@@ -3259,13 +3259,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.40775208334</v>
+        <v>46073.574418749995</v>
       </c>
       <c r="C34" s="5">
-        <v>46198.39838270833</v>
+        <v>46198.565049375</v>
       </c>
       <c r="D34" s="5">
-        <v>46198.398395208336</v>
+        <v>46198.565061875</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3312,13 +3312,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="9">
-        <v>46073.407752349536</v>
+        <v>46073.57441901621</v>
       </c>
       <c r="C35" s="9">
-        <v>46108.60108274306</v>
+        <v>46108.76774940972</v>
       </c>
       <c r="D35" s="9">
-        <v>46197.54244535879</v>
+        <v>46197.70911202546</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>134</v>
@@ -3377,13 +3377,13 @@
         <v>138</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.40775028935</v>
+        <v>46073.57441695602</v>
       </c>
       <c r="C36" s="5">
-        <v>46108.60118219907</v>
+        <v>46108.76784886574</v>
       </c>
       <c r="D36" s="5">
-        <v>46197.54247858796</v>
+        <v>46197.70914525463</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>139</v>
@@ -3442,13 +3442,13 @@
         <v>142</v>
       </c>
       <c r="B37" s="9">
-        <v>46090.529563310185</v>
+        <v>46090.69622997685</v>
       </c>
       <c r="C37" s="9">
-        <v>46108.60141636574</v>
+        <v>46108.76808303241</v>
       </c>
       <c r="D37" s="9">
-        <v>46108.60143265047</v>
+        <v>46108.76809931713</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>143</v>
@@ -3507,13 +3507,13 @@
         <v>147</v>
       </c>
       <c r="B38" s="5">
-        <v>46090.52978670139</v>
+        <v>46090.69645336806</v>
       </c>
       <c r="C38" s="5">
-        <v>46198.39836409722</v>
+        <v>46198.565030763886</v>
       </c>
       <c r="D38" s="5">
-        <v>46198.398383125</v>
+        <v>46198.565049791665</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>148</v>
@@ -3572,13 +3572,13 @@
         <v>153</v>
       </c>
       <c r="B39" s="9">
-        <v>46073.4077505787</v>
+        <v>46073.57441724537</v>
       </c>
       <c r="C39" s="9">
-        <v>46111.63221431713</v>
+        <v>46111.7988809838</v>
       </c>
       <c r="D39" s="9">
-        <v>46111.63222694444</v>
+        <v>46111.79889361111</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>154</v>
@@ -3625,13 +3625,13 @@
         <v>156</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.40775079861</v>
+        <v>46073.57441746528</v>
       </c>
       <c r="C40" s="5">
-        <v>46111.63215450232</v>
+        <v>46111.79882116898</v>
       </c>
       <c r="D40" s="5">
-        <v>46111.63217065972</v>
+        <v>46111.798837326394</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>157</v>
@@ -3690,13 +3690,13 @@
         <v>161</v>
       </c>
       <c r="B41" s="9">
-        <v>46073.40775103009</v>
+        <v>46073.57441769676</v>
       </c>
       <c r="C41" s="9">
-        <v>46111.632198287036</v>
+        <v>46111.7988649537</v>
       </c>
       <c r="D41" s="9">
-        <v>46111.632214178244</v>
+        <v>46111.79888084491</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>162</v>
@@ -3755,13 +3755,13 @@
         <v>165</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.40775126158</v>
+        <v>46073.57441792824</v>
       </c>
       <c r="C42" s="5">
-        <v>46195.74522711805</v>
+        <v>46195.91189378472</v>
       </c>
       <c r="D42" s="5">
-        <v>46196.684344803245</v>
+        <v>46196.8510114699</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>166</v>
@@ -3804,13 +3804,13 @@
         <v>168</v>
       </c>
       <c r="B43" s="9">
-        <v>46073.407751493054</v>
+        <v>46073.574418159726</v>
       </c>
       <c r="C43" s="9">
-        <v>46107.56083722222</v>
+        <v>46107.72750388889</v>
       </c>
       <c r="D43" s="9">
-        <v>46196.684302152775</v>
+        <v>46196.850968819446</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>169</v>
@@ -3869,13 +3869,13 @@
         <v>173</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.40775171296</v>
+        <v>46073.574418379634</v>
       </c>
       <c r="C44" s="5">
-        <v>46146.39678314815</v>
+        <v>46146.563449814814</v>
       </c>
       <c r="D44" s="5">
-        <v>46195.74489944444</v>
+        <v>46195.911566111114</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>174</v>
@@ -3934,13 +3934,13 @@
         <v>177</v>
       </c>
       <c r="B45" s="9">
-        <v>46073.40775194444</v>
+        <v>46073.57441861111</v>
       </c>
       <c r="C45" s="9">
-        <v>46195.745206631946</v>
+        <v>46195.91187329861</v>
       </c>
       <c r="D45" s="9">
-        <v>46196.74385425926</v>
+        <v>46196.91052092593</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>178</v>
@@ -3999,13 +3999,13 @@
         <v>181</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.4077521875</v>
+        <v>46073.57441885417</v>
       </c>
       <c r="C46" s="5">
-        <v>46195.44041152778</v>
+        <v>46195.60707819444</v>
       </c>
       <c r="D46" s="5">
-        <v>46195.440423078704</v>
+        <v>46195.607089745376</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>154</v>
@@ -4052,13 +4052,13 @@
         <v>183</v>
       </c>
       <c r="B47" s="9">
-        <v>46073.40775005787</v>
+        <v>46073.574416724536</v>
       </c>
       <c r="C47" s="9">
-        <v>46127.48360153935</v>
+        <v>46127.65026820602</v>
       </c>
       <c r="D47" s="9">
-        <v>46127.48373905093</v>
+        <v>46127.65040571759</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>184</v>
@@ -4117,13 +4117,13 @@
         <v>186</v>
       </c>
       <c r="B48" s="5">
-        <v>46073.40775244213</v>
+        <v>46073.5744191088</v>
       </c>
       <c r="C48" s="5">
-        <v>46195.44039379629</v>
+        <v>46195.607060462964</v>
       </c>
       <c r="D48" s="5">
-        <v>46195.44041170139</v>
+        <v>46195.607078368055</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>187</v>
@@ -4182,13 +4182,13 @@
         <v>189</v>
       </c>
       <c r="B49" s="9">
-        <v>46073.40775033565</v>
+        <v>46073.57441700231</v>
       </c>
       <c r="C49" s="9">
-        <v>46122.48811438658</v>
+        <v>46122.654781053236</v>
       </c>
       <c r="D49" s="9">
-        <v>46122.488134652776</v>
+        <v>46122.65480131944</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>190</v>
@@ -4247,13 +4247,13 @@
         <v>192</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.40775060185</v>
+        <v>46073.57441726852</v>
       </c>
       <c r="C50" s="5">
-        <v>46205.32204649306</v>
+        <v>46205.48871315972</v>
       </c>
       <c r="D50" s="5">
-        <v>46205.3220575</v>
+        <v>46205.488724166666</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>193</v>
@@ -4300,13 +4300,13 @@
         <v>195</v>
       </c>
       <c r="B51" s="9">
-        <v>46073.407751192135</v>
+        <v>46073.57441785879</v>
       </c>
       <c r="C51" s="9">
-        <v>46197.33879725695</v>
+        <v>46197.50546392361</v>
       </c>
       <c r="D51" s="9">
-        <v>46197.3388141551</v>
+        <v>46197.50548082176</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>196</v>
@@ -4365,13 +4365,13 @@
         <v>198</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.4077514699</v>
+        <v>46073.57441813657</v>
       </c>
       <c r="C52" s="5">
-        <v>46197.338886412035</v>
+        <v>46197.50555307871</v>
       </c>
       <c r="D52" s="5">
-        <v>46197.338901423616</v>
+        <v>46197.50556809027</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>199</v>
@@ -4430,13 +4430,13 @@
         <v>202</v>
       </c>
       <c r="B53" s="9">
-        <v>46073.40775171296</v>
+        <v>46073.574418379634</v>
       </c>
       <c r="C53" s="9">
-        <v>46197.33890447917</v>
+        <v>46197.50557114583</v>
       </c>
       <c r="D53" s="9">
-        <v>46197.338922106486</v>
+        <v>46197.50558877314</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>203</v>
@@ -4495,13 +4495,13 @@
         <v>205</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.40775196759</v>
+        <v>46073.57441863426</v>
       </c>
       <c r="C54" s="5">
-        <v>46197.339196574074</v>
+        <v>46197.505863240745</v>
       </c>
       <c r="D54" s="5">
-        <v>46197.33921306713</v>
+        <v>46197.5058797338</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>206</v>
@@ -4560,13 +4560,13 @@
         <v>208</v>
       </c>
       <c r="B55" s="9">
-        <v>46073.40775226852</v>
+        <v>46073.57441893518</v>
       </c>
       <c r="C55" s="9">
-        <v>46197.3392925</v>
+        <v>46197.505959166665</v>
       </c>
       <c r="D55" s="9">
-        <v>46197.339310138894</v>
+        <v>46197.50597680555</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>151</v>
@@ -4623,13 +4623,13 @@
         <v>211</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.407752534724</v>
+        <v>46073.57441920139</v>
       </c>
       <c r="C56" s="5">
-        <v>46205.322026145834</v>
+        <v>46205.488692812505</v>
       </c>
       <c r="D56" s="5">
-        <v>46205.32204734954</v>
+        <v>46205.4887140162</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>212</v>
@@ -4686,11 +4686,11 @@
         <v>214</v>
       </c>
       <c r="B57" s="9">
-        <v>46073.40775020834</v>
+        <v>46073.574416874995</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46205.73027799769</v>
+        <v>46205.89694466435</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>215</v>
@@ -4733,11 +4733,11 @@
         <v>217</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.407750555554</v>
+        <v>46073.57441722222</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46205.32204747685</v>
+        <v>46211.699397881945</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>218</v>
@@ -4794,11 +4794,11 @@
         <v>224</v>
       </c>
       <c r="B59" s="9">
-        <v>46073.407750810184</v>
+        <v>46073.57441747685</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46107.99797167824</v>
+        <v>46108.16463834491</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>225</v>
@@ -4855,13 +4855,13 @@
         <v>227</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.40775108796</v>
+        <v>46073.57441775463</v>
       </c>
       <c r="C60" s="5">
-        <v>46205.730267673614</v>
+        <v>46205.89693434028</v>
       </c>
       <c r="D60" s="5">
-        <v>46205.73433416667</v>
+        <v>46205.90100083333</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>228</v>
@@ -4920,11 +4920,11 @@
         <v>230</v>
       </c>
       <c r="B61" s="9">
-        <v>46073.40775134259</v>
+        <v>46073.57441800926</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46205.73028505787</v>
+        <v>46205.89695172454</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>231</v>
@@ -4983,11 +4983,11 @@
         <v>233</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.4077516088</v>
+        <v>46073.574418275464</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46090.53515497685</v>
+        <v>46090.70182164352</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>234</v>
@@ -5030,11 +5030,11 @@
         <v>236</v>
       </c>
       <c r="B63" s="9">
-        <v>46073.40775190972</v>
+        <v>46073.57441857639</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46121.00034344908</v>
+        <v>46121.167010115736</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>237</v>
@@ -5093,11 +5093,11 @@
         <v>240</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.407752175925</v>
+        <v>46073.57441884259</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46121.00034346065</v>
+        <v>46121.16701012732</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>241</v>

--- a/data/50001508 - XEMORTIZ STOCK.xlsx
+++ b/data/50001508 - XEMORTIZ STOCK.xlsx
@@ -4690,7 +4690,7 @@
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46205.89694466435</v>
+        <v>46213.509536840276</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>215</v>
@@ -4796,9 +4796,11 @@
       <c r="B59" s="9">
         <v>46073.57441747685</v>
       </c>
-      <c r="C59" s="10"/>
+      <c r="C59" s="9">
+        <v>46213.509524988425</v>
+      </c>
       <c r="D59" s="9">
-        <v>46108.16463834491</v>
+        <v>46213.50954438657</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>225</v>
@@ -4844,10 +4846,10 @@
         <v>32</v>
       </c>
       <c r="T59" s="10">
-        <v>0</v>
-      </c>
-      <c r="U59" s="11" t="s">
-        <v>94</v>
+        <v>1</v>
+      </c>
+      <c r="U59" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -4861,7 +4863,7 @@
         <v>46205.89693434028</v>
       </c>
       <c r="D60" s="5">
-        <v>46205.90100083333</v>
+        <v>46213.50954549768</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>228</v>
@@ -4911,8 +4913,8 @@
       <c r="T60" s="6">
         <v>1</v>
       </c>
-      <c r="U60" s="7" t="s">
-        <v>27</v>
+      <c r="U60" s="12" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001508 - XEMORTIZ STOCK.xlsx
+++ b/data/50001508 - XEMORTIZ STOCK.xlsx
@@ -1413,7 +1413,7 @@
         <v>46092.72097336805</v>
       </c>
       <c r="D4" s="5">
-        <v>46092.72098704861</v>
+        <v>46214.31316644676</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2090,7 +2090,7 @@
         <v>46114.52188712963</v>
       </c>
       <c r="D15" s="9">
-        <v>46114.521897847226</v>
+        <v>46214.320695428236</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>63</v>
@@ -2403,7 +2403,7 @@
         <v>46134.60708307871</v>
       </c>
       <c r="D20" s="5">
-        <v>46134.60710188658</v>
+        <v>46214.32071828704</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -4005,7 +4005,7 @@
         <v>46195.60707819444</v>
       </c>
       <c r="D46" s="5">
-        <v>46195.607089745376</v>
+        <v>46214.320753622684</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>154</v>

--- a/data/50001508 - XEMORTIZ STOCK.xlsx
+++ b/data/50001508 - XEMORTIZ STOCK.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="239">
   <si>
     <t>50001508 - XEMORTIZ STOCK</t>
   </si>
@@ -256,9 +256,6 @@
     <t>propuesta rodete</t>
   </si>
   <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
     <t xml:space="preserve">
 Rodete:
 Monobloque GEL 7-42 - Código: 300059
@@ -292,12 +289,6 @@
   </si>
   <si>
     <t>propuesta compras a codigo // aprovisionamiento</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
   </si>
   <si>
     <t>Propuesta compras:,Generación OC materiales</t>
@@ -2217,11 +2208,9 @@
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H17" s="10"/>
       <c r="I17" s="9">
         <v>46041</v>
       </c>
@@ -2232,7 +2221,7 @@
         <v>26</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M17" s="10" t="s">
         <v>26</v>
@@ -2244,7 +2233,7 @@
         <v>54</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q17" s="9">
         <v>46042</v>
@@ -2264,7 +2253,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B18" s="5">
         <v>46073.574419236116</v>
@@ -2276,7 +2265,7 @@
         <v>46133.896346724534</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2297,7 +2286,7 @@
         <v>26</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M18" s="6" t="s">
         <v>26</v>
@@ -2309,7 +2298,7 @@
         <v>51</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q18" s="5">
         <v>46042</v>
@@ -2329,7 +2318,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B19" s="9">
         <v>46073.5744165162</v>
@@ -2341,17 +2330,15 @@
         <v>46100.785884259254</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>80</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H19" s="10"/>
       <c r="I19" s="9">
         <v>46041</v>
       </c>
@@ -2374,7 +2361,7 @@
         <v>58</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="Q19" s="9">
         <v>46042</v>
@@ -2394,7 +2381,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B20" s="5">
         <v>46073.57441688658</v>
@@ -2406,7 +2393,7 @@
         <v>46214.32071828704</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>25</v>
@@ -2430,7 +2417,7 @@
         <v>26</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>26</v>
@@ -2447,7 +2434,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B21" s="9">
         <v>46073.57441755787</v>
@@ -2459,16 +2446,16 @@
         <v>46133.89220711806</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I21" s="9">
         <v>46043</v>
@@ -2486,13 +2473,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="Q21" s="9">
         <v>46048</v>
@@ -2512,7 +2499,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B22" s="5">
         <v>46073.57441785879</v>
@@ -2524,16 +2511,16 @@
         <v>46114.78100939815</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I22" s="5">
         <v>46043</v>
@@ -2551,29 +2538,29 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
       <c r="S22" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T22" s="6">
         <v>0</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B23" s="9">
         <v>46073.57441814815</v>
@@ -2585,16 +2572,16 @@
         <v>46114.78105144676</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I23" s="9">
         <v>46045</v>
@@ -2612,29 +2599,29 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
       <c r="S23" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T23" s="10">
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B24" s="5">
         <v>46073.57441936343</v>
@@ -2646,16 +2633,16 @@
         <v>46133.8975922338</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I24" s="5">
         <v>46043</v>
@@ -2673,13 +2660,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="Q24" s="5">
         <v>46064</v>
@@ -2699,7 +2686,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B25" s="9">
         <v>46073.57441965278</v>
@@ -2711,16 +2698,16 @@
         <v>46122.70442476852</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I25" s="9">
         <v>46043</v>
@@ -2738,29 +2725,29 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O25" s="10" t="s">
         <v>69</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B26" s="5">
         <v>46073.574416469906</v>
@@ -2772,16 +2759,16 @@
         <v>46133.897567673615</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I26" s="5">
         <v>46045</v>
@@ -2799,29 +2786,29 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="O26" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="O26" s="6" t="s">
-        <v>102</v>
-      </c>
       <c r="P26" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
       <c r="S26" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
       </c>
       <c r="U26" s="11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B27" s="9">
         <v>46073.574416840274</v>
@@ -2833,16 +2820,16 @@
         <v>46097.55137980324</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I27" s="9">
         <v>46043</v>
@@ -2860,13 +2847,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="Q27" s="9">
         <v>46080</v>
@@ -2886,7 +2873,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B28" s="5">
         <v>46073.574417129625</v>
@@ -2898,16 +2885,16 @@
         <v>46097.55128159722</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I28" s="5">
         <v>46043</v>
@@ -2925,29 +2912,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B29" s="9">
         <v>46073.57441739584</v>
@@ -2959,16 +2946,16 @@
         <v>46097.55131616898</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I29" s="9">
         <v>46052</v>
@@ -2986,29 +2973,29 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="O29" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="O29" s="10" t="s">
-        <v>111</v>
-      </c>
       <c r="P29" s="10" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
       <c r="S29" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T29" s="10">
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B30" s="5">
         <v>46073.57441769676</v>
@@ -3020,16 +3007,16 @@
         <v>46097.55135262731</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I30" s="5">
         <v>46052</v>
@@ -3047,29 +3034,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B31" s="9">
         <v>46073.574417951386</v>
@@ -3081,16 +3068,16 @@
         <v>46111.79876402778</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I31" s="9">
         <v>46043</v>
@@ -3108,13 +3095,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="Q31" s="9">
         <v>46071</v>
@@ -3134,7 +3121,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B32" s="5">
         <v>46073.57441821759</v>
@@ -3146,16 +3133,16 @@
         <v>46097.551928483794</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I32" s="5">
         <v>46043</v>
@@ -3173,29 +3160,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B33" s="9">
         <v>46073.57441847222</v>
@@ -3207,16 +3194,16 @@
         <v>46111.798738171296</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I33" s="9">
         <v>46052</v>
@@ -3234,29 +3221,29 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
       <c r="S33" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T33" s="10">
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B34" s="5">
         <v>46073.574418749995</v>
@@ -3268,7 +3255,7 @@
         <v>46198.565061875</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>25</v>
@@ -3292,7 +3279,7 @@
         <v>26</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>26</v>
@@ -3309,7 +3296,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B35" s="9">
         <v>46073.57441901621</v>
@@ -3321,16 +3308,16 @@
         <v>46197.70911202546</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I35" s="9">
         <v>46041</v>
@@ -3348,13 +3335,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>58</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="Q35" s="9">
         <v>46045</v>
@@ -3374,7 +3361,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B36" s="5">
         <v>46073.57441695602</v>
@@ -3386,16 +3373,16 @@
         <v>46197.70914525463</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I36" s="5">
         <v>46059</v>
@@ -3413,13 +3400,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="Q36" s="5">
         <v>46065</v>
@@ -3439,7 +3426,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B37" s="9">
         <v>46090.69622997685</v>
@@ -3451,16 +3438,16 @@
         <v>46108.76809931713</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I37" s="9">
         <v>46066</v>
@@ -3478,13 +3465,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="Q37" s="9">
         <v>46066</v>
@@ -3504,7 +3491,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B38" s="5">
         <v>46090.69645336806</v>
@@ -3516,16 +3503,16 @@
         <v>46198.565049791665</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I38" s="5">
         <v>46104</v>
@@ -3543,13 +3530,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="Q38" s="5">
         <v>46104</v>
@@ -3569,7 +3556,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B39" s="9">
         <v>46073.57441724537</v>
@@ -3581,7 +3568,7 @@
         <v>46111.79889361111</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>25</v>
@@ -3605,7 +3592,7 @@
         <v>26</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3622,7 +3609,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B40" s="5">
         <v>46073.57441746528</v>
@@ -3634,16 +3621,16 @@
         <v>46111.798837326394</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I40" s="5">
         <v>46072</v>
@@ -3661,13 +3648,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="Q40" s="5">
         <v>46073</v>
@@ -3687,7 +3674,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B41" s="9">
         <v>46073.57441769676</v>
@@ -3699,16 +3686,16 @@
         <v>46111.79888084491</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I41" s="9">
         <v>46076</v>
@@ -3726,13 +3713,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="O41" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="O41" s="10" t="s">
-        <v>157</v>
-      </c>
       <c r="P41" s="10" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="Q41" s="9">
         <v>46077</v>
@@ -3752,7 +3739,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B42" s="5">
         <v>46073.57441792824</v>
@@ -3764,7 +3751,7 @@
         <v>46196.8510114699</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3788,7 +3775,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3801,7 +3788,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B43" s="9">
         <v>46073.574418159726</v>
@@ -3813,16 +3800,16 @@
         <v>46196.850968819446</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I43" s="9">
         <v>46078</v>
@@ -3840,13 +3827,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="Q43" s="9">
         <v>46080</v>
@@ -3866,7 +3853,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B44" s="5">
         <v>46073.574418379634</v>
@@ -3878,16 +3865,16 @@
         <v>46195.911566111114</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I44" s="5">
         <v>46083</v>
@@ -3905,13 +3892,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="Q44" s="5">
         <v>46087</v>
@@ -3931,7 +3918,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B45" s="9">
         <v>46073.57441861111</v>
@@ -3943,16 +3930,16 @@
         <v>46196.91052092593</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I45" s="9">
         <v>46090</v>
@@ -3970,13 +3957,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="Q45" s="9">
         <v>46090</v>
@@ -3996,7 +3983,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B46" s="5">
         <v>46073.57441885417</v>
@@ -4008,7 +3995,7 @@
         <v>46214.320753622684</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4032,7 +4019,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4049,7 +4036,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B47" s="9">
         <v>46073.574416724536</v>
@@ -4061,16 +4048,16 @@
         <v>46127.65040571759</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I47" s="9">
         <v>46049</v>
@@ -4088,13 +4075,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="Q47" s="9">
         <v>46049</v>
@@ -4114,7 +4101,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B48" s="5">
         <v>46073.5744191088</v>
@@ -4126,16 +4113,16 @@
         <v>46195.607078368055</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I48" s="5">
         <v>46065</v>
@@ -4153,13 +4140,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Q48" s="5">
         <v>46065</v>
@@ -4179,7 +4166,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B49" s="9">
         <v>46073.57441700231</v>
@@ -4191,16 +4178,16 @@
         <v>46122.65480131944</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I49" s="9">
         <v>46083</v>
@@ -4218,13 +4205,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q49" s="9">
         <v>46083</v>
@@ -4244,7 +4231,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B50" s="5">
         <v>46073.57441726852</v>
@@ -4256,7 +4243,7 @@
         <v>46205.488724166666</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4280,7 +4267,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4297,7 +4284,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B51" s="9">
         <v>46073.57441785879</v>
@@ -4309,17 +4296,15 @@
         <v>46197.50548082176</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H51" s="10"/>
       <c r="I51" s="9">
         <v>46091</v>
       </c>
@@ -4336,13 +4321,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="Q51" s="9">
         <v>46097</v>
@@ -4362,7 +4347,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B52" s="5">
         <v>46073.57441813657</v>
@@ -4374,17 +4359,15 @@
         <v>46197.50556809027</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H52" s="6"/>
       <c r="I52" s="5">
         <v>46098</v>
       </c>
@@ -4401,13 +4384,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="Q52" s="5">
         <v>46098</v>
@@ -4427,7 +4410,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B53" s="9">
         <v>46073.574418379634</v>
@@ -4439,17 +4422,15 @@
         <v>46197.50558877314</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H53" s="10"/>
       <c r="I53" s="9">
         <v>46099</v>
       </c>
@@ -4466,13 +4447,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="Q53" s="9">
         <v>46099</v>
@@ -4492,7 +4473,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B54" s="5">
         <v>46073.57441863426</v>
@@ -4504,17 +4485,15 @@
         <v>46197.5058797338</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H54" s="6"/>
       <c r="I54" s="5">
         <v>46100</v>
       </c>
@@ -4531,13 +4510,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="Q54" s="5">
         <v>46100</v>
@@ -4557,7 +4536,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B55" s="9">
         <v>46073.57441893518</v>
@@ -4569,17 +4548,15 @@
         <v>46197.50597680555</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H55" s="10"/>
       <c r="I55" s="10"/>
       <c r="J55" s="9">
         <v>46101</v>
@@ -4594,13 +4571,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="Q55" s="9">
         <v>46101</v>
@@ -4620,7 +4597,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B56" s="5">
         <v>46073.57441920139</v>
@@ -4632,17 +4609,15 @@
         <v>46205.4887140162</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H56" s="6"/>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
         <v>46105</v>
@@ -4657,13 +4632,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="Q56" s="5">
         <v>46105</v>
@@ -4683,7 +4658,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B57" s="9">
         <v>46073.574416874995</v>
@@ -4693,7 +4668,7 @@
         <v>46213.509536840276</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>25</v>
@@ -4717,7 +4692,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -4730,7 +4705,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B58" s="5">
         <v>46073.57441722222</v>
@@ -4740,16 +4715,16 @@
         <v>46211.699397881945</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
@@ -4759,19 +4734,19 @@
         <v>26</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="M58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="Q58" s="5">
         <v>46106</v>
@@ -4786,12 +4761,12 @@
         <v>0</v>
       </c>
       <c r="U58" s="12" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B59" s="9">
         <v>46073.57441747685</v>
@@ -4803,17 +4778,15 @@
         <v>46213.50954438657</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H59" s="10"/>
       <c r="I59" s="10"/>
       <c r="J59" s="9">
         <v>46107</v>
@@ -4828,13 +4801,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="O59" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="O59" s="10" t="s">
-        <v>218</v>
-      </c>
       <c r="P59" s="10" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="Q59" s="9">
         <v>46107</v>
@@ -4854,7 +4827,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B60" s="5">
         <v>46073.57441775463</v>
@@ -4866,16 +4839,16 @@
         <v>46213.50954549768</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I60" s="5">
         <v>46108</v>
@@ -4893,13 +4866,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="Q60" s="5">
         <v>46080</v>
@@ -4908,18 +4881,18 @@
         <v>46108</v>
       </c>
       <c r="S60" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T60" s="6">
         <v>1</v>
       </c>
       <c r="U60" s="12" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B61" s="9">
         <v>46073.57441800926</v>
@@ -4929,16 +4902,16 @@
         <v>46205.89695172454</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I61" s="9">
         <v>46111</v>
@@ -4956,13 +4929,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="Q61" s="9">
         <v>46111</v>
@@ -4977,12 +4950,12 @@
         <v>0</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B62" s="5">
         <v>46073.574418275464</v>
@@ -4992,7 +4965,7 @@
         <v>46090.70182164352</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5016,7 +4989,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5029,7 +5002,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B63" s="9">
         <v>46073.57441857639</v>
@@ -5039,16 +5012,16 @@
         <v>46121.167010115736</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="I63" s="9">
         <v>46112</v>
@@ -5066,13 +5039,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="O63" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="P63" s="10" t="s">
         <v>231</v>
-      </c>
-      <c r="P63" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="Q63" s="9">
         <v>46120</v>
@@ -5087,12 +5060,12 @@
         <v>0</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B64" s="5">
         <v>46073.57441884259</v>
@@ -5102,16 +5075,16 @@
         <v>46121.16701012732</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="I64" s="5">
         <v>46112</v>
@@ -5129,13 +5102,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="O64" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="Q64" s="5">
         <v>46120</v>
@@ -5150,7 +5123,7 @@
         <v>0</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001508 - XEMORTIZ STOCK.xlsx
+++ b/data/50001508 - XEMORTIZ STOCK.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="240">
   <si>
     <t>50001508 - XEMORTIZ STOCK</t>
   </si>
@@ -254,6 +254,9 @@
   </si>
   <si>
     <t>propuesta rodete</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -2199,7 +2202,7 @@
         <v>46114.52187152777</v>
       </c>
       <c r="D17" s="9">
-        <v>46133.89260450231</v>
+        <v>46223.810965763885</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>69</v>
@@ -2208,9 +2211,11 @@
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H17" s="10"/>
+        <v>70</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>70</v>
+      </c>
       <c r="I17" s="9">
         <v>46041</v>
       </c>
@@ -2221,7 +2226,7 @@
         <v>26</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M17" s="10" t="s">
         <v>26</v>
@@ -2233,7 +2238,7 @@
         <v>54</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q17" s="9">
         <v>46042</v>
@@ -2253,7 +2258,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B18" s="5">
         <v>46073.574419236116</v>
@@ -2265,7 +2270,7 @@
         <v>46133.896346724534</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2286,7 +2291,7 @@
         <v>26</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M18" s="6" t="s">
         <v>26</v>
@@ -2298,7 +2303,7 @@
         <v>51</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q18" s="5">
         <v>46042</v>
@@ -2318,7 +2323,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B19" s="9">
         <v>46073.5744165162</v>
@@ -2327,18 +2332,20 @@
         <v>46097.55150556713</v>
       </c>
       <c r="D19" s="9">
-        <v>46100.785884259254</v>
+        <v>46223.81096241898</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" s="10"/>
+        <v>70</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>70</v>
+      </c>
       <c r="I19" s="9">
         <v>46041</v>
       </c>
@@ -2361,7 +2368,7 @@
         <v>58</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q19" s="9">
         <v>46042</v>
@@ -2381,7 +2388,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B20" s="5">
         <v>46073.57441688658</v>
@@ -2393,7 +2400,7 @@
         <v>46214.32071828704</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>25</v>
@@ -2417,7 +2424,7 @@
         <v>26</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>26</v>
@@ -2434,7 +2441,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B21" s="9">
         <v>46073.57441755787</v>
@@ -2446,16 +2453,16 @@
         <v>46133.89220711806</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I21" s="9">
         <v>46043</v>
@@ -2473,13 +2480,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q21" s="9">
         <v>46048</v>
@@ -2499,7 +2506,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B22" s="5">
         <v>46073.57441785879</v>
@@ -2511,16 +2518,16 @@
         <v>46114.78100939815</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I22" s="5">
         <v>46043</v>
@@ -2538,29 +2545,29 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
       <c r="S22" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T22" s="6">
         <v>0</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B23" s="9">
         <v>46073.57441814815</v>
@@ -2572,16 +2579,16 @@
         <v>46114.78105144676</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I23" s="9">
         <v>46045</v>
@@ -2599,29 +2606,29 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
       <c r="S23" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T23" s="10">
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B24" s="5">
         <v>46073.57441936343</v>
@@ -2633,16 +2640,16 @@
         <v>46133.8975922338</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I24" s="5">
         <v>46043</v>
@@ -2660,13 +2667,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q24" s="5">
         <v>46064</v>
@@ -2686,7 +2693,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B25" s="9">
         <v>46073.57441965278</v>
@@ -2698,16 +2705,16 @@
         <v>46122.70442476852</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I25" s="9">
         <v>46043</v>
@@ -2725,29 +2732,29 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O25" s="10" t="s">
         <v>69</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B26" s="5">
         <v>46073.574416469906</v>
@@ -2759,16 +2766,16 @@
         <v>46133.897567673615</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I26" s="5">
         <v>46045</v>
@@ -2786,29 +2793,29 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
       <c r="S26" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
       </c>
       <c r="U26" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B27" s="9">
         <v>46073.574416840274</v>
@@ -2820,16 +2827,16 @@
         <v>46097.55137980324</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I27" s="9">
         <v>46043</v>
@@ -2847,13 +2854,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q27" s="9">
         <v>46080</v>
@@ -2873,7 +2880,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B28" s="5">
         <v>46073.574417129625</v>
@@ -2885,16 +2892,16 @@
         <v>46097.55128159722</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I28" s="5">
         <v>46043</v>
@@ -2912,29 +2919,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B29" s="9">
         <v>46073.57441739584</v>
@@ -2946,16 +2953,16 @@
         <v>46097.55131616898</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I29" s="9">
         <v>46052</v>
@@ -2973,29 +2980,29 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
       <c r="S29" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T29" s="10">
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B30" s="5">
         <v>46073.57441769676</v>
@@ -3007,16 +3014,16 @@
         <v>46097.55135262731</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I30" s="5">
         <v>46052</v>
@@ -3034,29 +3041,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B31" s="9">
         <v>46073.574417951386</v>
@@ -3068,16 +3075,16 @@
         <v>46111.79876402778</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I31" s="9">
         <v>46043</v>
@@ -3095,13 +3102,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q31" s="9">
         <v>46071</v>
@@ -3121,7 +3128,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B32" s="5">
         <v>46073.57441821759</v>
@@ -3133,16 +3140,16 @@
         <v>46097.551928483794</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I32" s="5">
         <v>46043</v>
@@ -3160,29 +3167,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B33" s="9">
         <v>46073.57441847222</v>
@@ -3194,16 +3201,16 @@
         <v>46111.798738171296</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I33" s="9">
         <v>46052</v>
@@ -3221,29 +3228,29 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
       <c r="S33" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T33" s="10">
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B34" s="5">
         <v>46073.574418749995</v>
@@ -3255,7 +3262,7 @@
         <v>46198.565061875</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>25</v>
@@ -3279,7 +3286,7 @@
         <v>26</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>26</v>
@@ -3296,7 +3303,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B35" s="9">
         <v>46073.57441901621</v>
@@ -3308,16 +3315,16 @@
         <v>46197.70911202546</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I35" s="9">
         <v>46041</v>
@@ -3335,13 +3342,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>58</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q35" s="9">
         <v>46045</v>
@@ -3361,7 +3368,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B36" s="5">
         <v>46073.57441695602</v>
@@ -3373,16 +3380,16 @@
         <v>46197.70914525463</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I36" s="5">
         <v>46059</v>
@@ -3400,13 +3407,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q36" s="5">
         <v>46065</v>
@@ -3426,7 +3433,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B37" s="9">
         <v>46090.69622997685</v>
@@ -3438,16 +3445,16 @@
         <v>46108.76809931713</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I37" s="9">
         <v>46066</v>
@@ -3465,13 +3472,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q37" s="9">
         <v>46066</v>
@@ -3491,7 +3498,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B38" s="5">
         <v>46090.69645336806</v>
@@ -3503,16 +3510,16 @@
         <v>46198.565049791665</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I38" s="5">
         <v>46104</v>
@@ -3530,13 +3537,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q38" s="5">
         <v>46104</v>
@@ -3556,7 +3563,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B39" s="9">
         <v>46073.57441724537</v>
@@ -3568,7 +3575,7 @@
         <v>46111.79889361111</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>25</v>
@@ -3592,7 +3599,7 @@
         <v>26</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3609,7 +3616,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B40" s="5">
         <v>46073.57441746528</v>
@@ -3621,16 +3628,16 @@
         <v>46111.798837326394</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I40" s="5">
         <v>46072</v>
@@ -3648,13 +3655,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q40" s="5">
         <v>46073</v>
@@ -3674,7 +3681,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B41" s="9">
         <v>46073.57441769676</v>
@@ -3686,16 +3693,16 @@
         <v>46111.79888084491</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I41" s="9">
         <v>46076</v>
@@ -3713,13 +3720,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q41" s="9">
         <v>46077</v>
@@ -3739,7 +3746,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B42" s="5">
         <v>46073.57441792824</v>
@@ -3751,7 +3758,7 @@
         <v>46196.8510114699</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3775,7 +3782,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3788,7 +3795,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B43" s="9">
         <v>46073.574418159726</v>
@@ -3800,16 +3807,16 @@
         <v>46196.850968819446</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I43" s="9">
         <v>46078</v>
@@ -3827,13 +3834,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q43" s="9">
         <v>46080</v>
@@ -3853,7 +3860,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B44" s="5">
         <v>46073.574418379634</v>
@@ -3865,16 +3872,16 @@
         <v>46195.911566111114</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I44" s="5">
         <v>46083</v>
@@ -3892,13 +3899,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q44" s="5">
         <v>46087</v>
@@ -3918,7 +3925,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B45" s="9">
         <v>46073.57441861111</v>
@@ -3930,16 +3937,16 @@
         <v>46196.91052092593</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I45" s="9">
         <v>46090</v>
@@ -3957,13 +3964,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q45" s="9">
         <v>46090</v>
@@ -3983,7 +3990,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B46" s="5">
         <v>46073.57441885417</v>
@@ -3995,7 +4002,7 @@
         <v>46214.320753622684</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4019,7 +4026,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4036,7 +4043,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B47" s="9">
         <v>46073.574416724536</v>
@@ -4048,16 +4055,16 @@
         <v>46127.65040571759</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I47" s="9">
         <v>46049</v>
@@ -4075,13 +4082,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q47" s="9">
         <v>46049</v>
@@ -4101,7 +4108,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B48" s="5">
         <v>46073.5744191088</v>
@@ -4113,16 +4120,16 @@
         <v>46195.607078368055</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I48" s="5">
         <v>46065</v>
@@ -4140,13 +4147,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q48" s="5">
         <v>46065</v>
@@ -4166,7 +4173,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B49" s="9">
         <v>46073.57441700231</v>
@@ -4178,16 +4185,16 @@
         <v>46122.65480131944</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I49" s="9">
         <v>46083</v>
@@ -4205,13 +4212,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q49" s="9">
         <v>46083</v>
@@ -4231,7 +4238,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B50" s="5">
         <v>46073.57441726852</v>
@@ -4243,7 +4250,7 @@
         <v>46205.488724166666</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4267,7 +4274,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4284,7 +4291,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B51" s="9">
         <v>46073.57441785879</v>
@@ -4293,18 +4300,20 @@
         <v>46197.50546392361</v>
       </c>
       <c r="D51" s="9">
-        <v>46197.50548082176</v>
+        <v>46223.81110523148</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H51" s="10"/>
+        <v>70</v>
+      </c>
+      <c r="H51" s="10" t="s">
+        <v>70</v>
+      </c>
       <c r="I51" s="9">
         <v>46091</v>
       </c>
@@ -4321,13 +4330,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q51" s="9">
         <v>46097</v>
@@ -4347,7 +4356,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B52" s="5">
         <v>46073.57441813657</v>
@@ -4356,18 +4365,20 @@
         <v>46197.50555307871</v>
       </c>
       <c r="D52" s="5">
-        <v>46197.50556809027</v>
+        <v>46223.81110195602</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H52" s="6"/>
+        <v>70</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="I52" s="5">
         <v>46098</v>
       </c>
@@ -4384,13 +4395,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q52" s="5">
         <v>46098</v>
@@ -4410,7 +4421,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B53" s="9">
         <v>46073.574418379634</v>
@@ -4419,18 +4430,20 @@
         <v>46197.50557114583</v>
       </c>
       <c r="D53" s="9">
-        <v>46197.50558877314</v>
+        <v>46223.8110984838</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H53" s="10"/>
+        <v>70</v>
+      </c>
+      <c r="H53" s="10" t="s">
+        <v>70</v>
+      </c>
       <c r="I53" s="9">
         <v>46099</v>
       </c>
@@ -4447,13 +4460,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q53" s="9">
         <v>46099</v>
@@ -4473,7 +4486,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B54" s="5">
         <v>46073.57441863426</v>
@@ -4482,18 +4495,20 @@
         <v>46197.505863240745</v>
       </c>
       <c r="D54" s="5">
-        <v>46197.5058797338</v>
+        <v>46223.81109472222</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H54" s="6"/>
+        <v>70</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="I54" s="5">
         <v>46100</v>
       </c>
@@ -4510,13 +4525,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q54" s="5">
         <v>46100</v>
@@ -4536,7 +4551,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B55" s="9">
         <v>46073.57441893518</v>
@@ -4545,18 +4560,20 @@
         <v>46197.505959166665</v>
       </c>
       <c r="D55" s="9">
-        <v>46197.50597680555</v>
+        <v>46223.81109128472</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H55" s="10"/>
+        <v>70</v>
+      </c>
+      <c r="H55" s="10" t="s">
+        <v>70</v>
+      </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9">
         <v>46101</v>
@@ -4571,13 +4588,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q55" s="9">
         <v>46101</v>
@@ -4597,7 +4614,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B56" s="5">
         <v>46073.57441920139</v>
@@ -4606,18 +4623,20 @@
         <v>46205.488692812505</v>
       </c>
       <c r="D56" s="5">
-        <v>46205.4887140162</v>
+        <v>46223.81108594907</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H56" s="6"/>
+        <v>70</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
         <v>46105</v>
@@ -4632,13 +4651,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q56" s="5">
         <v>46105</v>
@@ -4658,7 +4677,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B57" s="9">
         <v>46073.574416874995</v>
@@ -4668,7 +4687,7 @@
         <v>46213.509536840276</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>25</v>
@@ -4692,7 +4711,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -4705,7 +4724,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B58" s="5">
         <v>46073.57441722222</v>
@@ -4715,16 +4734,16 @@
         <v>46211.699397881945</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
@@ -4734,19 +4753,19 @@
         <v>26</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q58" s="5">
         <v>46106</v>
@@ -4761,12 +4780,12 @@
         <v>0</v>
       </c>
       <c r="U58" s="12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B59" s="9">
         <v>46073.57441747685</v>
@@ -4775,18 +4794,20 @@
         <v>46213.509524988425</v>
       </c>
       <c r="D59" s="9">
-        <v>46213.50954438657</v>
+        <v>46223.811153622686</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H59" s="10"/>
+        <v>70</v>
+      </c>
+      <c r="H59" s="10" t="s">
+        <v>70</v>
+      </c>
       <c r="I59" s="10"/>
       <c r="J59" s="9">
         <v>46107</v>
@@ -4801,13 +4822,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q59" s="9">
         <v>46107</v>
@@ -4827,7 +4848,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B60" s="5">
         <v>46073.57441775463</v>
@@ -4839,16 +4860,16 @@
         <v>46213.50954549768</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I60" s="5">
         <v>46108</v>
@@ -4866,13 +4887,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q60" s="5">
         <v>46080</v>
@@ -4881,18 +4902,18 @@
         <v>46108</v>
       </c>
       <c r="S60" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T60" s="6">
         <v>1</v>
       </c>
       <c r="U60" s="12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B61" s="9">
         <v>46073.57441800926</v>
@@ -4902,16 +4923,16 @@
         <v>46205.89695172454</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I61" s="9">
         <v>46111</v>
@@ -4929,13 +4950,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q61" s="9">
         <v>46111</v>
@@ -4950,12 +4971,12 @@
         <v>0</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B62" s="5">
         <v>46073.574418275464</v>
@@ -4965,7 +4986,7 @@
         <v>46090.70182164352</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -4989,7 +5010,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5002,7 +5023,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B63" s="9">
         <v>46073.57441857639</v>
@@ -5012,16 +5033,16 @@
         <v>46121.167010115736</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I63" s="9">
         <v>46112</v>
@@ -5039,13 +5060,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q63" s="9">
         <v>46120</v>
@@ -5060,12 +5081,12 @@
         <v>0</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B64" s="5">
         <v>46073.57441884259</v>
@@ -5075,16 +5096,16 @@
         <v>46121.16701012732</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I64" s="5">
         <v>46112</v>
@@ -5102,13 +5123,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q64" s="5">
         <v>46120</v>
@@ -5123,7 +5144,7 @@
         <v>0</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001508 - XEMORTIZ STOCK.xlsx
+++ b/data/50001508 - XEMORTIZ STOCK.xlsx
@@ -4857,7 +4857,7 @@
         <v>46205.89693434028</v>
       </c>
       <c r="D60" s="5">
-        <v>46213.50954549768</v>
+        <v>46224.66064472222</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>226</v>

--- a/data/50001508 - XEMORTIZ STOCK.xlsx
+++ b/data/50001508 - XEMORTIZ STOCK.xlsx
@@ -4731,7 +4731,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46211.699397881945</v>
+        <v>46225.55231209491</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>216</v>

--- a/data/50001508 - XEMORTIZ STOCK.xlsx
+++ b/data/50001508 - XEMORTIZ STOCK.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="241">
   <si>
     <t>50001508 - XEMORTIZ STOCK</t>
   </si>
@@ -254,6 +254,9 @@
   </si>
   <si>
     <t>propuesta rodete</t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
   </si>
   <si>
     <t>nespinoza@zitron.com</t>
@@ -2214,7 +2217,7 @@
         <v>70</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I17" s="9">
         <v>46041</v>
@@ -2226,7 +2229,7 @@
         <v>26</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M17" s="10" t="s">
         <v>26</v>
@@ -2238,7 +2241,7 @@
         <v>54</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q17" s="9">
         <v>46042</v>
@@ -2258,7 +2261,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B18" s="5">
         <v>46073.574419236116</v>
@@ -2270,7 +2273,7 @@
         <v>46133.896346724534</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2291,7 +2294,7 @@
         <v>26</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M18" s="6" t="s">
         <v>26</v>
@@ -2303,7 +2306,7 @@
         <v>51</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q18" s="5">
         <v>46042</v>
@@ -2323,7 +2326,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B19" s="9">
         <v>46073.5744165162</v>
@@ -2335,7 +2338,7 @@
         <v>46223.81096241898</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -2344,7 +2347,7 @@
         <v>70</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I19" s="9">
         <v>46041</v>
@@ -2368,7 +2371,7 @@
         <v>58</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q19" s="9">
         <v>46042</v>
@@ -2388,7 +2391,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B20" s="5">
         <v>46073.57441688658</v>
@@ -2400,7 +2403,7 @@
         <v>46214.32071828704</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>25</v>
@@ -2424,7 +2427,7 @@
         <v>26</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>26</v>
@@ -2441,7 +2444,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B21" s="9">
         <v>46073.57441755787</v>
@@ -2453,16 +2456,16 @@
         <v>46133.89220711806</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I21" s="9">
         <v>46043</v>
@@ -2480,13 +2483,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q21" s="9">
         <v>46048</v>
@@ -2506,7 +2509,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B22" s="5">
         <v>46073.57441785879</v>
@@ -2518,16 +2521,16 @@
         <v>46114.78100939815</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I22" s="5">
         <v>46043</v>
@@ -2545,29 +2548,29 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
       <c r="S22" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T22" s="6">
         <v>0</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B23" s="9">
         <v>46073.57441814815</v>
@@ -2579,16 +2582,16 @@
         <v>46114.78105144676</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I23" s="9">
         <v>46045</v>
@@ -2606,29 +2609,29 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
       <c r="S23" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T23" s="10">
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B24" s="5">
         <v>46073.57441936343</v>
@@ -2640,16 +2643,16 @@
         <v>46133.8975922338</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I24" s="5">
         <v>46043</v>
@@ -2667,13 +2670,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q24" s="5">
         <v>46064</v>
@@ -2693,7 +2696,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B25" s="9">
         <v>46073.57441965278</v>
@@ -2705,16 +2708,16 @@
         <v>46122.70442476852</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I25" s="9">
         <v>46043</v>
@@ -2732,29 +2735,29 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O25" s="10" t="s">
         <v>69</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B26" s="5">
         <v>46073.574416469906</v>
@@ -2766,16 +2769,16 @@
         <v>46133.897567673615</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I26" s="5">
         <v>46045</v>
@@ -2793,29 +2796,29 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
       <c r="S26" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
       </c>
       <c r="U26" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B27" s="9">
         <v>46073.574416840274</v>
@@ -2827,16 +2830,16 @@
         <v>46097.55137980324</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I27" s="9">
         <v>46043</v>
@@ -2854,13 +2857,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q27" s="9">
         <v>46080</v>
@@ -2880,7 +2883,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B28" s="5">
         <v>46073.574417129625</v>
@@ -2892,16 +2895,16 @@
         <v>46097.55128159722</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I28" s="5">
         <v>46043</v>
@@ -2919,29 +2922,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B29" s="9">
         <v>46073.57441739584</v>
@@ -2953,16 +2956,16 @@
         <v>46097.55131616898</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I29" s="9">
         <v>46052</v>
@@ -2980,29 +2983,29 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
       <c r="S29" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T29" s="10">
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B30" s="5">
         <v>46073.57441769676</v>
@@ -3014,16 +3017,16 @@
         <v>46097.55135262731</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I30" s="5">
         <v>46052</v>
@@ -3041,29 +3044,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B31" s="9">
         <v>46073.574417951386</v>
@@ -3075,16 +3078,16 @@
         <v>46111.79876402778</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I31" s="9">
         <v>46043</v>
@@ -3102,13 +3105,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q31" s="9">
         <v>46071</v>
@@ -3128,7 +3131,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B32" s="5">
         <v>46073.57441821759</v>
@@ -3140,16 +3143,16 @@
         <v>46097.551928483794</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I32" s="5">
         <v>46043</v>
@@ -3167,29 +3170,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B33" s="9">
         <v>46073.57441847222</v>
@@ -3201,16 +3204,16 @@
         <v>46111.798738171296</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I33" s="9">
         <v>46052</v>
@@ -3228,29 +3231,29 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
       <c r="S33" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T33" s="10">
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B34" s="5">
         <v>46073.574418749995</v>
@@ -3262,7 +3265,7 @@
         <v>46198.565061875</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>25</v>
@@ -3286,7 +3289,7 @@
         <v>26</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>26</v>
@@ -3303,7 +3306,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B35" s="9">
         <v>46073.57441901621</v>
@@ -3315,16 +3318,16 @@
         <v>46197.70911202546</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I35" s="9">
         <v>46041</v>
@@ -3342,13 +3345,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>58</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q35" s="9">
         <v>46045</v>
@@ -3368,7 +3371,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B36" s="5">
         <v>46073.57441695602</v>
@@ -3380,16 +3383,16 @@
         <v>46197.70914525463</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I36" s="5">
         <v>46059</v>
@@ -3407,13 +3410,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q36" s="5">
         <v>46065</v>
@@ -3433,7 +3436,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B37" s="9">
         <v>46090.69622997685</v>
@@ -3445,16 +3448,16 @@
         <v>46108.76809931713</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I37" s="9">
         <v>46066</v>
@@ -3472,13 +3475,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q37" s="9">
         <v>46066</v>
@@ -3498,7 +3501,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B38" s="5">
         <v>46090.69645336806</v>
@@ -3510,16 +3513,16 @@
         <v>46198.565049791665</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I38" s="5">
         <v>46104</v>
@@ -3537,13 +3540,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q38" s="5">
         <v>46104</v>
@@ -3563,7 +3566,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B39" s="9">
         <v>46073.57441724537</v>
@@ -3575,7 +3578,7 @@
         <v>46111.79889361111</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>25</v>
@@ -3599,7 +3602,7 @@
         <v>26</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3616,7 +3619,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B40" s="5">
         <v>46073.57441746528</v>
@@ -3628,16 +3631,16 @@
         <v>46111.798837326394</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I40" s="5">
         <v>46072</v>
@@ -3655,13 +3658,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q40" s="5">
         <v>46073</v>
@@ -3681,7 +3684,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B41" s="9">
         <v>46073.57441769676</v>
@@ -3693,16 +3696,16 @@
         <v>46111.79888084491</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I41" s="9">
         <v>46076</v>
@@ -3720,13 +3723,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q41" s="9">
         <v>46077</v>
@@ -3746,7 +3749,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B42" s="5">
         <v>46073.57441792824</v>
@@ -3758,7 +3761,7 @@
         <v>46196.8510114699</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3782,7 +3785,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3795,7 +3798,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B43" s="9">
         <v>46073.574418159726</v>
@@ -3807,16 +3810,16 @@
         <v>46196.850968819446</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I43" s="9">
         <v>46078</v>
@@ -3834,13 +3837,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q43" s="9">
         <v>46080</v>
@@ -3860,7 +3863,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B44" s="5">
         <v>46073.574418379634</v>
@@ -3872,16 +3875,16 @@
         <v>46195.911566111114</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I44" s="5">
         <v>46083</v>
@@ -3899,13 +3902,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q44" s="5">
         <v>46087</v>
@@ -3925,7 +3928,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B45" s="9">
         <v>46073.57441861111</v>
@@ -3937,16 +3940,16 @@
         <v>46196.91052092593</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I45" s="9">
         <v>46090</v>
@@ -3964,13 +3967,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q45" s="9">
         <v>46090</v>
@@ -3990,7 +3993,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B46" s="5">
         <v>46073.57441885417</v>
@@ -4002,7 +4005,7 @@
         <v>46214.320753622684</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4026,7 +4029,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4043,7 +4046,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B47" s="9">
         <v>46073.574416724536</v>
@@ -4055,16 +4058,16 @@
         <v>46127.65040571759</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I47" s="9">
         <v>46049</v>
@@ -4082,13 +4085,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q47" s="9">
         <v>46049</v>
@@ -4108,7 +4111,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B48" s="5">
         <v>46073.5744191088</v>
@@ -4120,16 +4123,16 @@
         <v>46195.607078368055</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I48" s="5">
         <v>46065</v>
@@ -4147,13 +4150,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q48" s="5">
         <v>46065</v>
@@ -4173,7 +4176,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B49" s="9">
         <v>46073.57441700231</v>
@@ -4185,16 +4188,16 @@
         <v>46122.65480131944</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I49" s="9">
         <v>46083</v>
@@ -4212,13 +4215,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q49" s="9">
         <v>46083</v>
@@ -4238,7 +4241,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B50" s="5">
         <v>46073.57441726852</v>
@@ -4250,7 +4253,7 @@
         <v>46205.488724166666</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4274,7 +4277,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4291,7 +4294,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B51" s="9">
         <v>46073.57441785879</v>
@@ -4303,7 +4306,7 @@
         <v>46223.81110523148</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4312,7 +4315,7 @@
         <v>70</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I51" s="9">
         <v>46091</v>
@@ -4330,13 +4333,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q51" s="9">
         <v>46097</v>
@@ -4356,7 +4359,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B52" s="5">
         <v>46073.57441813657</v>
@@ -4368,7 +4371,7 @@
         <v>46223.81110195602</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4377,7 +4380,7 @@
         <v>70</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I52" s="5">
         <v>46098</v>
@@ -4395,13 +4398,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q52" s="5">
         <v>46098</v>
@@ -4421,7 +4424,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B53" s="9">
         <v>46073.574418379634</v>
@@ -4433,7 +4436,7 @@
         <v>46223.8110984838</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
@@ -4442,7 +4445,7 @@
         <v>70</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I53" s="9">
         <v>46099</v>
@@ -4460,13 +4463,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q53" s="9">
         <v>46099</v>
@@ -4486,7 +4489,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B54" s="5">
         <v>46073.57441863426</v>
@@ -4498,7 +4501,7 @@
         <v>46223.81109472222</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -4507,7 +4510,7 @@
         <v>70</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I54" s="5">
         <v>46100</v>
@@ -4525,13 +4528,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q54" s="5">
         <v>46100</v>
@@ -4551,7 +4554,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B55" s="9">
         <v>46073.57441893518</v>
@@ -4563,7 +4566,7 @@
         <v>46223.81109128472</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
@@ -4572,7 +4575,7 @@
         <v>70</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9">
@@ -4588,13 +4591,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q55" s="9">
         <v>46101</v>
@@ -4614,7 +4617,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B56" s="5">
         <v>46073.57441920139</v>
@@ -4626,7 +4629,7 @@
         <v>46223.81108594907</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -4635,7 +4638,7 @@
         <v>70</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -4651,13 +4654,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q56" s="5">
         <v>46105</v>
@@ -4677,7 +4680,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B57" s="9">
         <v>46073.574416874995</v>
@@ -4687,7 +4690,7 @@
         <v>46213.509536840276</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>25</v>
@@ -4711,7 +4714,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -4724,7 +4727,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B58" s="5">
         <v>46073.57441722222</v>
@@ -4734,16 +4737,16 @@
         <v>46225.55231209491</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
@@ -4753,19 +4756,19 @@
         <v>26</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q58" s="5">
         <v>46106</v>
@@ -4780,12 +4783,12 @@
         <v>0</v>
       </c>
       <c r="U58" s="12" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B59" s="9">
         <v>46073.57441747685</v>
@@ -4797,7 +4800,7 @@
         <v>46223.811153622686</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -4806,7 +4809,7 @@
         <v>70</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="9">
@@ -4822,13 +4825,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q59" s="9">
         <v>46107</v>
@@ -4848,7 +4851,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B60" s="5">
         <v>46073.57441775463</v>
@@ -4860,16 +4863,16 @@
         <v>46224.66064472222</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I60" s="5">
         <v>46108</v>
@@ -4887,13 +4890,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q60" s="5">
         <v>46080</v>
@@ -4902,18 +4905,18 @@
         <v>46108</v>
       </c>
       <c r="S60" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T60" s="6">
         <v>1</v>
       </c>
       <c r="U60" s="12" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B61" s="9">
         <v>46073.57441800926</v>
@@ -4923,16 +4926,16 @@
         <v>46205.89695172454</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I61" s="9">
         <v>46111</v>
@@ -4950,13 +4953,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q61" s="9">
         <v>46111</v>
@@ -4971,12 +4974,12 @@
         <v>0</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B62" s="5">
         <v>46073.574418275464</v>
@@ -4986,7 +4989,7 @@
         <v>46090.70182164352</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5010,7 +5013,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5023,7 +5026,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B63" s="9">
         <v>46073.57441857639</v>
@@ -5033,16 +5036,16 @@
         <v>46121.167010115736</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I63" s="9">
         <v>46112</v>
@@ -5060,13 +5063,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q63" s="9">
         <v>46120</v>
@@ -5081,12 +5084,12 @@
         <v>0</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B64" s="5">
         <v>46073.57441884259</v>
@@ -5096,16 +5099,16 @@
         <v>46121.16701012732</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I64" s="5">
         <v>46112</v>
@@ -5123,13 +5126,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q64" s="5">
         <v>46120</v>
@@ -5144,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001508 - XEMORTIZ STOCK.xlsx
+++ b/data/50001508 - XEMORTIZ STOCK.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="245">
   <si>
     <t>50001508 - XEMORTIZ STOCK</t>
   </si>
@@ -453,6 +453,9 @@
     <t>Plano Definitivos,Plano Preliminar,Check Planos,Check pruebas FAT</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
     <t>1213377491559682</t>
   </si>
   <si>
@@ -513,6 +516,18 @@
     <t>Ingenieria y diseñoo:,RE-PINTADO</t>
   </si>
   <si>
+    <t>1216916625315556</t>
+  </si>
+  <si>
+    <t>4232 - ZVN 1-6-25/2</t>
+  </si>
+  <si>
+    <t>1216916625315557</t>
+  </si>
+  <si>
+    <t>4233 - ZVN 1-7-42/2</t>
+  </si>
+  <si>
     <t>1213377491559684</t>
   </si>
   <si>
@@ -721,9 +736,6 @@
   </si>
   <si>
     <t>Embalaje,Logistica:</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1213333053701064</t>
@@ -1301,7 +1313,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U64"/>
+  <dimension ref="A1:U66"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -3262,7 +3274,7 @@
         <v>46198.565049375</v>
       </c>
       <c r="D34" s="5">
-        <v>46198.565061875</v>
+        <v>46230.60689199074</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3300,13 +3312,13 @@
       <c r="T34" s="6">
         <v>1</v>
       </c>
-      <c r="U34" s="7" t="s">
-        <v>27</v>
+      <c r="U34" s="12" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B35" s="9">
         <v>46073.57441901621</v>
@@ -3318,16 +3330,16 @@
         <v>46197.70911202546</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I35" s="9">
         <v>46041</v>
@@ -3351,7 +3363,7 @@
         <v>58</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q35" s="9">
         <v>46045</v>
@@ -3371,7 +3383,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B36" s="5">
         <v>46073.57441695602</v>
@@ -3383,16 +3395,16 @@
         <v>46197.70914525463</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I36" s="5">
         <v>46059</v>
@@ -3413,10 +3425,10 @@
         <v>130</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q36" s="5">
         <v>46065</v>
@@ -3436,7 +3448,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B37" s="9">
         <v>46090.69622997685</v>
@@ -3448,16 +3460,16 @@
         <v>46108.76809931713</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I37" s="9">
         <v>46066</v>
@@ -3478,10 +3490,10 @@
         <v>130</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q37" s="9">
         <v>46066</v>
@@ -3501,28 +3513,26 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B38" s="5">
         <v>46090.69645336806</v>
       </c>
-      <c r="C38" s="5">
-        <v>46198.565030763886</v>
-      </c>
+      <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46198.565049791665</v>
+        <v>46230.60721100694</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I38" s="5">
         <v>46104</v>
@@ -3543,10 +3553,10 @@
         <v>130</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q38" s="5">
         <v>46104</v>
@@ -3566,29 +3576,35 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B39" s="9">
-        <v>46073.57441724537</v>
+        <v>46230.6059065625</v>
       </c>
       <c r="C39" s="9">
-        <v>46111.7988809838</v>
+        <v>46230.60687260417</v>
       </c>
       <c r="D39" s="9">
-        <v>46111.79889361111</v>
+        <v>46230.60708903935</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H39" s="10"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="10"/>
+        <v>149</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="I39" s="9">
+        <v>46104</v>
+      </c>
+      <c r="J39" s="9">
+        <v>46104</v>
+      </c>
       <c r="K39" s="10" t="s">
         <v>26</v>
       </c>
@@ -3596,13 +3612,13 @@
         <v>26</v>
       </c>
       <c r="M39" s="10" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>26</v>
+        <v>148</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>154</v>
+        <v>26</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3610,25 +3626,19 @@
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
       <c r="S39" s="10"/>
-      <c r="T39" s="10">
-        <v>1</v>
-      </c>
-      <c r="U39" s="7" t="s">
-        <v>27</v>
-      </c>
+      <c r="T39" s="10"/>
+      <c r="U39" s="10"/>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>155</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.57441746528</v>
-      </c>
-      <c r="C40" s="5">
-        <v>46111.79882116898</v>
-      </c>
+        <v>46230.6059374537</v>
+      </c>
+      <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46111.798837326394</v>
+        <v>46230.607092314815</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>156</v>
@@ -3637,16 +3647,16 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="I40" s="5">
-        <v>46072</v>
+        <v>46104</v>
       </c>
       <c r="J40" s="5">
-        <v>46073</v>
+        <v>46104</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>26</v>
@@ -3658,61 +3668,45 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>127</v>
+        <v>26</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q40" s="5">
-        <v>46073</v>
-      </c>
-      <c r="R40" s="5">
-        <v>46072</v>
-      </c>
-      <c r="S40" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="T40" s="6">
-        <v>1</v>
-      </c>
-      <c r="U40" s="7" t="s">
-        <v>27</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q40" s="6"/>
+      <c r="R40" s="6"/>
+      <c r="S40" s="6"/>
+      <c r="T40" s="6"/>
+      <c r="U40" s="6"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B41" s="9">
-        <v>46073.57441769676</v>
+        <v>46073.57441724537</v>
       </c>
       <c r="C41" s="9">
-        <v>46111.7988649537</v>
+        <v>46111.7988809838</v>
       </c>
       <c r="D41" s="9">
-        <v>46111.79888084491</v>
+        <v>46111.79889361111</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="I41" s="9">
-        <v>46076</v>
-      </c>
-      <c r="J41" s="9">
-        <v>46077</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H41" s="10"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
       <c r="K41" s="10" t="s">
         <v>26</v>
       </c>
@@ -3720,26 +3714,20 @@
         <v>26</v>
       </c>
       <c r="M41" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>153</v>
+        <v>26</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q41" s="9">
-        <v>46077</v>
-      </c>
-      <c r="R41" s="9">
-        <v>46076</v>
-      </c>
-      <c r="S41" s="11" t="s">
-        <v>32</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q41" s="10"/>
+      <c r="R41" s="10"/>
+      <c r="S41" s="10"/>
       <c r="T41" s="10">
         <v>1</v>
       </c>
@@ -3749,83 +3737,99 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B42" s="5">
+        <v>46073.57441746528</v>
+      </c>
+      <c r="C42" s="5">
+        <v>46111.79882116898</v>
+      </c>
+      <c r="D42" s="5">
+        <v>46111.798837326394</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="I42" s="5">
+        <v>46072</v>
+      </c>
+      <c r="J42" s="5">
+        <v>46073</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N42" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="O42" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="P42" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="B42" s="5">
-        <v>46073.57441792824</v>
-      </c>
-      <c r="C42" s="5">
-        <v>46195.91189378472</v>
-      </c>
-      <c r="D42" s="5">
-        <v>46196.8510114699</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="6"/>
-      <c r="K42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M42" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="N42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O42" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="P42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="6"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
+      <c r="Q42" s="5">
+        <v>46073</v>
+      </c>
+      <c r="R42" s="5">
+        <v>46072</v>
+      </c>
+      <c r="S42" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="T42" s="6">
+        <v>1</v>
+      </c>
+      <c r="U42" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="B43" s="9">
+        <v>46073.57441769676</v>
+      </c>
+      <c r="C43" s="9">
+        <v>46111.7988649537</v>
+      </c>
+      <c r="D43" s="9">
+        <v>46111.79888084491</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="B43" s="9">
-        <v>46073.574418159726</v>
-      </c>
-      <c r="C43" s="9">
-        <v>46107.72750388889</v>
-      </c>
-      <c r="D43" s="9">
-        <v>46196.850968819446</v>
-      </c>
-      <c r="E43" s="10" t="s">
+      <c r="H43" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>170</v>
-      </c>
       <c r="I43" s="9">
-        <v>46078</v>
+        <v>46076</v>
       </c>
       <c r="J43" s="9">
-        <v>46080</v>
+        <v>46077</v>
       </c>
       <c r="K43" s="10" t="s">
         <v>26</v>
@@ -3837,19 +3841,19 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="Q43" s="9">
-        <v>46080</v>
+        <v>46077</v>
       </c>
       <c r="R43" s="9">
-        <v>46078</v>
+        <v>46076</v>
       </c>
       <c r="S43" s="11" t="s">
         <v>32</v>
@@ -3863,35 +3867,29 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.574418379634</v>
+        <v>46073.57441792824</v>
       </c>
       <c r="C44" s="5">
-        <v>46146.563449814814</v>
+        <v>46195.91189378472</v>
       </c>
       <c r="D44" s="5">
-        <v>46195.911566111114</v>
+        <v>46196.8510114699</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="I44" s="5">
-        <v>46083</v>
-      </c>
-      <c r="J44" s="5">
-        <v>46087</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6"/>
       <c r="K44" s="6" t="s">
         <v>26</v>
       </c>
@@ -3899,87 +3897,77 @@
         <v>26</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>165</v>
+        <v>26</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q44" s="5">
-        <v>46087</v>
-      </c>
-      <c r="R44" s="5">
-        <v>46083</v>
-      </c>
-      <c r="S44" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="T44" s="6">
-        <v>1</v>
-      </c>
-      <c r="U44" s="7" t="s">
-        <v>27</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q44" s="6"/>
+      <c r="R44" s="6"/>
+      <c r="S44" s="6"/>
+      <c r="T44" s="6"/>
+      <c r="U44" s="6"/>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="B45" s="9">
+        <v>46073.574418159726</v>
+      </c>
+      <c r="C45" s="9">
+        <v>46107.72750388889</v>
+      </c>
+      <c r="D45" s="9">
+        <v>46196.850968819446</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="I45" s="9">
+        <v>46078</v>
+      </c>
+      <c r="J45" s="9">
+        <v>46080</v>
+      </c>
+      <c r="K45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N45" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="O45" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="P45" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="B45" s="9">
-        <v>46073.57441861111</v>
-      </c>
-      <c r="C45" s="9">
-        <v>46195.91187329861</v>
-      </c>
-      <c r="D45" s="9">
-        <v>46196.91052092593</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="F45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G45" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="I45" s="9">
-        <v>46090</v>
-      </c>
-      <c r="J45" s="9">
-        <v>46090</v>
-      </c>
-      <c r="K45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N45" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="O45" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="P45" s="10" t="s">
-        <v>179</v>
-      </c>
       <c r="Q45" s="9">
-        <v>46090</v>
+        <v>46080</v>
       </c>
       <c r="R45" s="9">
-        <v>46090</v>
+        <v>46078</v>
       </c>
       <c r="S45" s="11" t="s">
         <v>32</v>
@@ -3993,50 +3981,62 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B46" s="5">
+        <v>46073.574418379634</v>
+      </c>
+      <c r="C46" s="5">
+        <v>46146.563449814814</v>
+      </c>
+      <c r="D46" s="5">
+        <v>46195.911566111114</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="I46" s="5">
+        <v>46083</v>
+      </c>
+      <c r="J46" s="5">
+        <v>46087</v>
+      </c>
+      <c r="K46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N46" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="O46" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="P46" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="B46" s="5">
-        <v>46073.57441885417</v>
-      </c>
-      <c r="C46" s="5">
-        <v>46195.60707819444</v>
-      </c>
-      <c r="D46" s="5">
-        <v>46214.320753622684</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="6"/>
-      <c r="K46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M46" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="N46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O46" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="P46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q46" s="6"/>
-      <c r="R46" s="6"/>
-      <c r="S46" s="6"/>
+      <c r="Q46" s="5">
+        <v>46087</v>
+      </c>
+      <c r="R46" s="5">
+        <v>46083</v>
+      </c>
+      <c r="S46" s="11" t="s">
+        <v>32</v>
+      </c>
       <c r="T46" s="6">
         <v>1</v>
       </c>
@@ -4046,58 +4046,58 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B47" s="9">
+        <v>46073.57441861111</v>
+      </c>
+      <c r="C47" s="9">
+        <v>46195.91187329861</v>
+      </c>
+      <c r="D47" s="9">
+        <v>46196.91052092593</v>
+      </c>
+      <c r="E47" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="B47" s="9">
-        <v>46073.574416724536</v>
-      </c>
-      <c r="C47" s="9">
-        <v>46127.65026820602</v>
-      </c>
-      <c r="D47" s="9">
-        <v>46127.65040571759</v>
-      </c>
-      <c r="E47" s="10" t="s">
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="I47" s="9">
+        <v>46090</v>
+      </c>
+      <c r="J47" s="9">
+        <v>46090</v>
+      </c>
+      <c r="K47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N47" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="O47" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="F47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="I47" s="9">
-        <v>46049</v>
-      </c>
-      <c r="J47" s="9">
-        <v>46049</v>
-      </c>
-      <c r="K47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N47" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="O47" s="10" t="s">
-        <v>95</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>184</v>
       </c>
       <c r="Q47" s="9">
-        <v>46049</v>
+        <v>46090</v>
       </c>
       <c r="R47" s="9">
-        <v>46049</v>
+        <v>46090</v>
       </c>
       <c r="S47" s="11" t="s">
         <v>32</v>
@@ -4114,59 +4114,47 @@
         <v>185</v>
       </c>
       <c r="B48" s="5">
-        <v>46073.5744191088</v>
+        <v>46073.57441885417</v>
       </c>
       <c r="C48" s="5">
-        <v>46195.607060462964</v>
+        <v>46195.60707819444</v>
       </c>
       <c r="D48" s="5">
-        <v>46195.607078368055</v>
+        <v>46214.320753622684</v>
       </c>
       <c r="E48" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M48" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O48" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="F48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="I48" s="5">
-        <v>46065</v>
-      </c>
-      <c r="J48" s="5">
-        <v>46065</v>
-      </c>
-      <c r="K48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N48" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="O48" s="6" t="s">
-        <v>104</v>
-      </c>
       <c r="P48" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q48" s="5">
-        <v>46065</v>
-      </c>
-      <c r="R48" s="5">
-        <v>46065</v>
-      </c>
-      <c r="S48" s="11" t="s">
-        <v>32</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q48" s="6"/>
+      <c r="R48" s="6"/>
+      <c r="S48" s="6"/>
       <c r="T48" s="6">
         <v>1</v>
       </c>
@@ -4176,58 +4164,58 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="B49" s="9">
+        <v>46073.574416724536</v>
+      </c>
+      <c r="C49" s="9">
+        <v>46127.65026820602</v>
+      </c>
+      <c r="D49" s="9">
+        <v>46127.65040571759</v>
+      </c>
+      <c r="E49" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="B49" s="9">
-        <v>46073.57441700231</v>
-      </c>
-      <c r="C49" s="9">
-        <v>46122.654781053236</v>
-      </c>
-      <c r="D49" s="9">
-        <v>46122.65480131944</v>
-      </c>
-      <c r="E49" s="10" t="s">
+      <c r="F49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="I49" s="9">
+        <v>46049</v>
+      </c>
+      <c r="J49" s="9">
+        <v>46049</v>
+      </c>
+      <c r="K49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N49" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="O49" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="P49" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="F49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G49" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="I49" s="9">
-        <v>46083</v>
-      </c>
-      <c r="J49" s="9">
-        <v>46083</v>
-      </c>
-      <c r="K49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N49" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="O49" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="P49" s="10" t="s">
-        <v>190</v>
-      </c>
       <c r="Q49" s="9">
-        <v>46083</v>
+        <v>46049</v>
       </c>
       <c r="R49" s="9">
-        <v>46083</v>
+        <v>46049</v>
       </c>
       <c r="S49" s="11" t="s">
         <v>32</v>
@@ -4241,50 +4229,62 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B50" s="5">
+        <v>46073.5744191088</v>
+      </c>
+      <c r="C50" s="5">
+        <v>46195.607060462964</v>
+      </c>
+      <c r="D50" s="5">
+        <v>46195.607078368055</v>
+      </c>
+      <c r="E50" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="B50" s="5">
-        <v>46073.57441726852</v>
-      </c>
-      <c r="C50" s="5">
-        <v>46205.48871315972</v>
-      </c>
-      <c r="D50" s="5">
-        <v>46205.488724166666</v>
-      </c>
-      <c r="E50" s="6" t="s">
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="I50" s="5">
+        <v>46065</v>
+      </c>
+      <c r="J50" s="5">
+        <v>46065</v>
+      </c>
+      <c r="K50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N50" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="O50" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="P50" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="6"/>
-      <c r="K50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M50" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="N50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O50" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="P50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q50" s="6"/>
-      <c r="R50" s="6"/>
-      <c r="S50" s="6"/>
+      <c r="Q50" s="5">
+        <v>46065</v>
+      </c>
+      <c r="R50" s="5">
+        <v>46065</v>
+      </c>
+      <c r="S50" s="11" t="s">
+        <v>32</v>
+      </c>
       <c r="T50" s="6">
         <v>1</v>
       </c>
@@ -4294,58 +4294,58 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="B51" s="9">
+        <v>46073.57441700231</v>
+      </c>
+      <c r="C51" s="9">
+        <v>46122.654781053236</v>
+      </c>
+      <c r="D51" s="9">
+        <v>46122.65480131944</v>
+      </c>
+      <c r="E51" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="B51" s="9">
-        <v>46073.57441785879</v>
-      </c>
-      <c r="C51" s="9">
-        <v>46197.50546392361</v>
-      </c>
-      <c r="D51" s="9">
-        <v>46223.81110523148</v>
-      </c>
-      <c r="E51" s="10" t="s">
+      <c r="F51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="H51" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="I51" s="9">
+        <v>46083</v>
+      </c>
+      <c r="J51" s="9">
+        <v>46083</v>
+      </c>
+      <c r="K51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N51" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="O51" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="P51" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="F51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I51" s="9">
-        <v>46091</v>
-      </c>
-      <c r="J51" s="9">
-        <v>46097</v>
-      </c>
-      <c r="K51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N51" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="O51" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="P51" s="10" t="s">
-        <v>196</v>
-      </c>
       <c r="Q51" s="9">
-        <v>46097</v>
+        <v>46083</v>
       </c>
       <c r="R51" s="9">
-        <v>46091</v>
+        <v>46083</v>
       </c>
       <c r="S51" s="11" t="s">
         <v>32</v>
@@ -4359,62 +4359,50 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B52" s="5">
+        <v>46073.57441726852</v>
+      </c>
+      <c r="C52" s="5">
+        <v>46205.48871315972</v>
+      </c>
+      <c r="D52" s="5">
+        <v>46205.488724166666</v>
+      </c>
+      <c r="E52" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="B52" s="5">
-        <v>46073.57441813657</v>
-      </c>
-      <c r="C52" s="5">
-        <v>46197.50555307871</v>
-      </c>
-      <c r="D52" s="5">
-        <v>46223.81110195602</v>
-      </c>
-      <c r="E52" s="6" t="s">
+      <c r="F52" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H52" s="6"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="6"/>
+      <c r="K52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M52" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O52" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="I52" s="5">
-        <v>46098</v>
-      </c>
-      <c r="J52" s="5">
-        <v>46098</v>
-      </c>
-      <c r="K52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N52" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="O52" s="6" t="s">
-        <v>199</v>
-      </c>
       <c r="P52" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q52" s="5">
-        <v>46098</v>
-      </c>
-      <c r="R52" s="5">
-        <v>46098</v>
-      </c>
-      <c r="S52" s="11" t="s">
-        <v>32</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q52" s="6"/>
+      <c r="R52" s="6"/>
+      <c r="S52" s="6"/>
       <c r="T52" s="6">
         <v>1</v>
       </c>
@@ -4424,19 +4412,19 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B53" s="9">
-        <v>46073.574418379634</v>
+        <v>46073.57441785879</v>
       </c>
       <c r="C53" s="9">
-        <v>46197.50557114583</v>
+        <v>46197.50546392361</v>
       </c>
       <c r="D53" s="9">
-        <v>46223.8110984838</v>
+        <v>46223.81110523148</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
@@ -4448,10 +4436,10 @@
         <v>71</v>
       </c>
       <c r="I53" s="9">
-        <v>46099</v>
+        <v>46091</v>
       </c>
       <c r="J53" s="9">
-        <v>46099</v>
+        <v>46097</v>
       </c>
       <c r="K53" s="10" t="s">
         <v>26</v>
@@ -4463,19 +4451,19 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q53" s="9">
-        <v>46099</v>
+        <v>46097</v>
       </c>
       <c r="R53" s="9">
-        <v>46099</v>
+        <v>46091</v>
       </c>
       <c r="S53" s="11" t="s">
         <v>32</v>
@@ -4489,19 +4477,19 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.57441863426</v>
+        <v>46073.57441813657</v>
       </c>
       <c r="C54" s="5">
-        <v>46197.505863240745</v>
+        <v>46197.50555307871</v>
       </c>
       <c r="D54" s="5">
-        <v>46223.81109472222</v>
+        <v>46223.81110195602</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -4513,10 +4501,10 @@
         <v>71</v>
       </c>
       <c r="I54" s="5">
-        <v>46100</v>
+        <v>46098</v>
       </c>
       <c r="J54" s="5">
-        <v>46100</v>
+        <v>46098</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>26</v>
@@ -4528,19 +4516,19 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="Q54" s="5">
-        <v>46100</v>
+        <v>46098</v>
       </c>
       <c r="R54" s="5">
-        <v>46100</v>
+        <v>46098</v>
       </c>
       <c r="S54" s="11" t="s">
         <v>32</v>
@@ -4554,19 +4542,19 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="B55" s="9">
+        <v>46073.574418379634</v>
+      </c>
+      <c r="C55" s="9">
+        <v>46197.50557114583</v>
+      </c>
+      <c r="D55" s="9">
+        <v>46223.8110984838</v>
+      </c>
+      <c r="E55" s="10" t="s">
         <v>207</v>
-      </c>
-      <c r="B55" s="9">
-        <v>46073.57441893518</v>
-      </c>
-      <c r="C55" s="9">
-        <v>46197.505959166665</v>
-      </c>
-      <c r="D55" s="9">
-        <v>46223.81109128472</v>
-      </c>
-      <c r="E55" s="10" t="s">
-        <v>150</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
@@ -4577,9 +4565,11 @@
       <c r="H55" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="I55" s="10"/>
+      <c r="I55" s="9">
+        <v>46099</v>
+      </c>
       <c r="J55" s="9">
-        <v>46101</v>
+        <v>46099</v>
       </c>
       <c r="K55" s="10" t="s">
         <v>26</v>
@@ -4591,19 +4581,19 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>208</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="Q55" s="9">
-        <v>46101</v>
+        <v>46099</v>
       </c>
       <c r="R55" s="9">
-        <v>46101</v>
+        <v>46099</v>
       </c>
       <c r="S55" s="11" t="s">
         <v>32</v>
@@ -4617,19 +4607,19 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B56" s="5">
+        <v>46073.57441863426</v>
+      </c>
+      <c r="C56" s="5">
+        <v>46197.505863240745</v>
+      </c>
+      <c r="D56" s="5">
+        <v>46223.81109472222</v>
+      </c>
+      <c r="E56" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="B56" s="5">
-        <v>46073.57441920139</v>
-      </c>
-      <c r="C56" s="5">
-        <v>46205.488692812505</v>
-      </c>
-      <c r="D56" s="5">
-        <v>46223.81108594907</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -4640,9 +4630,11 @@
       <c r="H56" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="I56" s="6"/>
+      <c r="I56" s="5">
+        <v>46100</v>
+      </c>
       <c r="J56" s="5">
-        <v>46105</v>
+        <v>46100</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>26</v>
@@ -4654,19 +4646,19 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>147</v>
+        <v>211</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="Q56" s="5">
-        <v>46105</v>
+        <v>46100</v>
       </c>
       <c r="R56" s="5">
-        <v>46105</v>
+        <v>46100</v>
       </c>
       <c r="S56" s="11" t="s">
         <v>32</v>
@@ -4680,141 +4672,153 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="B57" s="9">
+        <v>46073.57441893518</v>
+      </c>
+      <c r="C57" s="9">
+        <v>46197.505959166665</v>
+      </c>
+      <c r="D57" s="9">
+        <v>46223.81109128472</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H57" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="I57" s="10"/>
+      <c r="J57" s="9">
+        <v>46101</v>
+      </c>
+      <c r="K57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N57" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="O57" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="B57" s="9">
-        <v>46073.574416874995</v>
-      </c>
-      <c r="C57" s="10"/>
-      <c r="D57" s="9">
-        <v>46213.509536840276</v>
-      </c>
-      <c r="E57" s="10" t="s">
+      <c r="P57" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="F57" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H57" s="10"/>
-      <c r="I57" s="10"/>
-      <c r="J57" s="10"/>
-      <c r="K57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M57" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="N57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O57" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="P57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q57" s="10"/>
-      <c r="R57" s="10"/>
-      <c r="S57" s="10"/>
-      <c r="T57" s="10"/>
-      <c r="U57" s="10"/>
+      <c r="Q57" s="9">
+        <v>46101</v>
+      </c>
+      <c r="R57" s="9">
+        <v>46101</v>
+      </c>
+      <c r="S57" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="T57" s="10">
+        <v>1</v>
+      </c>
+      <c r="U57" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B58" s="5">
+        <v>46073.57441920139</v>
+      </c>
+      <c r="C58" s="5">
+        <v>46205.488692812505</v>
+      </c>
+      <c r="D58" s="5">
+        <v>46230.60689228009</v>
+      </c>
+      <c r="E58" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="B58" s="5">
-        <v>46073.57441722222</v>
-      </c>
-      <c r="C58" s="6"/>
-      <c r="D58" s="5">
-        <v>46225.55231209491</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>217</v>
-      </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>218</v>
+        <v>70</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>219</v>
+        <v>71</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
-        <v>46106</v>
+        <v>46105</v>
       </c>
       <c r="K58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>220</v>
+        <v>26</v>
       </c>
       <c r="M58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>211</v>
+        <v>148</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="Q58" s="5">
-        <v>46106</v>
+        <v>46105</v>
       </c>
       <c r="R58" s="5">
-        <v>46106</v>
+        <v>46105</v>
       </c>
       <c r="S58" s="11" t="s">
         <v>32</v>
       </c>
       <c r="T58" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U58" s="12" t="s">
-        <v>222</v>
+        <v>132</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B59" s="9">
-        <v>46073.57441747685</v>
-      </c>
-      <c r="C59" s="9">
-        <v>46213.509524988425</v>
-      </c>
+        <v>46073.574416874995</v>
+      </c>
+      <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46223.811153622686</v>
+        <v>46213.509536840276</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>71</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H59" s="10"/>
       <c r="I59" s="10"/>
-      <c r="J59" s="9">
-        <v>46107</v>
-      </c>
+      <c r="J59" s="10"/>
       <c r="K59" s="10" t="s">
         <v>26</v>
       </c>
@@ -4822,236 +4826,240 @@
         <v>26</v>
       </c>
       <c r="M59" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>214</v>
+        <v>26</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="Q59" s="9">
-        <v>46107</v>
-      </c>
-      <c r="R59" s="9">
-        <v>46107</v>
-      </c>
-      <c r="S59" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="T59" s="10">
-        <v>1</v>
-      </c>
-      <c r="U59" s="7" t="s">
-        <v>27</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q59" s="10"/>
+      <c r="R59" s="10"/>
+      <c r="S59" s="10"/>
+      <c r="T59" s="10"/>
+      <c r="U59" s="10"/>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B60" s="5">
+        <v>46073.57441722222</v>
+      </c>
+      <c r="C60" s="6"/>
+      <c r="D60" s="5">
+        <v>46225.55231209491</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="I60" s="6"/>
+      <c r="J60" s="5">
+        <v>46106</v>
+      </c>
+      <c r="K60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L60" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="M60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N60" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="O60" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="P60" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="B60" s="5">
-        <v>46073.57441775463</v>
-      </c>
-      <c r="C60" s="5">
-        <v>46205.89693434028</v>
-      </c>
-      <c r="D60" s="5">
-        <v>46224.66064472222</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="I60" s="5">
-        <v>46108</v>
-      </c>
-      <c r="J60" s="5">
-        <v>46108</v>
-      </c>
-      <c r="K60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N60" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="O60" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="P60" s="6" t="s">
-        <v>228</v>
-      </c>
       <c r="Q60" s="5">
-        <v>46080</v>
+        <v>46106</v>
       </c>
       <c r="R60" s="5">
-        <v>46108</v>
-      </c>
-      <c r="S60" s="7" t="s">
-        <v>92</v>
+        <v>46106</v>
+      </c>
+      <c r="S60" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T60" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U60" s="12" t="s">
-        <v>222</v>
+        <v>132</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="B61" s="9">
+        <v>46073.57441747685</v>
+      </c>
+      <c r="C61" s="9">
+        <v>46213.509524988425</v>
+      </c>
+      <c r="D61" s="9">
+        <v>46223.811153622686</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G61" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H61" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="I61" s="10"/>
+      <c r="J61" s="9">
+        <v>46107</v>
+      </c>
+      <c r="K61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N61" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="O61" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="P61" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="B61" s="9">
-        <v>46073.57441800926</v>
-      </c>
-      <c r="C61" s="10"/>
-      <c r="D61" s="9">
-        <v>46205.89695172454</v>
-      </c>
-      <c r="E61" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="F61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G61" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="I61" s="9">
-        <v>46111</v>
-      </c>
-      <c r="J61" s="9">
-        <v>46111</v>
-      </c>
-      <c r="K61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N61" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="O61" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="P61" s="10" t="s">
-        <v>231</v>
-      </c>
       <c r="Q61" s="9">
-        <v>46111</v>
+        <v>46107</v>
       </c>
       <c r="R61" s="9">
-        <v>46111</v>
+        <v>46107</v>
       </c>
       <c r="S61" s="11" t="s">
         <v>32</v>
       </c>
       <c r="T61" s="10">
-        <v>0</v>
-      </c>
-      <c r="U61" s="12" t="s">
-        <v>222</v>
+        <v>1</v>
+      </c>
+      <c r="U61" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B62" s="5">
+        <v>46073.57441775463</v>
+      </c>
+      <c r="C62" s="5">
+        <v>46205.89693434028</v>
+      </c>
+      <c r="D62" s="5">
+        <v>46224.66064472222</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="I62" s="5">
+        <v>46108</v>
+      </c>
+      <c r="J62" s="5">
+        <v>46108</v>
+      </c>
+      <c r="K62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N62" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="O62" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="P62" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="B62" s="5">
-        <v>46073.574418275464</v>
-      </c>
-      <c r="C62" s="6"/>
-      <c r="D62" s="5">
-        <v>46090.70182164352</v>
-      </c>
-      <c r="E62" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="F62" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H62" s="6"/>
-      <c r="I62" s="6"/>
-      <c r="J62" s="6"/>
-      <c r="K62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M62" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="N62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O62" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="P62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q62" s="6"/>
-      <c r="R62" s="6"/>
-      <c r="S62" s="6"/>
-      <c r="T62" s="6"/>
-      <c r="U62" s="6"/>
+      <c r="Q62" s="5">
+        <v>46080</v>
+      </c>
+      <c r="R62" s="5">
+        <v>46108</v>
+      </c>
+      <c r="S62" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="T62" s="6">
+        <v>1</v>
+      </c>
+      <c r="U62" s="12" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B63" s="9">
-        <v>46073.57441857639</v>
+        <v>46073.57441800926</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46121.167010115736</v>
+        <v>46205.89695172454</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>237</v>
+        <v>174</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>238</v>
+        <v>175</v>
       </c>
       <c r="I63" s="9">
-        <v>46112</v>
+        <v>46111</v>
       </c>
       <c r="J63" s="9">
-        <v>46120</v>
+        <v>46111</v>
       </c>
       <c r="K63" s="10" t="s">
         <v>26</v>
@@ -5063,19 +5071,19 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q63" s="9">
-        <v>46120</v>
+        <v>46111</v>
       </c>
       <c r="R63" s="9">
-        <v>46112</v>
+        <v>46111</v>
       </c>
       <c r="S63" s="11" t="s">
         <v>32</v>
@@ -5083,70 +5091,180 @@
       <c r="T63" s="10">
         <v>0</v>
       </c>
-      <c r="U63" s="11" t="s">
-        <v>93</v>
+      <c r="U63" s="12" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.57441884259</v>
+        <v>46073.574418275464</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
+        <v>46090.70182164352</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H64" s="6"/>
+      <c r="I64" s="6"/>
+      <c r="J64" s="6"/>
+      <c r="K64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M64" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O64" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="P64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q64" s="6"/>
+      <c r="R64" s="6"/>
+      <c r="S64" s="6"/>
+      <c r="T64" s="6"/>
+      <c r="U64" s="6"/>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A65" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="B65" s="9">
+        <v>46073.57441857639</v>
+      </c>
+      <c r="C65" s="10"/>
+      <c r="D65" s="9">
+        <v>46121.167010115736</v>
+      </c>
+      <c r="E65" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="F65" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G65" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="H65" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="I65" s="9">
+        <v>46112</v>
+      </c>
+      <c r="J65" s="9">
+        <v>46120</v>
+      </c>
+      <c r="K65" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L65" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M65" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N65" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="O65" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="P65" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q65" s="9">
+        <v>46120</v>
+      </c>
+      <c r="R65" s="9">
+        <v>46112</v>
+      </c>
+      <c r="S65" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="T65" s="10">
+        <v>0</v>
+      </c>
+      <c r="U65" s="11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B66" s="5">
+        <v>46073.57441884259</v>
+      </c>
+      <c r="C66" s="6"/>
+      <c r="D66" s="5">
         <v>46121.16701012732</v>
       </c>
-      <c r="E64" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="F64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G64" s="6" t="s">
+      <c r="E66" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="I66" s="5">
+        <v>46112</v>
+      </c>
+      <c r="J66" s="5">
+        <v>46120</v>
+      </c>
+      <c r="K66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N66" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="H64" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="I64" s="5">
+      <c r="O66" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="P66" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q66" s="5">
+        <v>46120</v>
+      </c>
+      <c r="R66" s="5">
         <v>46112</v>
       </c>
-      <c r="J64" s="5">
-        <v>46120</v>
-      </c>
-      <c r="K64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N64" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="O64" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q64" s="5">
-        <v>46120</v>
-      </c>
-      <c r="R64" s="5">
-        <v>46112</v>
-      </c>
-      <c r="S64" s="11" t="s">
+      <c r="S66" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="T64" s="6">
+      <c r="T66" s="6">
         <v>0</v>
       </c>
-      <c r="U64" s="11" t="s">
+      <c r="U66" s="11" t="s">
         <v>93</v>
       </c>
     </row>

--- a/data/50001508 - XEMORTIZ STOCK.xlsx
+++ b/data/50001508 - XEMORTIZ STOCK.xlsx
@@ -3274,7 +3274,7 @@
         <v>46198.565049375</v>
       </c>
       <c r="D34" s="5">
-        <v>46230.60689199074</v>
+        <v>46230.721807141206</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3518,9 +3518,11 @@
       <c r="B38" s="5">
         <v>46090.69645336806</v>
       </c>
-      <c r="C38" s="6"/>
+      <c r="C38" s="5">
+        <v>46230.72179773149</v>
+      </c>
       <c r="D38" s="5">
-        <v>46230.60721100694</v>
+        <v>46230.7218775463</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>148</v>
@@ -3636,9 +3638,11 @@
       <c r="B40" s="5">
         <v>46230.6059374537</v>
       </c>
-      <c r="C40" s="6"/>
+      <c r="C40" s="5">
+        <v>46230.72178359954</v>
+      </c>
       <c r="D40" s="5">
-        <v>46230.607092314815</v>
+        <v>46230.72178535879</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>156</v>
@@ -4744,7 +4748,7 @@
         <v>46205.488692812505</v>
       </c>
       <c r="D58" s="5">
-        <v>46230.60689228009</v>
+        <v>46230.72180876158</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>216</v>

--- a/data/50001508 - XEMORTIZ STOCK.xlsx
+++ b/data/50001508 - XEMORTIZ STOCK.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="245">
   <si>
     <t>50001508 - XEMORTIZ STOCK</t>
   </si>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46213.509536840276</v>
+        <v>46241.58882872685</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>219</v>
@@ -4844,8 +4844,12 @@
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
       <c r="S59" s="10"/>
-      <c r="T59" s="10"/>
-      <c r="U59" s="10"/>
+      <c r="T59" s="10">
+        <v>1</v>
+      </c>
+      <c r="U59" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
@@ -4854,9 +4858,11 @@
       <c r="B60" s="5">
         <v>46073.57441722222</v>
       </c>
-      <c r="C60" s="6"/>
+      <c r="C60" s="5">
+        <v>46241.58875648148</v>
+      </c>
       <c r="D60" s="5">
-        <v>46225.55231209491</v>
+        <v>46241.58877232639</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>222</v>
@@ -4902,10 +4908,10 @@
         <v>32</v>
       </c>
       <c r="T60" s="6">
-        <v>0</v>
-      </c>
-      <c r="U60" s="12" t="s">
-        <v>132</v>
+        <v>1</v>
+      </c>
+      <c r="U60" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -4919,7 +4925,7 @@
         <v>46213.509524988425</v>
       </c>
       <c r="D61" s="9">
-        <v>46223.811153622686</v>
+        <v>46241.58877274305</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>228</v>
@@ -4967,8 +4973,8 @@
       <c r="T61" s="10">
         <v>1</v>
       </c>
-      <c r="U61" s="7" t="s">
-        <v>27</v>
+      <c r="U61" s="12" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5043,9 +5049,11 @@
       <c r="B63" s="9">
         <v>46073.57441800926</v>
       </c>
-      <c r="C63" s="10"/>
+      <c r="C63" s="9">
+        <v>46241.58878601852</v>
+      </c>
       <c r="D63" s="9">
-        <v>46205.89695172454</v>
+        <v>46241.58880578703</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>234</v>
@@ -5093,10 +5101,10 @@
         <v>32</v>
       </c>
       <c r="T63" s="10">
-        <v>0</v>
-      </c>
-      <c r="U63" s="12" t="s">
-        <v>132</v>
+        <v>1</v>
+      </c>
+      <c r="U63" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5155,7 +5163,7 @@
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46121.167010115736</v>
+        <v>46241.58880346065</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>240</v>
@@ -5205,8 +5213,8 @@
       <c r="T65" s="10">
         <v>0</v>
       </c>
-      <c r="U65" s="11" t="s">
-        <v>93</v>
+      <c r="U65" s="12" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5218,7 +5226,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46121.16701012732</v>
+        <v>46241.58880321759</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>244</v>
@@ -5268,8 +5276,8 @@
       <c r="T66" s="6">
         <v>0</v>
       </c>
-      <c r="U66" s="11" t="s">
-        <v>93</v>
+      <c r="U66" s="12" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001508 - XEMORTIZ STOCK.xlsx
+++ b/data/50001508 - XEMORTIZ STOCK.xlsx
@@ -4807,9 +4807,11 @@
       <c r="B59" s="9">
         <v>46073.574416874995</v>
       </c>
-      <c r="C59" s="10"/>
+      <c r="C59" s="9">
+        <v>46244.56617951389</v>
+      </c>
       <c r="D59" s="9">
-        <v>46241.58882872685</v>
+        <v>46244.56618136574</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>219</v>

--- a/data/50001508 - XEMORTIZ STOCK.xlsx
+++ b/data/50001508 - XEMORTIZ STOCK.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="245">
   <si>
     <t>50001508 - XEMORTIZ STOCK</t>
   </si>
@@ -5116,9 +5116,11 @@
       <c r="B64" s="5">
         <v>46073.574418275464</v>
       </c>
-      <c r="C64" s="6"/>
+      <c r="C64" s="5">
+        <v>46251.941438009264</v>
+      </c>
       <c r="D64" s="5">
-        <v>46090.70182164352</v>
+        <v>46251.9414521412</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>237</v>
@@ -5153,8 +5155,12 @@
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
       <c r="S64" s="6"/>
-      <c r="T64" s="6"/>
-      <c r="U64" s="6"/>
+      <c r="T64" s="6">
+        <v>1</v>
+      </c>
+      <c r="U64" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
@@ -5163,9 +5169,11 @@
       <c r="B65" s="9">
         <v>46073.57441857639</v>
       </c>
-      <c r="C65" s="10"/>
+      <c r="C65" s="9">
+        <v>46251.94140861111</v>
+      </c>
       <c r="D65" s="9">
-        <v>46241.58880346065</v>
+        <v>46251.94143015046</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>240</v>
@@ -5213,10 +5221,10 @@
         <v>32</v>
       </c>
       <c r="T65" s="10">
-        <v>0</v>
-      </c>
-      <c r="U65" s="12" t="s">
-        <v>132</v>
+        <v>1</v>
+      </c>
+      <c r="U65" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5226,9 +5234,11 @@
       <c r="B66" s="5">
         <v>46073.57441884259</v>
       </c>
-      <c r="C66" s="6"/>
+      <c r="C66" s="5">
+        <v>46251.94142050926</v>
+      </c>
       <c r="D66" s="5">
-        <v>46241.58880321759</v>
+        <v>46251.94144018518</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>244</v>
@@ -5276,10 +5286,10 @@
         <v>32</v>
       </c>
       <c r="T66" s="6">
-        <v>0</v>
-      </c>
-      <c r="U66" s="12" t="s">
-        <v>132</v>
+        <v>1</v>
+      </c>
+      <c r="U66" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
